--- a/VerveStacks_DZA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DZA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E210A12A-2A91-45E9-BF9D-5883C6F48BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6307C349-8B88-41D7-B4BC-9E09033B7D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1286,18 +1286,252 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_036</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 36</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_061</t>
   </si>
   <si>
@@ -1310,72 +1544,6 @@
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_042</t>
   </si>
   <si>
@@ -1400,22 +1568,94 @@
     <t>connecting solar to buses in cluster 57</t>
   </si>
   <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
   </si>
   <si>
     <t>distr_solelc_spv_043</t>
@@ -1442,291 +1682,126 @@
     <t>connecting solar to buses in cluster 60</t>
   </si>
   <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w1056389360-220,e_w993660788-220,e_w217933343-220,e_w217926708-220,e_DZ152-220,e_w292487199-220</t>
+  </si>
+  <si>
+    <t>e_w637266751-220,e_w293224489-220</t>
+  </si>
+  <si>
+    <t>e_w293467436-220,e_w261824495-220,e_w261824497-220,e_w380271836-220,e_DZ138-220</t>
+  </si>
+  <si>
+    <t>e_w292110924-220,e_w226922540-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w381517754-220</t>
+  </si>
+  <si>
+    <t>e_DZ65-400,e_DZ64-220,e_DZ60-220,e_w377716686-400,e_DZ91-220,e_DZ50-400,e_w371593266-220</t>
+  </si>
+  <si>
+    <t>e_DZ73-220,e_w107655510-220,e_w221085150-400,e_DZ10-220,e_DZ53-220,e_DZ8-220,e_DZ49-220,e_DZ37-220</t>
+  </si>
+  <si>
+    <t>e_DZ80-220,e_w294673631-220,e_DZ23-220,e_w226392269-400,e_DZ51-220,e_w385608518-220</t>
+  </si>
+  <si>
+    <t>e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
+  </si>
+  <si>
+    <t>e_w293224489-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220,e_w227962923-220,e_w292110924-220,e_w569616494-220,e_w1056389360-220</t>
+  </si>
+  <si>
+    <t>e_w637266751-220</t>
+  </si>
+  <si>
+    <t>e_w575738414-220,e_DZ128-400,e_w390634433-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w226918874-220,e_w1167367928-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_DZ160-220,e_w227962923-220,e_w569616494-220</t>
+  </si>
+  <si>
+    <t>e_DZ130-220,e_w173805804-220,e_DZ126-220,e_DZ118-220</t>
+  </si>
+  <si>
+    <t>e_w174338940-220,e_w359380463-400,e_DZ118-220,e_w174347010-220,e_DZ103-220,e_DZ74-220</t>
+  </si>
+  <si>
+    <t>e_DZ87-400,e_w174171686-220,e_DZ85-220,e_w936350097-220,e_w340227647-220</t>
+  </si>
+  <si>
+    <t>e_w261824495-220,e_w1031001205-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w1167367928-220,e_w226918874-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220</t>
+  </si>
+  <si>
+    <t>e_w293467436-220,e_w381517754-220,e_DZ130-220,e_w261824495-220</t>
+  </si>
+  <si>
+    <t>e_w226922540-220</t>
+  </si>
+  <si>
+    <t>e_w1377912118-400,e_w387845900-220,e_w312609390-220,e_w390634433-220,e_w380645355-220,e_DZ86-225</t>
+  </si>
+  <si>
+    <t>e_w637266751-220,e_w293224489-220,e_w262778514-220,e_w262778513-220</t>
+  </si>
+  <si>
+    <t>e_DZ118-220,e_w1031001205-220,e_DZ103-220,e_DZ115-220</t>
+  </si>
+  <si>
+    <t>e_w1031851533-220,e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220</t>
+  </si>
+  <si>
+    <t>e_DZ145-220,e_w317645796-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220,e_w310510674-220</t>
+  </si>
+  <si>
+    <t>e_w226922540-220,e_w637266751-220</t>
+  </si>
+  <si>
+    <t>e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_w217930454-220,e_w217933346-220,e_DZ156-220,e_DZ145-220,e_DZ159-220,e_w262778515-220</t>
+  </si>
+  <si>
+    <t>e_DZ75-220,e_w176684982-220,e_w175343993-220,e_w174512286-400,e_w694011253-400,e_w694000748-220,e_w175176155-220,e_w177011339-220</t>
+  </si>
+  <si>
+    <t>e_DZ40-220,e_DZ3-220,e_w379387167-220,e_w173534563-220,e_w177004931-220,e_DZ7-220,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>e_w637288557-220,e_w262778515-220,e_w262778513-220</t>
+  </si>
+  <si>
     <t>e_w310510674-220,e_w293467436-220,e_w569616494-220</t>
   </si>
   <si>
-    <t>e_w292110924-220,e_w226922540-220</t>
-  </si>
-  <si>
     <t>e_w993660788-220,e_DZ150-220,e_w217933343-220,e_DZ149-220,e_DZ152-220,e_w217933346-220,e_DZ148-220</t>
   </si>
   <si>
-    <t>e_w310510674-220,e_w226918874-220,e_w1167367928-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_DZ160-220,e_w227962923-220,e_w569616494-220</t>
-  </si>
-  <si>
-    <t>e_DZ130-220,e_w173805804-220,e_DZ126-220,e_DZ118-220</t>
-  </si>
-  <si>
-    <t>e_w174338940-220,e_w359380463-400,e_DZ118-220,e_w174347010-220,e_DZ103-220,e_DZ74-220</t>
-  </si>
-  <si>
-    <t>e_DZ87-400,e_w174171686-220,e_DZ85-220,e_w936350097-220,e_w340227647-220</t>
-  </si>
-  <si>
-    <t>e_w261824495-220,e_w1031001205-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220,e_w227962923-220,e_w292110924-220,e_w569616494-220,e_w1056389360-220</t>
-  </si>
-  <si>
-    <t>e_w637266751-220</t>
-  </si>
-  <si>
-    <t>e_w575738414-220,e_DZ128-400,e_w390634433-220</t>
-  </si>
-  <si>
     <t>e_w310510674-220,e_DZ160-220</t>
   </si>
   <si>
@@ -1736,19 +1811,37 @@
     <t>e_w380271836-400,e_DZ133-220,e_DZ150-220,e_w1031851533-220</t>
   </si>
   <si>
-    <t>e_w226922540-220,e_w637266751-220</t>
-  </si>
-  <si>
-    <t>e_DZ80-220,e_w294673631-220,e_DZ23-220,e_w226392269-400,e_DZ51-220,e_w385608518-220</t>
-  </si>
-  <si>
-    <t>e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
-  </si>
-  <si>
-    <t>e_w293224489-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220</t>
+    <t>e_w569616494-220,e_w293467436-220,e_w261824497-220,e_w1056389360-220,e_w993660788-220</t>
+  </si>
+  <si>
+    <t>e_w993660788-220,e_w261824497-220,e_w380271836-220,e_DZ150-220,e_w217933343-220</t>
+  </si>
+  <si>
+    <t>e_DZ125-220,e_w1031851533-220,e_DZ121-220,e_w226886714-220,e_w317645604-220,e_w694205382-220,e_w694205380-220,e_w365883660-220,e_w575738414-220,e_w694000747-400</t>
+  </si>
+  <si>
+    <t>e_w637266751-220,e_DZ159-220,e_w293224489-220,e_w476360977-220</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ129-220,e_DZ124-220,e_DZ113-400,e_w381266482-220,e_DZ102-220,e_w174342293-220,e_DZ88-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w292110924-220</t>
+  </si>
+  <si>
+    <t>e_DZ132-220,e_w173808767-220,e_w833562295-400,e_DZ131-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w292110924-220,e_w226922540-220,e_w1056389360-220</t>
+  </si>
+  <si>
+    <t>e_DZ137-220,e_w261824495-220,e_DZ138-220,e_w380271836-220,e_w43843800-220</t>
+  </si>
+  <si>
+    <t>e_w226922540-220,e_w1056389360-220,e_w637266751-220</t>
+  </si>
+  <si>
+    <t>e_w1056389360-220,e_w637266751-220,e_w217926708-220</t>
   </si>
   <si>
     <t>e_DZ114-220,e_DZ73-220,e_w221085150-220,e_DZ125-220,e_w226879630-220,e_w381355305-220</t>
@@ -1757,97 +1850,172 @@
     <t>e_w226922540-220,e_w637266751-220,e_w293224489-220</t>
   </si>
   <si>
-    <t>e_w1056389360-220,e_w993660788-220,e_w217933343-220,e_w217926708-220,e_DZ152-220,e_w292487199-220</t>
-  </si>
-  <si>
-    <t>e_w637266751-220,e_w293224489-220</t>
-  </si>
-  <si>
-    <t>e_w569616494-220,e_w293467436-220,e_w261824497-220,e_w1056389360-220,e_w993660788-220</t>
-  </si>
-  <si>
-    <t>e_w993660788-220,e_w261824497-220,e_w380271836-220,e_DZ150-220,e_w217933343-220</t>
-  </si>
-  <si>
-    <t>e_DZ125-220,e_w1031851533-220,e_DZ121-220,e_w226886714-220,e_w317645604-220,e_w694205382-220,e_w694205380-220,e_w365883660-220,e_w575738414-220,e_w694000747-400</t>
-  </si>
-  <si>
-    <t>e_w637266751-220,e_DZ159-220,e_w293224489-220,e_w476360977-220</t>
-  </si>
-  <si>
-    <t>e_w1056389360-220,e_w637266751-220,e_w217926708-220</t>
-  </si>
-  <si>
-    <t>e_DZ118-220,e_w1031001205-220,e_DZ103-220,e_DZ115-220</t>
-  </si>
-  <si>
-    <t>e_w1031851533-220,e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220</t>
-  </si>
-  <si>
-    <t>e_DZ145-220,e_w317645796-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>e_w293467436-220,e_w261824495-220,e_w261824497-220,e_w380271836-220,e_DZ138-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w1167367928-220,e_w226918874-220</t>
-  </si>
-  <si>
-    <t>e_w293467436-220,e_w381517754-220,e_DZ130-220,e_w261824495-220</t>
-  </si>
-  <si>
-    <t>e_w226922540-220</t>
-  </si>
-  <si>
-    <t>e_w1377912118-400,e_w387845900-220,e_w312609390-220,e_w390634433-220,e_w380645355-220,e_DZ86-225</t>
-  </si>
-  <si>
-    <t>e_w637266751-220,e_w293224489-220,e_w262778514-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>e_w637288557-220,e_w262778515-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w381517754-220</t>
-  </si>
-  <si>
-    <t>e_DZ65-400,e_DZ64-220,e_DZ60-220,e_w377716686-400,e_DZ91-220,e_DZ50-400,e_w371593266-220</t>
-  </si>
-  <si>
-    <t>e_DZ73-220,e_w107655510-220,e_w221085150-400,e_DZ10-220,e_DZ53-220,e_DZ8-220,e_DZ49-220,e_DZ37-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220,e_w310510674-220</t>
-  </si>
-  <si>
-    <t>e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_w217930454-220,e_w217933346-220,e_DZ156-220,e_DZ145-220,e_DZ159-220,e_w262778515-220</t>
-  </si>
-  <si>
-    <t>e_DZ75-220,e_w176684982-220,e_w175343993-220,e_w174512286-400,e_w694011253-400,e_w694000748-220,e_w175176155-220,e_w177011339-220</t>
-  </si>
-  <si>
-    <t>e_DZ40-220,e_DZ3-220,e_w379387167-220,e_w173534563-220,e_w177004931-220,e_DZ7-220,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>e_DZ127-220,e_DZ129-220,e_DZ124-220,e_DZ113-400,e_w381266482-220,e_DZ102-220,e_w174342293-220,e_DZ88-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w292110924-220</t>
-  </si>
-  <si>
-    <t>e_DZ132-220,e_w173808767-220,e_w833562295-400,e_DZ131-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w292110924-220,e_w226922540-220,e_w1056389360-220</t>
-  </si>
-  <si>
-    <t>e_DZ137-220,e_w261824495-220,e_DZ138-220,e_w380271836-220,e_w43843800-220</t>
-  </si>
-  <si>
-    <t>e_w226922540-220,e_w1056389360-220,e_w637266751-220</t>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_wonelc_won_032</t>
@@ -1874,58 +2042,94 @@
     <t>connecting wind onshore to buses in cluster 60</t>
   </si>
   <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1958,28 +2162,64 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_wonelc_won_053</t>
@@ -2000,244 +2240,124 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_DZ160-220,e_w310510674-220,e_w227962923-220,e_w569616494-220</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_w292110924-220,e_w227962923-220,e_w1056389360-220,e_w226922540-220</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w1056389360-220,e_w569616494-220,e_w993660788-220,e_w217933343-220,e_w637266751-220,e_w217926708-220</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w261824495-220,e_w1031001205-220,e_DZ118-220,e_DZ115-220,e_w226985195-220</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_DZ150-220,e_w380271836-400,e_w993660788-220,e_w1031851533-220,e_w217933343-220,e_DZ149-220,e_w217941443-220,e_DZ148-220</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w226918874-220</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w694000748-220,e_w175176155-220,e_w387845900-220,e_w312609390-220,e_DZ40-220,e_w390634433-220,e_w380645355-220,e_w379387167-220,e_DZ86-225,e_w177004931-220</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w226879630-220,e_DZ80-220,e_w294673631-220,e_w226392269-400,e_DZ51-220,e_w365883660-220,e_w385608518-220,e_DZ75-220,e_w694000747-400,e_w175343993-220,e_w174512286-400,e_w1377912118-400</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w226918874-220,e_DZ160-220</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w173808767-220,e_w833562295-400,e_DZ131-220,e_w381517754-220,e_DZ130-220,e_DZ126-220,e_w261824495-220</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_DZ124-220,e_DZ113-400,e_DZ107-220,e_DZ102-220,e_DZ88-220,e_DZ87-400,e_w174171686-220,e_w936350097-220,e_w340227647-220,e_DZ65-400,e_w377716686-400,e_w371593266-220,e_w107655510-220,e_DZ10-220,e_DZ8-220,e_DZ37-220</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_w569616494-220,e_w261824497-220,e_w261824495-220,e_w380271836-220,e_DZ138-220</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
   </si>
   <si>
     <t>elc_won_032</t>
@@ -2255,46 +2375,76 @@
     <t>e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220,e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
   </si>
   <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_DZ160-220,e_w310510674-220,e_w227962923-220,e_w569616494-220</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_w292110924-220,e_w227962923-220,e_w1056389360-220,e_w226922540-220</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w1056389360-220,e_w569616494-220,e_w993660788-220,e_w217933343-220,e_w637266751-220,e_w217926708-220</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w261824495-220,e_w1031001205-220,e_DZ118-220,e_DZ115-220,e_w226985195-220</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_DZ150-220,e_w380271836-400,e_w993660788-220,e_w1031851533-220,e_w217933343-220,e_DZ149-220,e_w217941443-220,e_DZ148-220</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ132-220,e_DZ129-220,e_w173808767-220,e_DZ131-220</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_w993660788-220,e_w217933343-220,e_DZ152-220,e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_DZ156-220,e_DZ159-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w637266751-220,e_w217926708-220,e_w293224489-220</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_w217933346-220,e_w217930454-220,e_w292487199-220,e_DZ145-220,e_w317645796-220,e_w262778515-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_w293467436-220,e_w381517754-220,e_w261824495-220,e_DZ137-220,e_DZ138-220,e_w380271836-220,e_w43843800-220,e_w380271836-400,e_DZ133-220,e_DZ125-220</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_DZ74-220,e_DZ103-220,e_DZ64-220,e_DZ60-220,e_DZ115-220,e_DZ91-220,e_DZ50-400,e_DZ114-220,e_DZ73-220,e_w221085150-220,e_w221085150-400,e_w226879630-220,e_DZ53-220</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w381266482-220,e_w173805804-220,e_w174342293-220,e_DZ130-220,e_w174338940-220,e_DZ126-220,e_w359380463-400,e_DZ85-220,e_DZ118-220,e_w174347010-220,e_DZ103-220</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_DZ125-220,e_w1031851533-220,e_w381355305-220,e_DZ121-220,e_w226886714-220,e_w1033643187-220,e_w317645604-220,e_w694205382-220,e_w694205380-220</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w217926708-220,e_w637266751-220,e_DZ156-220,e_DZ159-220,e_w293224489-220,e_w476360977-220,e_w637288557-220,e_w262778515-220,e_w262778513-220,e_w262778514-220</t>
   </si>
   <si>
     <t>elc_won_011</t>
@@ -2318,25 +2468,49 @@
     <t>elc_won_010</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w381266482-220,e_w173805804-220,e_w174342293-220,e_DZ130-220,e_w174338940-220,e_DZ126-220,e_w359380463-400,e_DZ85-220,e_DZ118-220,e_w174347010-220,e_DZ103-220</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_DZ125-220,e_w1031851533-220,e_w381355305-220,e_DZ121-220,e_w226886714-220,e_w1033643187-220,e_w317645604-220,e_w694205382-220,e_w694205380-220</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w217926708-220,e_w637266751-220,e_DZ156-220,e_DZ159-220,e_w293224489-220,e_w476360977-220,e_w637288557-220,e_w262778515-220,e_w262778513-220,e_w262778514-220</t>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>e_w226918874-220,e_DZ160-220,e_w1167367928-220,e_w227962923-220,e_w569616494-220</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_w227962923-220,e_w569616494-220,e_w1056389360-220</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w569616494-220,e_w261824497-220,e_w993660788-220</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_DZ23-220,e_DZ34-220,e_w176684982-220,e_w694011253-400,e_w177011339-220,e_DZ3-220,e_w173534563-220,e_DZ7-220,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
   </si>
   <si>
     <t>elc_won_053</t>
@@ -2351,178 +2525,34 @@
     <t>elc_won_016</t>
   </si>
   <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w226918874-220,e_DZ160-220</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w173808767-220,e_w833562295-400,e_DZ131-220,e_w381517754-220,e_DZ130-220,e_DZ126-220,e_w261824495-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_DZ124-220,e_DZ113-400,e_DZ107-220,e_DZ102-220,e_DZ88-220,e_DZ87-400,e_w174171686-220,e_w936350097-220,e_w340227647-220,e_DZ65-400,e_w377716686-400,e_w371593266-220,e_w107655510-220,e_DZ10-220,e_DZ8-220,e_DZ37-220</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_w569616494-220,e_w261824497-220,e_w261824495-220,e_w380271836-220,e_DZ138-220</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_w293467436-220,e_w381517754-220,e_w261824495-220,e_DZ137-220,e_DZ138-220,e_w380271836-220,e_w43843800-220,e_w380271836-400,e_DZ133-220,e_DZ125-220</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_DZ74-220,e_DZ103-220,e_DZ64-220,e_DZ60-220,e_DZ115-220,e_DZ91-220,e_DZ50-400,e_DZ114-220,e_DZ73-220,e_w221085150-220,e_w221085150-400,e_w226879630-220,e_DZ53-220</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_DZ127-220,e_DZ132-220,e_DZ129-220,e_w173808767-220,e_DZ131-220</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_w993660788-220,e_w217933343-220,e_DZ152-220,e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_DZ156-220,e_DZ159-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w637266751-220,e_w217926708-220,e_w293224489-220</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_w217933346-220,e_w217930454-220,e_w292487199-220,e_DZ145-220,e_w317645796-220,e_w262778515-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w569616494-220,e_w261824497-220,e_w993660788-220</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_DZ23-220,e_DZ34-220,e_w176684982-220,e_w694011253-400,e_w177011339-220,e_DZ3-220,e_w173534563-220,e_DZ7-220,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w226918874-220</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w694000748-220,e_w175176155-220,e_w387845900-220,e_w312609390-220,e_DZ40-220,e_w390634433-220,e_w380645355-220,e_w379387167-220,e_DZ86-225,e_w177004931-220</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w226879630-220,e_DZ80-220,e_w294673631-220,e_w226392269-400,e_DZ51-220,e_w365883660-220,e_w385608518-220,e_DZ75-220,e_w694000747-400,e_w175343993-220,e_w174512286-400,e_w1377912118-400</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>e_w226918874-220,e_DZ160-220,e_w1167367928-220,e_w227962923-220,e_w569616494-220</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_w227962923-220,e_w569616494-220,e_w1056389360-220</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_010</t>
@@ -2531,30 +2561,18 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_008</t>
   </si>
   <si>
@@ -2567,22 +2585,34 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_DZ1-400,e_DZ7-220</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ113-400</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_DZ42-220,e_w377716686-400</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ124-220</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_DZ5-220,e_w694011253-400</t>
   </si>
   <si>
     <t>elc_wof_010</t>
@@ -2591,30 +2621,18 @@
     <t>e_DZ88-220</t>
   </si>
   <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_DZ5-220,e_w694011253-400</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_DZ127-220,e_DZ124-220</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_DZ1-400,e_DZ7-220</t>
-  </si>
-  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
     <t>e_DZ107-220,e_DZ102-220</t>
   </si>
   <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w172698243-220,e_w107655510-220,e_DZ10-220</t>
+  </si>
+  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
@@ -2625,24 +2643,6 @@
   </si>
   <si>
     <t>e_w176932220-400,e_DZ3-220</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w172698243-220,e_w107655510-220,e_DZ10-220</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_DZ127-220,e_DZ113-400</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_DZ42-220,e_w377716686-400</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8461,7 +8461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51C47B8-BC30-4990-AF10-B51C1C754798}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0999DBAF-E388-4EE4-B97C-500ACA1273FC}">
   <dimension ref="B9:BD75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8699,16 +8699,16 @@
         <v>385</v>
       </c>
       <c r="Y11" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="Z11" t="s">
         <v>519</v>
       </c>
       <c r="AA11">
-        <v>0.99140122988281854</v>
+        <v>0.98979380819350882</v>
       </c>
       <c r="AB11">
-        <v>157.64411881499262</v>
+        <v>187.11351645233776</v>
       </c>
       <c r="AD11" t="s">
         <v>384</v>
@@ -8738,13 +8738,13 @@
         <v>703</v>
       </c>
       <c r="AN11" t="s">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="AO11">
-        <v>0.97927855406064401</v>
+        <v>0.97500946832970314</v>
       </c>
       <c r="AP11">
-        <v>379.89317555486042</v>
+        <v>458.15974728877472</v>
       </c>
       <c r="AR11" t="s">
         <v>384</v>
@@ -8777,10 +8777,10 @@
         <v>819</v>
       </c>
       <c r="BC11">
-        <v>0.99970264496455319</v>
+        <v>0.9965021251763384</v>
       </c>
       <c r="BD11">
-        <v>5.4515089831922632</v>
+        <v>64.127705100462705</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8845,16 +8845,16 @@
         <v>389</v>
       </c>
       <c r="Y12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Z12" t="s">
         <v>520</v>
       </c>
       <c r="AA12">
-        <v>0.95056191060937778</v>
+        <v>0.9798698468265471</v>
       </c>
       <c r="AB12">
-        <v>906.36497216140765</v>
+        <v>369.05280817996936</v>
       </c>
       <c r="AD12" t="s">
         <v>384</v>
@@ -8884,13 +8884,13 @@
         <v>704</v>
       </c>
       <c r="AN12" t="s">
-        <v>568</v>
+        <v>541</v>
       </c>
       <c r="AO12">
-        <v>0.99261416554290038</v>
+        <v>0.97657215376744144</v>
       </c>
       <c r="AP12">
-        <v>135.40696504682549</v>
+        <v>429.51051426357446</v>
       </c>
       <c r="AR12" t="s">
         <v>384</v>
@@ -8923,10 +8923,10 @@
         <v>821</v>
       </c>
       <c r="BC12">
-        <v>0.99690129108492354</v>
+        <v>0.99529500707002927</v>
       </c>
       <c r="BD12">
-        <v>56.809663443069056</v>
+        <v>86.258203716130154</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8991,16 +8991,16 @@
         <v>391</v>
       </c>
       <c r="Y13" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="Z13" t="s">
         <v>521</v>
       </c>
       <c r="AA13">
-        <v>0.99693870689560904</v>
+        <v>0.99038856814984766</v>
       </c>
       <c r="AB13">
-        <v>56.123706913834091</v>
+        <v>176.20958391945942</v>
       </c>
       <c r="AD13" t="s">
         <v>384</v>
@@ -9030,13 +9030,13 @@
         <v>705</v>
       </c>
       <c r="AN13" t="s">
-        <v>555</v>
+        <v>706</v>
       </c>
       <c r="AO13">
-        <v>0.94939310241101427</v>
+        <v>0.98402112024048205</v>
       </c>
       <c r="AP13">
-        <v>927.79312246473887</v>
+        <v>292.94612892449663</v>
       </c>
       <c r="AR13" t="s">
         <v>384</v>
@@ -9069,10 +9069,10 @@
         <v>823</v>
       </c>
       <c r="BC13">
-        <v>0.99801675448684013</v>
+        <v>0.99819616407025835</v>
       </c>
       <c r="BD13">
-        <v>36.359501074597006</v>
+        <v>33.070325378597239</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9137,16 +9137,16 @@
         <v>393</v>
       </c>
       <c r="Y14" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="Z14" t="s">
         <v>522</v>
       </c>
       <c r="AA14">
-        <v>0.95575770595896115</v>
+        <v>0.96778401809933534</v>
       </c>
       <c r="AB14">
-        <v>811.10872408571242</v>
+        <v>590.62633484551873</v>
       </c>
       <c r="AD14" t="s">
         <v>384</v>
@@ -9173,16 +9173,16 @@
         <v>579</v>
       </c>
       <c r="AM14" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AN14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AO14">
-        <v>0.99702300519026088</v>
+        <v>0.99471898599413955</v>
       </c>
       <c r="AP14">
-        <v>54.578238178550102</v>
+        <v>96.818590107441551</v>
       </c>
       <c r="AR14" t="s">
         <v>384</v>
@@ -9215,10 +9215,10 @@
         <v>825</v>
       </c>
       <c r="BC14">
-        <v>0.9965021251763384</v>
+        <v>0.99801675448684013</v>
       </c>
       <c r="BD14">
-        <v>64.127705100462705</v>
+        <v>36.359501074597006</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9283,16 +9283,16 @@
         <v>395</v>
       </c>
       <c r="Y15" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="Z15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AA15">
-        <v>0.95951701524155131</v>
+        <v>0.98023840447090371</v>
       </c>
       <c r="AB15">
-        <v>742.18805390489183</v>
+        <v>362.29591803343288</v>
       </c>
       <c r="AD15" t="s">
         <v>384</v>
@@ -9319,16 +9319,16 @@
         <v>581</v>
       </c>
       <c r="AM15" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AN15" t="s">
-        <v>523</v>
+        <v>710</v>
       </c>
       <c r="AO15">
-        <v>0.97500946832970314</v>
+        <v>0.98741925140550357</v>
       </c>
       <c r="AP15">
-        <v>458.15974728877472</v>
+        <v>230.64705756576762</v>
       </c>
       <c r="AR15" t="s">
         <v>384</v>
@@ -9361,10 +9361,10 @@
         <v>827</v>
       </c>
       <c r="BC15">
-        <v>0.99790771621959851</v>
+        <v>0.99690129108492354</v>
       </c>
       <c r="BD15">
-        <v>38.358535974026807</v>
+        <v>56.809663443069056</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9429,16 +9429,16 @@
         <v>397</v>
       </c>
       <c r="Y16" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="Z16" t="s">
         <v>523</v>
       </c>
       <c r="AA16">
-        <v>0.98916491572478116</v>
+        <v>0.96873365246705256</v>
       </c>
       <c r="AB16">
-        <v>198.64321171234531</v>
+        <v>573.2163714373695</v>
       </c>
       <c r="AD16" t="s">
         <v>384</v>
@@ -9465,16 +9465,16 @@
         <v>583</v>
       </c>
       <c r="AM16" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AN16" t="s">
-        <v>539</v>
+        <v>712</v>
       </c>
       <c r="AO16">
-        <v>0.97657215376744144</v>
+        <v>0.99775066197427953</v>
       </c>
       <c r="AP16">
-        <v>429.51051426357446</v>
+        <v>41.237863804874586</v>
       </c>
       <c r="AR16" t="s">
         <v>384</v>
@@ -9507,10 +9507,10 @@
         <v>829</v>
       </c>
       <c r="BC16">
-        <v>0.99767880649372143</v>
+        <v>0.99970264496455319</v>
       </c>
       <c r="BD16">
-        <v>42.555214281773615</v>
+        <v>5.4515089831922632</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9575,16 +9575,16 @@
         <v>399</v>
       </c>
       <c r="Y17" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="Z17" t="s">
         <v>524</v>
       </c>
       <c r="AA17">
-        <v>0.99211425265089781</v>
+        <v>0.99513490828923246</v>
       </c>
       <c r="AB17">
-        <v>144.5720347335392</v>
+        <v>89.193348030739003</v>
       </c>
       <c r="AD17" t="s">
         <v>384</v>
@@ -9611,16 +9611,16 @@
         <v>585</v>
       </c>
       <c r="AM17" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="AN17" t="s">
-        <v>711</v>
+        <v>543</v>
       </c>
       <c r="AO17">
-        <v>0.98402112024048205</v>
+        <v>0.96555290739289967</v>
       </c>
       <c r="AP17">
-        <v>292.94612892449663</v>
+        <v>631.53003113017269</v>
       </c>
       <c r="AR17" t="s">
         <v>384</v>
@@ -9653,10 +9653,10 @@
         <v>831</v>
       </c>
       <c r="BC17">
-        <v>0.99766851268386103</v>
+        <v>0.99790771621959851</v>
       </c>
       <c r="BD17">
-        <v>42.743934129214161</v>
+        <v>38.358535974026807</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9721,16 +9721,16 @@
         <v>401</v>
       </c>
       <c r="Y18" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="Z18" t="s">
         <v>525</v>
       </c>
       <c r="AA18">
-        <v>0.99704781228873474</v>
+        <v>0.99859143525552441</v>
       </c>
       <c r="AB18">
-        <v>54.123441373196478</v>
+        <v>25.823686982052106</v>
       </c>
       <c r="AD18" t="s">
         <v>384</v>
@@ -9757,16 +9757,16 @@
         <v>587</v>
       </c>
       <c r="AM18" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AN18" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AO18">
-        <v>0.99471898599413955</v>
+        <v>0.99626371781833423</v>
       </c>
       <c r="AP18">
-        <v>96.818590107441551</v>
+        <v>68.49850666387222</v>
       </c>
       <c r="AR18" t="s">
         <v>384</v>
@@ -9867,16 +9867,16 @@
         <v>403</v>
       </c>
       <c r="Y19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Z19" t="s">
         <v>526</v>
       </c>
       <c r="AA19">
-        <v>0.99928861254927026</v>
+        <v>0.99942899655278006</v>
       </c>
       <c r="AB19">
-        <v>13.04210326337761</v>
+        <v>10.468396532365567</v>
       </c>
       <c r="AD19" t="s">
         <v>384</v>
@@ -9903,16 +9903,16 @@
         <v>589</v>
       </c>
       <c r="AM19" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AN19" t="s">
-        <v>715</v>
+        <v>550</v>
       </c>
       <c r="AO19">
-        <v>0.98741925140550357</v>
+        <v>0.97107796146874092</v>
       </c>
       <c r="AP19">
-        <v>230.64705756576762</v>
+        <v>530.23737307308215</v>
       </c>
       <c r="AR19" t="s">
         <v>384</v>
@@ -9945,10 +9945,10 @@
         <v>835</v>
       </c>
       <c r="BC19">
-        <v>0.99529500707002927</v>
+        <v>0.99767880649372143</v>
       </c>
       <c r="BD19">
-        <v>86.258203716130154</v>
+        <v>42.555214281773615</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10013,16 +10013,16 @@
         <v>405</v>
       </c>
       <c r="Y20" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="Z20" t="s">
         <v>527</v>
       </c>
       <c r="AA20">
-        <v>0.99918279077066829</v>
+        <v>0.99883776385939382</v>
       </c>
       <c r="AB20">
-        <v>14.982169204414204</v>
+        <v>21.30766257777988</v>
       </c>
       <c r="AD20" t="s">
         <v>384</v>
@@ -10049,16 +10049,16 @@
         <v>591</v>
       </c>
       <c r="AM20" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AN20" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AO20">
-        <v>0.99775066197427953</v>
+        <v>0.95357273401837306</v>
       </c>
       <c r="AP20">
-        <v>41.237863804874586</v>
+        <v>851.1665429964944</v>
       </c>
       <c r="AR20" t="s">
         <v>384</v>
@@ -10091,10 +10091,10 @@
         <v>837</v>
       </c>
       <c r="BC20">
-        <v>0.99819616407025835</v>
+        <v>0.99766851268386103</v>
       </c>
       <c r="BD20">
-        <v>33.070325378597239</v>
+        <v>42.743934129214161</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10159,16 +10159,16 @@
         <v>407</v>
       </c>
       <c r="Y21" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="Z21" t="s">
         <v>528</v>
       </c>
       <c r="AA21">
-        <v>0.99701498192870486</v>
+        <v>0.99648965438197512</v>
       </c>
       <c r="AB21">
-        <v>54.725331307078172</v>
+        <v>64.356336330456202</v>
       </c>
       <c r="AD21" t="s">
         <v>384</v>
@@ -10195,16 +10195,16 @@
         <v>593</v>
       </c>
       <c r="AM21" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AN21" t="s">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="AO21">
-        <v>0.96555290739289967</v>
+        <v>0.98030978036614613</v>
       </c>
       <c r="AP21">
-        <v>631.53003113017269</v>
+        <v>360.98735995398783</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10269,16 +10269,16 @@
         <v>409</v>
       </c>
       <c r="Y22" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="Z22" t="s">
         <v>529</v>
       </c>
       <c r="AA22">
-        <v>0.99538973816509291</v>
+        <v>0.95021137372232145</v>
       </c>
       <c r="AB22">
-        <v>84.521466973297393</v>
+        <v>912.79148175744024</v>
       </c>
       <c r="AD22" t="s">
         <v>384</v>
@@ -10305,16 +10305,16 @@
         <v>595</v>
       </c>
       <c r="AM22" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AN22" t="s">
-        <v>720</v>
+        <v>543</v>
       </c>
       <c r="AO22">
-        <v>0.99626371781833423</v>
+        <v>0.96113902088653813</v>
       </c>
       <c r="AP22">
-        <v>68.49850666387222</v>
+        <v>712.45128374680007</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10379,16 +10379,16 @@
         <v>411</v>
       </c>
       <c r="Y23" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="Z23" t="s">
         <v>530</v>
       </c>
       <c r="AA23">
-        <v>0.98685658514563523</v>
+        <v>0.99538973816509291</v>
       </c>
       <c r="AB23">
-        <v>240.96260566335508</v>
+        <v>84.521466973297393</v>
       </c>
       <c r="AD23" t="s">
         <v>384</v>
@@ -10418,13 +10418,13 @@
         <v>721</v>
       </c>
       <c r="AN23" t="s">
-        <v>535</v>
+        <v>722</v>
       </c>
       <c r="AO23">
-        <v>0.97107796146874092</v>
+        <v>0.99849102734574458</v>
       </c>
       <c r="AP23">
-        <v>530.23737307308215</v>
+        <v>27.664498661350322</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10489,16 +10489,16 @@
         <v>413</v>
       </c>
       <c r="Y24" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="Z24" t="s">
         <v>531</v>
       </c>
       <c r="AA24">
-        <v>0.99775167610563054</v>
+        <v>0.98685658514563523</v>
       </c>
       <c r="AB24">
-        <v>41.219271396774424</v>
+        <v>240.96260566335508</v>
       </c>
       <c r="AD24" t="s">
         <v>384</v>
@@ -10525,16 +10525,16 @@
         <v>599</v>
       </c>
       <c r="AM24" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AN24" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="AO24">
-        <v>0.98080645969778191</v>
+        <v>0.99456229904023075</v>
       </c>
       <c r="AP24">
-        <v>351.88157220733245</v>
+        <v>99.691184262436323</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10599,16 +10599,16 @@
         <v>415</v>
       </c>
       <c r="Y25" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="Z25" t="s">
         <v>532</v>
       </c>
       <c r="AA25">
-        <v>0.97773943430281773</v>
+        <v>0.99775167610563054</v>
       </c>
       <c r="AB25">
-        <v>408.11037111500889</v>
+        <v>41.219271396774424</v>
       </c>
       <c r="AD25" t="s">
         <v>384</v>
@@ -10635,16 +10635,16 @@
         <v>601</v>
       </c>
       <c r="AM25" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AN25" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="AO25">
-        <v>0.98622313794978356</v>
+        <v>0.98179238163829652</v>
       </c>
       <c r="AP25">
-        <v>252.57580425396782</v>
+        <v>333.80633663123064</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10709,16 +10709,16 @@
         <v>417</v>
       </c>
       <c r="Y26" t="s">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="Z26" t="s">
         <v>533</v>
       </c>
       <c r="AA26">
-        <v>0.99711217881919312</v>
+        <v>0.95575770595896115</v>
       </c>
       <c r="AB26">
-        <v>52.943388314793616</v>
+        <v>811.10872408571242</v>
       </c>
       <c r="AD26" t="s">
         <v>384</v>
@@ -10745,16 +10745,16 @@
         <v>603</v>
       </c>
       <c r="AM26" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AN26" t="s">
-        <v>725</v>
+        <v>531</v>
       </c>
       <c r="AO26">
-        <v>0.99468247729100656</v>
+        <v>0.97994970755923727</v>
       </c>
       <c r="AP26">
-        <v>97.487916331546771</v>
+        <v>367.58869474731648</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10819,16 +10819,16 @@
         <v>419</v>
       </c>
       <c r="Y27" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="Z27" t="s">
         <v>534</v>
       </c>
       <c r="AA27">
-        <v>0.99520306771735667</v>
+        <v>0.95951701524155131</v>
       </c>
       <c r="AB27">
-        <v>87.943758515128479</v>
+        <v>742.18805390489183</v>
       </c>
       <c r="AD27" t="s">
         <v>384</v>
@@ -10858,13 +10858,13 @@
         <v>726</v>
       </c>
       <c r="AN27" t="s">
-        <v>727</v>
+        <v>520</v>
       </c>
       <c r="AO27">
-        <v>0.9861789081627198</v>
+        <v>0.96599440792497671</v>
       </c>
       <c r="AP27">
-        <v>253.38668368347109</v>
+        <v>623.43585470875962</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10929,16 +10929,16 @@
         <v>421</v>
       </c>
       <c r="Y28" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="Z28" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AA28">
-        <v>0.95279789096470435</v>
+        <v>0.98916491572478116</v>
       </c>
       <c r="AB28">
-        <v>865.37199898041979</v>
+        <v>198.64321171234531</v>
       </c>
       <c r="AD28" t="s">
         <v>384</v>
@@ -10965,16 +10965,16 @@
         <v>607</v>
       </c>
       <c r="AM28" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AN28" t="s">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="AO28">
-        <v>0.98988983533388286</v>
+        <v>0.96976012134850453</v>
       </c>
       <c r="AP28">
-        <v>185.35301887881516</v>
+        <v>554.39777527741785</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11039,16 +11039,16 @@
         <v>423</v>
       </c>
       <c r="Y29" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="Z29" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AA29">
-        <v>0.99883776385939382</v>
+        <v>0.99211425265089781</v>
       </c>
       <c r="AB29">
-        <v>21.30766257777988</v>
+        <v>144.5720347335392</v>
       </c>
       <c r="AD29" t="s">
         <v>384</v>
@@ -11075,16 +11075,16 @@
         <v>609</v>
       </c>
       <c r="AM29" t="s">
+        <v>728</v>
+      </c>
+      <c r="AN29" t="s">
         <v>729</v>
       </c>
-      <c r="AN29" t="s">
-        <v>730</v>
-      </c>
       <c r="AO29">
-        <v>0.99878024082202155</v>
+        <v>0.99893003381794343</v>
       </c>
       <c r="AP29">
-        <v>22.362251596271118</v>
+        <v>19.616046671036653</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11149,16 +11149,16 @@
         <v>425</v>
       </c>
       <c r="Y30" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="Z30" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AA30">
-        <v>0.99648965438197512</v>
+        <v>0.99704781228873474</v>
       </c>
       <c r="AB30">
-        <v>64.356336330456202</v>
+        <v>54.123441373196478</v>
       </c>
       <c r="AD30" t="s">
         <v>384</v>
@@ -11185,16 +11185,16 @@
         <v>611</v>
       </c>
       <c r="AM30" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AN30" t="s">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="AO30">
-        <v>0.95826105465484257</v>
+        <v>0.96939675941164705</v>
       </c>
       <c r="AP30">
-        <v>765.21399799455378</v>
+        <v>561.05941078647095</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11259,16 +11259,16 @@
         <v>427</v>
       </c>
       <c r="Y31" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="Z31" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AA31">
-        <v>0.95021137372232145</v>
+        <v>0.99928861254927026</v>
       </c>
       <c r="AB31">
-        <v>912.79148175744024</v>
+        <v>13.04210326337761</v>
       </c>
       <c r="AD31" t="s">
         <v>384</v>
@@ -11295,16 +11295,16 @@
         <v>613</v>
       </c>
       <c r="AM31" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AN31" t="s">
-        <v>733</v>
+        <v>532</v>
       </c>
       <c r="AO31">
-        <v>0.99750387705430998</v>
+        <v>0.99774195493840256</v>
       </c>
       <c r="AP31">
-        <v>45.762254004316212</v>
+        <v>41.397492795953291</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11369,16 +11369,16 @@
         <v>429</v>
       </c>
       <c r="Y32" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="Z32" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA32">
-        <v>0.96752396217182168</v>
+        <v>0.99918279077066829</v>
       </c>
       <c r="AB32">
-        <v>595.39402684993593</v>
+        <v>14.982169204414204</v>
       </c>
       <c r="AD32" t="s">
         <v>384</v>
@@ -11405,16 +11405,16 @@
         <v>615</v>
       </c>
       <c r="AM32" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AN32" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="AO32">
-        <v>0.99561014484129162</v>
+        <v>0.96887169792625616</v>
       </c>
       <c r="AP32">
-        <v>80.480677909653664</v>
+        <v>570.68553801863686</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -11479,16 +11479,16 @@
         <v>431</v>
       </c>
       <c r="Y33" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
       <c r="Z33" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="AA33">
-        <v>0.96000937928358443</v>
+        <v>0.99701498192870486</v>
       </c>
       <c r="AB33">
-        <v>733.16137980095198</v>
+        <v>54.725331307078172</v>
       </c>
       <c r="AD33" t="s">
         <v>384</v>
@@ -11515,16 +11515,16 @@
         <v>617</v>
       </c>
       <c r="AM33" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AN33" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="AO33">
-        <v>0.99386337452089002</v>
+        <v>0.99522505489766133</v>
       </c>
       <c r="AP33">
-        <v>112.50480045034956</v>
+        <v>87.54066020954204</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -11589,16 +11589,16 @@
         <v>433</v>
       </c>
       <c r="Y34" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="Z34" t="s">
         <v>540</v>
       </c>
       <c r="AA34">
-        <v>0.99804665079186261</v>
+        <v>0.96681320638730428</v>
       </c>
       <c r="AB34">
-        <v>35.811402149186421</v>
+        <v>608.42454956608799</v>
       </c>
       <c r="AD34" t="s">
         <v>384</v>
@@ -11625,16 +11625,16 @@
         <v>619</v>
       </c>
       <c r="AM34" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="AN34" t="s">
-        <v>520</v>
+        <v>737</v>
       </c>
       <c r="AO34">
-        <v>0.968274309035423</v>
+        <v>0.99880608610203336</v>
       </c>
       <c r="AP34">
-        <v>581.63766768391201</v>
+        <v>21.888421462720675</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11699,16 +11699,16 @@
         <v>435</v>
       </c>
       <c r="Y35" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="Z35" t="s">
         <v>541</v>
       </c>
       <c r="AA35">
-        <v>0.97118475866494502</v>
+        <v>0.99003291540359517</v>
       </c>
       <c r="AB35">
-        <v>528.27942447600776</v>
+        <v>182.72988426742148</v>
       </c>
       <c r="AD35" t="s">
         <v>384</v>
@@ -11735,16 +11735,16 @@
         <v>621</v>
       </c>
       <c r="AM35" t="s">
+        <v>738</v>
+      </c>
+      <c r="AN35" t="s">
         <v>739</v>
       </c>
-      <c r="AN35" t="s">
-        <v>538</v>
-      </c>
       <c r="AO35">
-        <v>0.95295378578294154</v>
+        <v>0.98962776346505854</v>
       </c>
       <c r="AP35">
-        <v>862.51392731273927</v>
+        <v>190.15766980725988</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11809,16 +11809,16 @@
         <v>437</v>
       </c>
       <c r="Y36" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="Z36" t="s">
         <v>542</v>
       </c>
       <c r="AA36">
-        <v>0.98979380819350882</v>
+        <v>0.99451774199646181</v>
       </c>
       <c r="AB36">
-        <v>187.11351645233776</v>
+        <v>100.50806339819938</v>
       </c>
       <c r="AD36" t="s">
         <v>384</v>
@@ -11848,13 +11848,13 @@
         <v>740</v>
       </c>
       <c r="AN36" t="s">
-        <v>741</v>
+        <v>550</v>
       </c>
       <c r="AO36">
-        <v>0.96887169792625616</v>
+        <v>0.94978410374301969</v>
       </c>
       <c r="AP36">
-        <v>570.68553801863686</v>
+        <v>920.6247647113064</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11919,16 +11919,16 @@
         <v>439</v>
       </c>
       <c r="Y37" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="Z37" t="s">
         <v>543</v>
       </c>
       <c r="AA37">
-        <v>0.9798698468265471</v>
+        <v>0.97030132885522102</v>
       </c>
       <c r="AB37">
-        <v>369.05280817996936</v>
+        <v>544.47563765428208</v>
       </c>
       <c r="AD37" t="s">
         <v>384</v>
@@ -11955,16 +11955,16 @@
         <v>625</v>
       </c>
       <c r="AM37" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AN37" t="s">
-        <v>743</v>
+        <v>550</v>
       </c>
       <c r="AO37">
-        <v>0.99522505489766133</v>
+        <v>0.96417711299224196</v>
       </c>
       <c r="AP37">
-        <v>87.54066020954204</v>
+        <v>656.75292847556489</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -12029,16 +12029,16 @@
         <v>441</v>
       </c>
       <c r="Y38" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="Z38" t="s">
         <v>544</v>
       </c>
       <c r="AA38">
-        <v>0.98772771860538078</v>
+        <v>0.99876642704737761</v>
       </c>
       <c r="AB38">
-        <v>224.99182556801827</v>
+        <v>22.615504131410646</v>
       </c>
       <c r="AD38" t="s">
         <v>384</v>
@@ -12065,16 +12065,16 @@
         <v>627</v>
       </c>
       <c r="AM38" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="AN38" t="s">
-        <v>745</v>
+        <v>520</v>
       </c>
       <c r="AO38">
-        <v>0.99880608610203336</v>
+        <v>0.94931253417293127</v>
       </c>
       <c r="AP38">
-        <v>21.888421462720675</v>
+        <v>929.27020682959278</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -12139,16 +12139,16 @@
         <v>443</v>
       </c>
       <c r="Y39" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="Z39" t="s">
         <v>545</v>
       </c>
       <c r="AA39">
-        <v>0.99440237434462508</v>
+        <v>0.99064855295491527</v>
       </c>
       <c r="AB39">
-        <v>102.62313701520689</v>
+        <v>171.44319582655291</v>
       </c>
       <c r="AD39" t="s">
         <v>384</v>
@@ -12175,16 +12175,16 @@
         <v>629</v>
       </c>
       <c r="AM39" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="AN39" t="s">
-        <v>747</v>
+        <v>565</v>
       </c>
       <c r="AO39">
-        <v>0.98962776346505854</v>
+        <v>0.97927855406064401</v>
       </c>
       <c r="AP39">
-        <v>190.15766980725988</v>
+        <v>379.89317555486042</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -12249,16 +12249,16 @@
         <v>445</v>
       </c>
       <c r="Y40" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="Z40" t="s">
         <v>546</v>
       </c>
       <c r="AA40">
-        <v>0.99854932678297781</v>
+        <v>0.99735162606593653</v>
       </c>
       <c r="AB40">
-        <v>26.595675645406835</v>
+        <v>48.553522124496595</v>
       </c>
       <c r="AD40" t="s">
         <v>384</v>
@@ -12285,16 +12285,16 @@
         <v>631</v>
       </c>
       <c r="AM40" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="AN40" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="AO40">
-        <v>0.94978410374301969</v>
+        <v>0.99261416554290038</v>
       </c>
       <c r="AP40">
-        <v>920.6247647113064</v>
+        <v>135.40696504682549</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -12359,16 +12359,16 @@
         <v>447</v>
       </c>
       <c r="Y41" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="Z41" t="s">
         <v>547</v>
       </c>
       <c r="AA41">
-        <v>0.99739948219126473</v>
+        <v>0.99752334755484584</v>
       </c>
       <c r="AB41">
-        <v>47.676159826814242</v>
+        <v>45.405294827827106</v>
       </c>
       <c r="AD41" t="s">
         <v>384</v>
@@ -12395,16 +12395,16 @@
         <v>633</v>
       </c>
       <c r="AM41" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="AN41" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AO41">
-        <v>0.96417711299224196</v>
+        <v>0.94939310241101427</v>
       </c>
       <c r="AP41">
-        <v>656.75292847556489</v>
+        <v>927.79312246473887</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -12469,16 +12469,16 @@
         <v>449</v>
       </c>
       <c r="Y42" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Z42" t="s">
         <v>548</v>
       </c>
       <c r="AA42">
-        <v>0.99087272805509874</v>
+        <v>0.99394570454136</v>
       </c>
       <c r="AB42">
-        <v>167.33331898985637</v>
+        <v>110.99541674173295</v>
       </c>
       <c r="AD42" t="s">
         <v>384</v>
@@ -12505,16 +12505,16 @@
         <v>635</v>
       </c>
       <c r="AM42" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="AN42" t="s">
-        <v>543</v>
+        <v>747</v>
       </c>
       <c r="AO42">
-        <v>0.94931253417293127</v>
+        <v>0.99702300519026088</v>
       </c>
       <c r="AP42">
-        <v>929.27020682959278</v>
+        <v>54.578238178550102</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -12579,16 +12579,16 @@
         <v>451</v>
       </c>
       <c r="Y43" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="Z43" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="AA43">
-        <v>0.9646219268942855</v>
+        <v>0.98255746585766901</v>
       </c>
       <c r="AB43">
-        <v>648.59800693809962</v>
+        <v>319.77979260940054</v>
       </c>
       <c r="AD43" t="s">
         <v>384</v>
@@ -12615,16 +12615,16 @@
         <v>637</v>
       </c>
       <c r="AM43" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AN43" t="s">
-        <v>535</v>
+        <v>749</v>
       </c>
       <c r="AO43">
-        <v>0.98179238163829652</v>
+        <v>0.99858163704266301</v>
       </c>
       <c r="AP43">
-        <v>333.80633663123064</v>
+        <v>26.003320884511144</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12689,16 +12689,16 @@
         <v>453</v>
       </c>
       <c r="Y44" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="Z44" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA44">
-        <v>0.99735162606593653</v>
+        <v>0.97767806396937151</v>
       </c>
       <c r="AB44">
-        <v>48.553522124496595</v>
+        <v>409.23549389485521</v>
       </c>
       <c r="AD44" t="s">
         <v>384</v>
@@ -12725,16 +12725,16 @@
         <v>639</v>
       </c>
       <c r="AM44" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="AN44" t="s">
-        <v>530</v>
+        <v>751</v>
       </c>
       <c r="AO44">
-        <v>0.97994970755923727</v>
+        <v>0.9947854490299548</v>
       </c>
       <c r="AP44">
-        <v>367.58869474731648</v>
+        <v>95.600101117495868</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12799,16 +12799,16 @@
         <v>455</v>
       </c>
       <c r="Y45" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="Z45" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AA45">
-        <v>0.99752334755484584</v>
+        <v>0.99672701953917697</v>
       </c>
       <c r="AB45">
-        <v>45.405294827827106</v>
+        <v>60.004641781756348</v>
       </c>
       <c r="AD45" t="s">
         <v>384</v>
@@ -12835,16 +12835,16 @@
         <v>641</v>
       </c>
       <c r="AM45" t="s">
+        <v>752</v>
+      </c>
+      <c r="AN45" t="s">
         <v>753</v>
       </c>
-      <c r="AN45" t="s">
-        <v>543</v>
-      </c>
       <c r="AO45">
-        <v>0.96599440792497671</v>
+        <v>0.99300875779692943</v>
       </c>
       <c r="AP45">
-        <v>623.43585470875962</v>
+        <v>128.17277372296059</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12909,16 +12909,16 @@
         <v>457</v>
       </c>
       <c r="Y46" t="s">
-        <v>369</v>
+        <v>332</v>
       </c>
       <c r="Z46" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AA46">
-        <v>0.99394570454136</v>
+        <v>0.9983826950953073</v>
       </c>
       <c r="AB46">
-        <v>110.99541674173295</v>
+        <v>29.650589919365284</v>
       </c>
       <c r="AD46" t="s">
         <v>384</v>
@@ -12951,10 +12951,10 @@
         <v>755</v>
       </c>
       <c r="AO46">
-        <v>0.99478509214205779</v>
+        <v>0.99484872380281231</v>
       </c>
       <c r="AP46">
-        <v>95.606644062274157</v>
+        <v>94.440063615107306</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -13019,16 +13019,16 @@
         <v>459</v>
       </c>
       <c r="Y47" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="Z47" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA47">
-        <v>0.99038856814984766</v>
+        <v>0.9989617523467913</v>
       </c>
       <c r="AB47">
-        <v>176.20958391945942</v>
+        <v>19.034540308826394</v>
       </c>
       <c r="AD47" t="s">
         <v>384</v>
@@ -13058,13 +13058,13 @@
         <v>756</v>
       </c>
       <c r="AN47" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="AO47">
-        <v>0.98290798239987243</v>
+        <v>0.9562603934457885</v>
       </c>
       <c r="AP47">
-        <v>313.35365600233933</v>
+        <v>801.89278682721124</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -13129,16 +13129,16 @@
         <v>461</v>
       </c>
       <c r="Y48" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="Z48" t="s">
         <v>520</v>
       </c>
       <c r="AA48">
-        <v>0.96778401809933534</v>
+        <v>0.95385659112728594</v>
       </c>
       <c r="AB48">
-        <v>590.62633484551873</v>
+        <v>845.96249599975874</v>
       </c>
       <c r="AD48" t="s">
         <v>384</v>
@@ -13171,10 +13171,10 @@
         <v>758</v>
       </c>
       <c r="AO48">
-        <v>0.9982900002192614</v>
+        <v>0.99478509214205779</v>
       </c>
       <c r="AP48">
-        <v>31.349995980207169</v>
+        <v>95.606644062274157</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13239,16 +13239,16 @@
         <v>463</v>
       </c>
       <c r="Y49" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="Z49" t="s">
-        <v>520</v>
+        <v>554</v>
       </c>
       <c r="AA49">
-        <v>0.98023840447090371</v>
+        <v>0.9951402828161694</v>
       </c>
       <c r="AB49">
-        <v>362.29591803343288</v>
+        <v>89.094815036894559</v>
       </c>
       <c r="AD49" t="s">
         <v>384</v>
@@ -13278,13 +13278,13 @@
         <v>759</v>
       </c>
       <c r="AN49" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="AO49">
-        <v>0.97712291195856049</v>
+        <v>0.98290798239987243</v>
       </c>
       <c r="AP49">
-        <v>419.41328075972342</v>
+        <v>313.35365600233933</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13349,16 +13349,16 @@
         <v>465</v>
       </c>
       <c r="Y50" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Z50" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AA50">
-        <v>0.96681320638730428</v>
+        <v>0.99140122988281854</v>
       </c>
       <c r="AB50">
-        <v>608.42454956608799</v>
+        <v>157.64411881499262</v>
       </c>
       <c r="AD50" t="s">
         <v>384</v>
@@ -13388,13 +13388,13 @@
         <v>760</v>
       </c>
       <c r="AN50" t="s">
-        <v>555</v>
+        <v>761</v>
       </c>
       <c r="AO50">
-        <v>0.95922852522417379</v>
+        <v>0.9982900002192614</v>
       </c>
       <c r="AP50">
-        <v>747.47703755681346</v>
+        <v>31.349995980207169</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13459,16 +13459,16 @@
         <v>467</v>
       </c>
       <c r="Y51" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="Z51" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="AA51">
-        <v>0.99003291540359517</v>
+        <v>0.95056191060937778</v>
       </c>
       <c r="AB51">
-        <v>182.72988426742148</v>
+        <v>906.36497216140765</v>
       </c>
       <c r="AD51" t="s">
         <v>384</v>
@@ -13495,16 +13495,16 @@
         <v>653</v>
       </c>
       <c r="AM51" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AN51" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="AO51">
-        <v>0.96810449790566344</v>
+        <v>0.97712291195856049</v>
       </c>
       <c r="AP51">
-        <v>584.75087172950259</v>
+        <v>419.41328075972342</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13569,16 +13569,16 @@
         <v>469</v>
       </c>
       <c r="Y52" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="Z52" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AA52">
-        <v>0.99451774199646181</v>
+        <v>0.99693870689560904</v>
       </c>
       <c r="AB52">
-        <v>100.50806339819938</v>
+        <v>56.123706913834091</v>
       </c>
       <c r="AD52" t="s">
         <v>384</v>
@@ -13605,16 +13605,16 @@
         <v>655</v>
       </c>
       <c r="AM52" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AN52" t="s">
-        <v>763</v>
+        <v>543</v>
       </c>
       <c r="AO52">
-        <v>0.99858163704266301</v>
+        <v>0.95922852522417379</v>
       </c>
       <c r="AP52">
-        <v>26.003320884511144</v>
+        <v>747.47703755681346</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13679,16 +13679,16 @@
         <v>471</v>
       </c>
       <c r="Y53" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="Z53" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AA53">
-        <v>0.97030132885522102</v>
+        <v>0.97773943430281773</v>
       </c>
       <c r="AB53">
-        <v>544.47563765428208</v>
+        <v>408.11037111500889</v>
       </c>
       <c r="AD53" t="s">
         <v>384</v>
@@ -13718,13 +13718,13 @@
         <v>764</v>
       </c>
       <c r="AN53" t="s">
-        <v>765</v>
+        <v>543</v>
       </c>
       <c r="AO53">
-        <v>0.9947854490299548</v>
+        <v>0.96810449790566344</v>
       </c>
       <c r="AP53">
-        <v>95.600101117495868</v>
+        <v>584.75087172950259</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13789,16 +13789,16 @@
         <v>473</v>
       </c>
       <c r="Y54" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="Z54" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AA54">
-        <v>0.99876642704737761</v>
+        <v>0.99711217881919312</v>
       </c>
       <c r="AB54">
-        <v>22.615504131410646</v>
+        <v>52.943388314793616</v>
       </c>
       <c r="AD54" t="s">
         <v>384</v>
@@ -13825,16 +13825,16 @@
         <v>659</v>
       </c>
       <c r="AM54" t="s">
+        <v>765</v>
+      </c>
+      <c r="AN54" t="s">
         <v>766</v>
       </c>
-      <c r="AN54" t="s">
-        <v>767</v>
-      </c>
       <c r="AO54">
-        <v>0.99300875779692943</v>
+        <v>0.99878024082202155</v>
       </c>
       <c r="AP54">
-        <v>128.17277372296059</v>
+        <v>22.362251596271118</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13899,16 +13899,16 @@
         <v>475</v>
       </c>
       <c r="Y55" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="Z55" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AA55">
-        <v>0.99064855295491527</v>
+        <v>0.99520306771735667</v>
       </c>
       <c r="AB55">
-        <v>171.44319582655291</v>
+        <v>87.943758515128479</v>
       </c>
       <c r="AD55" t="s">
         <v>384</v>
@@ -13935,16 +13935,16 @@
         <v>661</v>
       </c>
       <c r="AM55" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AN55" t="s">
-        <v>769</v>
+        <v>522</v>
       </c>
       <c r="AO55">
-        <v>0.99484872380281231</v>
+        <v>0.95826105465484257</v>
       </c>
       <c r="AP55">
-        <v>94.440063615107306</v>
+        <v>765.21399799455378</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14009,16 +14009,16 @@
         <v>477</v>
       </c>
       <c r="Y56" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="Z56" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="AA56">
-        <v>0.9951402828161694</v>
+        <v>0.95279789096470435</v>
       </c>
       <c r="AB56">
-        <v>89.094815036894559</v>
+        <v>865.37199898041979</v>
       </c>
       <c r="AD56" t="s">
         <v>384</v>
@@ -14045,16 +14045,16 @@
         <v>663</v>
       </c>
       <c r="AM56" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="AN56" t="s">
-        <v>535</v>
+        <v>769</v>
       </c>
       <c r="AO56">
-        <v>0.9562603934457885</v>
+        <v>0.99750387705430998</v>
       </c>
       <c r="AP56">
-        <v>801.89278682721124</v>
+        <v>45.762254004316212</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14119,16 +14119,16 @@
         <v>479</v>
       </c>
       <c r="Y57" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="Z57" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA57">
-        <v>0.96873365246705256</v>
+        <v>0.98772771860538078</v>
       </c>
       <c r="AB57">
-        <v>573.2163714373695</v>
+        <v>224.99182556801827</v>
       </c>
       <c r="AD57" t="s">
         <v>384</v>
@@ -14155,16 +14155,16 @@
         <v>665</v>
       </c>
       <c r="AM57" t="s">
+        <v>770</v>
+      </c>
+      <c r="AN57" t="s">
         <v>771</v>
       </c>
-      <c r="AN57" t="s">
-        <v>523</v>
-      </c>
       <c r="AO57">
-        <v>0.96193362161848472</v>
+        <v>0.99561014484129162</v>
       </c>
       <c r="AP57">
-        <v>697.88360366111351</v>
+        <v>80.480677909653664</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14229,16 +14229,16 @@
         <v>481</v>
       </c>
       <c r="Y58" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="Z58" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA58">
-        <v>0.99513490828923246</v>
+        <v>0.99440237434462508</v>
       </c>
       <c r="AB58">
-        <v>89.193348030739003</v>
+        <v>102.62313701520689</v>
       </c>
       <c r="AD58" t="s">
         <v>384</v>
@@ -14268,13 +14268,13 @@
         <v>772</v>
       </c>
       <c r="AN58" t="s">
-        <v>773</v>
+        <v>520</v>
       </c>
       <c r="AO58">
-        <v>0.98925468246747761</v>
+        <v>0.98080645969778191</v>
       </c>
       <c r="AP58">
-        <v>196.99748809624356</v>
+        <v>351.88157220733245</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14339,16 +14339,16 @@
         <v>483</v>
       </c>
       <c r="Y59" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="Z59" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA59">
-        <v>0.99859143525552441</v>
+        <v>0.99854932678297781</v>
       </c>
       <c r="AB59">
-        <v>25.823686982052106</v>
+        <v>26.595675645406835</v>
       </c>
       <c r="AD59" t="s">
         <v>384</v>
@@ -14375,16 +14375,16 @@
         <v>669</v>
       </c>
       <c r="AM59" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AN59" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="AO59">
-        <v>0.94921224886563393</v>
+        <v>0.98622313794978356</v>
       </c>
       <c r="AP59">
-        <v>931.10877079671207</v>
+        <v>252.57580425396782</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14449,16 +14449,16 @@
         <v>485</v>
       </c>
       <c r="Y60" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="Z60" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA60">
-        <v>0.99942899655278006</v>
+        <v>0.99739948219126473</v>
       </c>
       <c r="AB60">
-        <v>10.468396532365567</v>
+        <v>47.676159826814242</v>
       </c>
       <c r="AD60" t="s">
         <v>384</v>
@@ -14485,16 +14485,16 @@
         <v>671</v>
       </c>
       <c r="AM60" t="s">
+        <v>774</v>
+      </c>
+      <c r="AN60" t="s">
         <v>775</v>
       </c>
-      <c r="AN60" t="s">
-        <v>776</v>
-      </c>
       <c r="AO60">
-        <v>0.99916742781336532</v>
+        <v>0.99468247729100656</v>
       </c>
       <c r="AP60">
-        <v>15.263823421635696</v>
+        <v>97.487916331546771</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14559,16 +14559,16 @@
         <v>487</v>
       </c>
       <c r="Y61" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Z61" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="AA61">
-        <v>0.98255746585766901</v>
+        <v>0.97448562633554281</v>
       </c>
       <c r="AB61">
-        <v>319.77979260940054</v>
+        <v>467.76351718171588</v>
       </c>
       <c r="AD61" t="s">
         <v>384</v>
@@ -14595,16 +14595,16 @@
         <v>673</v>
       </c>
       <c r="AM61" t="s">
+        <v>776</v>
+      </c>
+      <c r="AN61" t="s">
         <v>777</v>
       </c>
-      <c r="AN61" t="s">
-        <v>530</v>
-      </c>
       <c r="AO61">
-        <v>0.97346893638374543</v>
+        <v>0.9861789081627198</v>
       </c>
       <c r="AP61">
-        <v>486.40283296466674</v>
+        <v>253.38668368347109</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14669,16 +14669,16 @@
         <v>489</v>
       </c>
       <c r="Y62" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="Z62" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AA62">
-        <v>0.97767806396937151</v>
+        <v>0.99499214029327188</v>
       </c>
       <c r="AB62">
-        <v>409.23549389485521</v>
+        <v>91.810761290016288</v>
       </c>
       <c r="AD62" t="s">
         <v>384</v>
@@ -14708,13 +14708,13 @@
         <v>778</v>
       </c>
       <c r="AN62" t="s">
-        <v>779</v>
+        <v>520</v>
       </c>
       <c r="AO62">
-        <v>0.95357273401837306</v>
+        <v>0.98988983533388286</v>
       </c>
       <c r="AP62">
-        <v>851.1665429964944</v>
+        <v>185.35301887881516</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14779,16 +14779,16 @@
         <v>491</v>
       </c>
       <c r="Y63" t="s">
-        <v>370</v>
+        <v>323</v>
       </c>
       <c r="Z63" t="s">
         <v>564</v>
       </c>
       <c r="AA63">
-        <v>0.99672701953917697</v>
+        <v>0.99931793846074402</v>
       </c>
       <c r="AB63">
-        <v>60.004641781756348</v>
+        <v>12.504461553027108</v>
       </c>
       <c r="AD63" t="s">
         <v>384</v>
@@ -14815,16 +14815,16 @@
         <v>677</v>
       </c>
       <c r="AM63" t="s">
+        <v>779</v>
+      </c>
+      <c r="AN63" t="s">
         <v>780</v>
       </c>
-      <c r="AN63" t="s">
-        <v>559</v>
-      </c>
       <c r="AO63">
-        <v>0.98030978036614613</v>
+        <v>0.96153074659796378</v>
       </c>
       <c r="AP63">
-        <v>360.98735995398783</v>
+        <v>705.26964570399718</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14889,16 +14889,16 @@
         <v>493</v>
       </c>
       <c r="Y64" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="Z64" t="s">
         <v>565</v>
       </c>
       <c r="AA64">
-        <v>0.9983826950953073</v>
+        <v>0.97472500521308103</v>
       </c>
       <c r="AB64">
-        <v>29.650589919365284</v>
+        <v>463.3749044268481</v>
       </c>
       <c r="AD64" t="s">
         <v>384</v>
@@ -14928,13 +14928,13 @@
         <v>781</v>
       </c>
       <c r="AN64" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="AO64">
-        <v>0.96113902088653813</v>
+        <v>0.97193777368455281</v>
       </c>
       <c r="AP64">
-        <v>712.45128374680007</v>
+        <v>514.47414911653129</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14999,16 +14999,16 @@
         <v>495</v>
       </c>
       <c r="Y65" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="Z65" t="s">
         <v>566</v>
       </c>
       <c r="AA65">
-        <v>0.9989617523467913</v>
+        <v>0.99590119173517544</v>
       </c>
       <c r="AB65">
-        <v>19.034540308826394</v>
+        <v>75.144818188450657</v>
       </c>
       <c r="AD65" t="s">
         <v>384</v>
@@ -15041,10 +15041,10 @@
         <v>783</v>
       </c>
       <c r="AO65">
-        <v>0.99849102734574458</v>
+        <v>0.99534050757450643</v>
       </c>
       <c r="AP65">
-        <v>27.664498661350322</v>
+        <v>85.424027800715081</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15109,16 +15109,16 @@
         <v>497</v>
       </c>
       <c r="Y66" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="Z66" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="AA66">
-        <v>0.95385659112728594</v>
+        <v>0.99110706411505001</v>
       </c>
       <c r="AB66">
-        <v>845.96249599975874</v>
+        <v>163.03715789074991</v>
       </c>
       <c r="AD66" t="s">
         <v>384</v>
@@ -15151,10 +15151,10 @@
         <v>785</v>
       </c>
       <c r="AO66">
-        <v>0.99893003381794343</v>
+        <v>0.99277178058643201</v>
       </c>
       <c r="AP66">
-        <v>19.616046671036653</v>
+        <v>132.51735591541228</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15219,16 +15219,16 @@
         <v>499</v>
       </c>
       <c r="Y67" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="Z67" t="s">
-        <v>539</v>
+        <v>568</v>
       </c>
       <c r="AA67">
-        <v>0.97448562633554281</v>
+        <v>0.99685014674837746</v>
       </c>
       <c r="AB67">
-        <v>467.76351718171588</v>
+        <v>57.74730961308002</v>
       </c>
       <c r="AD67" t="s">
         <v>384</v>
@@ -15258,13 +15258,13 @@
         <v>786</v>
       </c>
       <c r="AN67" t="s">
-        <v>555</v>
+        <v>522</v>
       </c>
       <c r="AO67">
-        <v>0.96939675941164705</v>
+        <v>0.99185568153246984</v>
       </c>
       <c r="AP67">
-        <v>561.05941078647095</v>
+        <v>149.31250523805363</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15329,16 +15329,16 @@
         <v>501</v>
       </c>
       <c r="Y68" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="Z68" t="s">
-        <v>523</v>
+        <v>569</v>
       </c>
       <c r="AA68">
-        <v>0.99499214029327188</v>
+        <v>0.98711864194461818</v>
       </c>
       <c r="AB68">
-        <v>91.810761290016288</v>
+        <v>236.15823101533312</v>
       </c>
       <c r="AD68" t="s">
         <v>384</v>
@@ -15368,13 +15368,13 @@
         <v>787</v>
       </c>
       <c r="AN68" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AO68">
-        <v>0.99774195493840256</v>
+        <v>0.96193362161848472</v>
       </c>
       <c r="AP68">
-        <v>41.397492795953291</v>
+        <v>697.88360366111351</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15439,16 +15439,16 @@
         <v>503</v>
       </c>
       <c r="Y69" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="Z69" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AA69">
-        <v>0.99931793846074402</v>
+        <v>0.99031833701436367</v>
       </c>
       <c r="AB69">
-        <v>12.504461553027108</v>
+        <v>177.49715473666521</v>
       </c>
       <c r="AD69" t="s">
         <v>384</v>
@@ -15481,10 +15481,10 @@
         <v>789</v>
       </c>
       <c r="AO69">
-        <v>0.96153074659796378</v>
+        <v>0.98925468246747761</v>
       </c>
       <c r="AP69">
-        <v>705.26964570399718</v>
+        <v>196.99748809624356</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15549,16 +15549,16 @@
         <v>505</v>
       </c>
       <c r="Y70" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="Z70" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AA70">
-        <v>0.97472500521308103</v>
+        <v>0.99087272805509874</v>
       </c>
       <c r="AB70">
-        <v>463.3749044268481</v>
+        <v>167.33331898985637</v>
       </c>
       <c r="AD70" t="s">
         <v>384</v>
@@ -15588,13 +15588,13 @@
         <v>790</v>
       </c>
       <c r="AN70" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="AO70">
-        <v>0.97193777368455281</v>
+        <v>0.94921224886563393</v>
       </c>
       <c r="AP70">
-        <v>514.47414911653129</v>
+        <v>931.10877079671207</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15659,16 +15659,16 @@
         <v>507</v>
       </c>
       <c r="Y71" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="Z71" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="AA71">
-        <v>0.99590119173517544</v>
+        <v>0.9646219268942855</v>
       </c>
       <c r="AB71">
-        <v>75.144818188450657</v>
+        <v>648.59800693809962</v>
       </c>
       <c r="AD71" t="s">
         <v>384</v>
@@ -15701,10 +15701,10 @@
         <v>792</v>
       </c>
       <c r="AO71">
-        <v>0.99534050757450643</v>
+        <v>0.99916742781336532</v>
       </c>
       <c r="AP71">
-        <v>85.424027800715081</v>
+        <v>15.263823421635696</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15769,16 +15769,16 @@
         <v>509</v>
       </c>
       <c r="Y72" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="Z72" t="s">
-        <v>570</v>
+        <v>541</v>
       </c>
       <c r="AA72">
-        <v>0.99110706411505001</v>
+        <v>0.96752396217182168</v>
       </c>
       <c r="AB72">
-        <v>163.03715789074991</v>
+        <v>595.39402684993593</v>
       </c>
       <c r="AD72" t="s">
         <v>384</v>
@@ -15808,13 +15808,13 @@
         <v>793</v>
       </c>
       <c r="AN72" t="s">
-        <v>794</v>
+        <v>531</v>
       </c>
       <c r="AO72">
-        <v>0.99277178058643201</v>
+        <v>0.97346893638374543</v>
       </c>
       <c r="AP72">
-        <v>132.51735591541228</v>
+        <v>486.40283296466674</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -15879,16 +15879,16 @@
         <v>511</v>
       </c>
       <c r="Y73" t="s">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="Z73" t="s">
-        <v>571</v>
+        <v>522</v>
       </c>
       <c r="AA73">
-        <v>0.99685014674837746</v>
+        <v>0.96000937928358443</v>
       </c>
       <c r="AB73">
-        <v>57.74730961308002</v>
+        <v>733.16137980095198</v>
       </c>
       <c r="AD73" t="s">
         <v>384</v>
@@ -15915,16 +15915,16 @@
         <v>697</v>
       </c>
       <c r="AM73" t="s">
+        <v>794</v>
+      </c>
+      <c r="AN73" t="s">
         <v>795</v>
       </c>
-      <c r="AN73" t="s">
-        <v>520</v>
-      </c>
       <c r="AO73">
-        <v>0.99185568153246984</v>
+        <v>0.99386337452089002</v>
       </c>
       <c r="AP73">
-        <v>149.31250523805363</v>
+        <v>112.50480045034956</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -15989,16 +15989,16 @@
         <v>513</v>
       </c>
       <c r="Y74" t="s">
-        <v>365</v>
+        <v>318</v>
       </c>
       <c r="Z74" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AA74">
-        <v>0.98711864194461818</v>
+        <v>0.99804665079186261</v>
       </c>
       <c r="AB74">
-        <v>236.15823101533312</v>
+        <v>35.811402149186421</v>
       </c>
       <c r="AD74" t="s">
         <v>384</v>
@@ -16028,13 +16028,13 @@
         <v>796</v>
       </c>
       <c r="AN74" t="s">
-        <v>568</v>
+        <v>522</v>
       </c>
       <c r="AO74">
-        <v>0.96976012134850453</v>
+        <v>0.968274309035423</v>
       </c>
       <c r="AP74">
-        <v>554.39777527741785</v>
+        <v>581.63766768391201</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16099,16 +16099,16 @@
         <v>515</v>
       </c>
       <c r="Y75" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="Z75" t="s">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="AA75">
-        <v>0.99031833701436367</v>
+        <v>0.97118475866494502</v>
       </c>
       <c r="AB75">
-        <v>177.49715473666521</v>
+        <v>528.27942447600776</v>
       </c>
       <c r="AD75" t="s">
         <v>384</v>
@@ -16138,13 +16138,13 @@
         <v>797</v>
       </c>
       <c r="AN75" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="AO75">
-        <v>0.99456229904023075</v>
+        <v>0.95295378578294154</v>
       </c>
       <c r="AP75">
-        <v>99.691184262436323</v>
+        <v>862.51392731273927</v>
       </c>
     </row>
   </sheetData>
@@ -16153,7 +16153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2974C58A-9293-4B1A-ADD3-C2F346A83BC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5B677E-E748-497D-84C9-57B45DA1F700}">
   <dimension ref="B9:Z75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16265,7 +16265,7 @@
         <v>838</v>
       </c>
       <c r="K11" t="s">
-        <v>784</v>
+        <v>728</v>
       </c>
       <c r="L11">
         <v>4.2668408855841076</v>
@@ -16298,7 +16298,7 @@
         <v>968</v>
       </c>
       <c r="X11" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="Y11">
         <v>11.795999999999999</v>
@@ -16333,7 +16333,7 @@
         <v>840</v>
       </c>
       <c r="K12" t="s">
-        <v>782</v>
+        <v>721</v>
       </c>
       <c r="L12">
         <v>1.8684162546234937</v>
@@ -16366,7 +16366,7 @@
         <v>970</v>
       </c>
       <c r="X12" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="Y12">
         <v>3.17625</v>
@@ -16401,7 +16401,7 @@
         <v>842</v>
       </c>
       <c r="K13" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="L13">
         <v>0.70776635133171628</v>
@@ -16434,7 +16434,7 @@
         <v>972</v>
       </c>
       <c r="X13" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="Y13">
         <v>0.83550000000000002</v>
@@ -16469,7 +16469,7 @@
         <v>844</v>
       </c>
       <c r="K14" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="L14">
         <v>38.566850937358645</v>
@@ -16502,7 +16502,7 @@
         <v>974</v>
       </c>
       <c r="X14" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="Y14">
         <v>2.22675</v>
@@ -16537,7 +16537,7 @@
         <v>846</v>
       </c>
       <c r="K15" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="L15">
         <v>2.0845713431158761</v>
@@ -16605,7 +16605,7 @@
         <v>848</v>
       </c>
       <c r="K16" t="s">
-        <v>729</v>
+        <v>765</v>
       </c>
       <c r="L16">
         <v>5.0973809601425186</v>
@@ -16638,7 +16638,7 @@
         <v>978</v>
       </c>
       <c r="X16" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="Y16">
         <v>11.138249999999999</v>
@@ -16673,7 +16673,7 @@
         <v>850</v>
       </c>
       <c r="K17" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="L17">
         <v>2.1877470691969978</v>
@@ -16706,7 +16706,7 @@
         <v>980</v>
       </c>
       <c r="X17" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="Y17">
         <v>4.9755000000000003</v>
@@ -16741,7 +16741,7 @@
         <v>852</v>
       </c>
       <c r="K18" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="L18">
         <v>5.5730316958223378</v>
@@ -16774,7 +16774,7 @@
         <v>982</v>
       </c>
       <c r="X18" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="Y18">
         <v>3.4162499999999998</v>
@@ -16809,7 +16809,7 @@
         <v>854</v>
       </c>
       <c r="K19" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="L19">
         <v>6.4986819696730596</v>
@@ -16842,7 +16842,7 @@
         <v>984</v>
       </c>
       <c r="X19" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="Y19">
         <v>2.8919999999999999</v>
@@ -16877,7 +16877,7 @@
         <v>856</v>
       </c>
       <c r="K20" t="s">
-        <v>728</v>
+        <v>778</v>
       </c>
       <c r="L20">
         <v>47.844720893056341</v>
@@ -16910,7 +16910,7 @@
         <v>986</v>
       </c>
       <c r="X20" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="Y20">
         <v>2.1</v>
@@ -16945,7 +16945,7 @@
         <v>858</v>
       </c>
       <c r="K21" t="s">
-        <v>722</v>
+        <v>772</v>
       </c>
       <c r="L21">
         <v>98.68994695303239</v>
@@ -16980,7 +16980,7 @@
         <v>860</v>
       </c>
       <c r="K22" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="L22">
         <v>96.181751330332375</v>
@@ -17015,7 +17015,7 @@
         <v>862</v>
       </c>
       <c r="K23" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="L23">
         <v>87.202849070038098</v>
@@ -17050,7 +17050,7 @@
         <v>864</v>
       </c>
       <c r="K24" t="s">
-        <v>726</v>
+        <v>776</v>
       </c>
       <c r="L24">
         <v>78.197884523894999</v>
@@ -17085,7 +17085,7 @@
         <v>866</v>
       </c>
       <c r="K25" t="s">
-        <v>753</v>
+        <v>726</v>
       </c>
       <c r="L25">
         <v>42.529732597711799</v>
@@ -17120,7 +17120,7 @@
         <v>868</v>
       </c>
       <c r="K26" t="s">
-        <v>739</v>
+        <v>797</v>
       </c>
       <c r="L26">
         <v>34.587215740299207</v>
@@ -17155,7 +17155,7 @@
         <v>870</v>
       </c>
       <c r="K27" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="L27">
         <v>42.25643238813123</v>
@@ -17190,7 +17190,7 @@
         <v>872</v>
       </c>
       <c r="K28" t="s">
-        <v>781</v>
+        <v>720</v>
       </c>
       <c r="L28">
         <v>19.303135607289168</v>
@@ -17225,7 +17225,7 @@
         <v>874</v>
       </c>
       <c r="K29" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="L29">
         <v>50.305360025131641</v>
@@ -17260,7 +17260,7 @@
         <v>876</v>
       </c>
       <c r="K30" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="L30">
         <v>25.462515402991507</v>
@@ -17295,7 +17295,7 @@
         <v>878</v>
       </c>
       <c r="K31" t="s">
-        <v>786</v>
+        <v>730</v>
       </c>
       <c r="L31">
         <v>27.658680455660367</v>
@@ -17330,7 +17330,7 @@
         <v>880</v>
       </c>
       <c r="K32" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="L32">
         <v>26.661225597421318</v>
@@ -17365,7 +17365,7 @@
         <v>882</v>
       </c>
       <c r="K33" t="s">
-        <v>751</v>
+        <v>724</v>
       </c>
       <c r="L33">
         <v>43.955323212040426</v>
@@ -17400,7 +17400,7 @@
         <v>884</v>
       </c>
       <c r="K34" t="s">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="L34">
         <v>16.489617433165694</v>
@@ -17435,7 +17435,7 @@
         <v>886</v>
       </c>
       <c r="K35" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="L35">
         <v>25.647547433244167</v>
@@ -17470,7 +17470,7 @@
         <v>888</v>
       </c>
       <c r="K36" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="L36">
         <v>52.43600239879752</v>
@@ -17505,7 +17505,7 @@
         <v>890</v>
       </c>
       <c r="K37" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="L37">
         <v>49.250791120392286</v>
@@ -17540,7 +17540,7 @@
         <v>892</v>
       </c>
       <c r="K38" t="s">
-        <v>705</v>
+        <v>745</v>
       </c>
       <c r="L38">
         <v>96.8691729106054</v>
@@ -17575,7 +17575,7 @@
         <v>894</v>
       </c>
       <c r="K39" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="L39">
         <v>39.121166186979593</v>
@@ -17610,7 +17610,7 @@
         <v>896</v>
       </c>
       <c r="K40" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="L40">
         <v>52.098216977205659</v>
@@ -17645,7 +17645,7 @@
         <v>898</v>
       </c>
       <c r="K41" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="L41">
         <v>71.143701624958894</v>
@@ -17680,7 +17680,7 @@
         <v>900</v>
       </c>
       <c r="K42" t="s">
-        <v>703</v>
+        <v>743</v>
       </c>
       <c r="L42">
         <v>123.17884915939072</v>
@@ -17715,7 +17715,7 @@
         <v>902</v>
       </c>
       <c r="K43" t="s">
-        <v>704</v>
+        <v>744</v>
       </c>
       <c r="L43">
         <v>91.323946420506616</v>
@@ -17750,7 +17750,7 @@
         <v>904</v>
       </c>
       <c r="K44" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="L44">
         <v>51.618040044402491</v>
@@ -17785,7 +17785,7 @@
         <v>906</v>
       </c>
       <c r="K45" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="L45">
         <v>99.011450390281297</v>
@@ -17820,7 +17820,7 @@
         <v>908</v>
       </c>
       <c r="K46" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="L46">
         <v>61.706057214399763</v>
@@ -17855,7 +17855,7 @@
         <v>910</v>
       </c>
       <c r="K47" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="L47">
         <v>49.137871464813081</v>
@@ -17890,7 +17890,7 @@
         <v>912</v>
       </c>
       <c r="K48" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="L48">
         <v>33.734564973116228</v>
@@ -17925,7 +17925,7 @@
         <v>914</v>
       </c>
       <c r="K49" t="s">
-        <v>731</v>
+        <v>767</v>
       </c>
       <c r="L49">
         <v>47.816600382052599</v>
@@ -17960,7 +17960,7 @@
         <v>916</v>
       </c>
       <c r="K50" t="s">
-        <v>796</v>
+        <v>727</v>
       </c>
       <c r="L50">
         <v>46.698997298088187</v>
@@ -17995,7 +17995,7 @@
         <v>918</v>
       </c>
       <c r="K51" t="s">
-        <v>738</v>
+        <v>796</v>
       </c>
       <c r="L51">
         <v>75.050246959082855</v>
@@ -18030,7 +18030,7 @@
         <v>920</v>
       </c>
       <c r="K52" t="s">
-        <v>780</v>
+        <v>719</v>
       </c>
       <c r="L52">
         <v>75.030891903133281</v>
@@ -18065,7 +18065,7 @@
         <v>922</v>
       </c>
       <c r="K53" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="L53">
         <v>78.488972319419887</v>
@@ -18100,7 +18100,7 @@
         <v>924</v>
       </c>
       <c r="K54" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="L54">
         <v>56.196726218849591</v>
@@ -18135,7 +18135,7 @@
         <v>926</v>
       </c>
       <c r="K55" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="L55">
         <v>79.392159968768212</v>
@@ -18170,7 +18170,7 @@
         <v>928</v>
       </c>
       <c r="K56" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="L56">
         <v>62.768179395836441</v>
@@ -18205,7 +18205,7 @@
         <v>930</v>
       </c>
       <c r="K57" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="L57">
         <v>38.863455871308048</v>
@@ -18240,7 +18240,7 @@
         <v>932</v>
       </c>
       <c r="K58" t="s">
-        <v>723</v>
+        <v>773</v>
       </c>
       <c r="L58">
         <v>49.332782197188976</v>
@@ -18275,7 +18275,7 @@
         <v>934</v>
       </c>
       <c r="K59" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="L59">
         <v>47.929375805367769</v>
@@ -18310,7 +18310,7 @@
         <v>936</v>
       </c>
       <c r="K60" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="L60">
         <v>77.393342850934502</v>
@@ -18345,7 +18345,7 @@
         <v>938</v>
       </c>
       <c r="K61" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="L61">
         <v>45.478139706797812</v>
@@ -18380,7 +18380,7 @@
         <v>940</v>
       </c>
       <c r="K62" t="s">
-        <v>778</v>
+        <v>717</v>
       </c>
       <c r="L62">
         <v>48.140294920365903</v>
@@ -18415,7 +18415,7 @@
         <v>942</v>
       </c>
       <c r="K63" t="s">
-        <v>736</v>
+        <v>794</v>
       </c>
       <c r="L63">
         <v>15.637923531445407</v>
@@ -18450,7 +18450,7 @@
         <v>944</v>
       </c>
       <c r="K64" t="s">
-        <v>797</v>
+        <v>723</v>
       </c>
       <c r="L64">
         <v>51.794566350258954</v>
@@ -18485,7 +18485,7 @@
         <v>946</v>
       </c>
       <c r="K65" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="L65">
         <v>78.70246336743719</v>
@@ -18520,7 +18520,7 @@
         <v>948</v>
       </c>
       <c r="K66" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="L66">
         <v>86.908524101933608</v>
@@ -18555,7 +18555,7 @@
         <v>950</v>
       </c>
       <c r="K67" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="L67">
         <v>54.455844858601104</v>
@@ -18590,7 +18590,7 @@
         <v>952</v>
       </c>
       <c r="K68" t="s">
-        <v>787</v>
+        <v>731</v>
       </c>
       <c r="L68">
         <v>1.0625916947319844</v>
@@ -18625,7 +18625,7 @@
         <v>954</v>
       </c>
       <c r="K69" t="s">
-        <v>732</v>
+        <v>768</v>
       </c>
       <c r="L69">
         <v>19.300562207456217</v>
@@ -18660,7 +18660,7 @@
         <v>956</v>
       </c>
       <c r="K70" t="s">
-        <v>706</v>
+        <v>746</v>
       </c>
       <c r="L70">
         <v>29.976025047721809</v>
@@ -18695,7 +18695,7 @@
         <v>958</v>
       </c>
       <c r="K71" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="L71">
         <v>55.882428131538255</v>
@@ -18730,7 +18730,7 @@
         <v>960</v>
       </c>
       <c r="K72" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="L72">
         <v>58.276159234953511</v>
@@ -18765,7 +18765,7 @@
         <v>962</v>
       </c>
       <c r="K73" t="s">
-        <v>734</v>
+        <v>770</v>
       </c>
       <c r="L73">
         <v>110.24417575298389</v>
@@ -18800,7 +18800,7 @@
         <v>964</v>
       </c>
       <c r="K74" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="L74">
         <v>56.928196652598764</v>
@@ -18835,7 +18835,7 @@
         <v>966</v>
       </c>
       <c r="K75" t="s">
-        <v>724</v>
+        <v>774</v>
       </c>
       <c r="L75">
         <v>57.985815283224305</v>
@@ -18850,7 +18850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511AEFAC-9B77-4E9C-BC87-DA8F88930A57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940D22E2-1155-44CB-BA44-4AFF83ABD79D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20667,7 +20667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE64950D-9A5C-48EB-ADFA-F726C8F6B3E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FE2CF6-D61B-42A2-9E59-C6E48F85B3A0}">
   <dimension ref="B2:M51"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DZA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6307C349-8B88-41D7-B4BC-9E09033B7D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21603BC2-8BF0-49E7-9BEF-1CBAFE8865CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1286,82 +1286,322 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_054</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 54</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_059</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 59</t>
   </si>
   <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
   </si>
   <si>
     <t>distr_solelc_spv_033</t>
@@ -1382,54 +1622,6 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_041</t>
   </si>
   <si>
@@ -1466,108 +1658,6 @@
     <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_032</t>
   </si>
   <si>
@@ -1592,133 +1682,136 @@
     <t>connecting solar to buses in cluster 46</t>
   </si>
   <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_DZ80-220,e_w294673631-220,e_DZ23-220,e_w226392269-400,e_DZ51-220,e_w385608518-220</t>
+  </si>
+  <si>
+    <t>e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
+  </si>
+  <si>
+    <t>e_w293224489-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_w569616494-220</t>
+  </si>
+  <si>
+    <t>e_w292110924-220,e_w226922540-220</t>
+  </si>
+  <si>
+    <t>e_w993660788-220,e_DZ150-220,e_w217933343-220,e_DZ149-220,e_DZ152-220,e_w217933346-220,e_DZ148-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_DZ160-220</t>
+  </si>
+  <si>
+    <t>e_w1031001205-220,e_DZ115-220,e_w226985195-220,e_DZ133-220,e_DZ125-220</t>
+  </si>
+  <si>
+    <t>e_w380271836-400,e_DZ133-220,e_DZ150-220,e_w1031851533-220</t>
+  </si>
+  <si>
+    <t>e_w226922540-220,e_w637266751-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w381517754-220</t>
+  </si>
+  <si>
+    <t>e_DZ65-400,e_DZ64-220,e_DZ60-220,e_w377716686-400,e_DZ91-220,e_DZ50-400,e_w371593266-220</t>
+  </si>
+  <si>
+    <t>e_DZ73-220,e_w107655510-220,e_w221085150-400,e_DZ10-220,e_DZ53-220,e_DZ8-220,e_DZ49-220,e_DZ37-220</t>
+  </si>
+  <si>
+    <t>e_w1056389360-220,e_w637266751-220,e_w217926708-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w226918874-220,e_w1167367928-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_DZ160-220,e_w227962923-220,e_w569616494-220</t>
+  </si>
+  <si>
+    <t>e_DZ130-220,e_w173805804-220,e_DZ126-220,e_DZ118-220</t>
+  </si>
+  <si>
+    <t>e_w174338940-220,e_w359380463-400,e_DZ118-220,e_w174347010-220,e_DZ103-220,e_DZ74-220</t>
+  </si>
+  <si>
+    <t>e_DZ87-400,e_w174171686-220,e_DZ85-220,e_w936350097-220,e_w340227647-220</t>
+  </si>
+  <si>
+    <t>e_w261824495-220,e_w1031001205-220</t>
+  </si>
+  <si>
+    <t>e_w637288557-220,e_w262778515-220,e_w262778513-220</t>
+  </si>
+  <si>
+    <t>e_w293467436-220,e_w261824495-220,e_w261824497-220,e_w380271836-220,e_DZ138-220</t>
+  </si>
+  <si>
     <t>e_w1056389360-220,e_w993660788-220,e_w217933343-220,e_w217926708-220,e_DZ152-220,e_w292487199-220</t>
   </si>
   <si>
     <t>e_w637266751-220,e_w293224489-220</t>
   </si>
   <si>
-    <t>e_w293467436-220,e_w261824495-220,e_w261824497-220,e_w380271836-220,e_DZ138-220</t>
-  </si>
-  <si>
-    <t>e_w292110924-220,e_w226922540-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w381517754-220</t>
-  </si>
-  <si>
-    <t>e_DZ65-400,e_DZ64-220,e_DZ60-220,e_w377716686-400,e_DZ91-220,e_DZ50-400,e_w371593266-220</t>
-  </si>
-  <si>
-    <t>e_DZ73-220,e_w107655510-220,e_w221085150-400,e_DZ10-220,e_DZ53-220,e_DZ8-220,e_DZ49-220,e_DZ37-220</t>
-  </si>
-  <si>
-    <t>e_DZ80-220,e_w294673631-220,e_DZ23-220,e_w226392269-400,e_DZ51-220,e_w385608518-220</t>
-  </si>
-  <si>
-    <t>e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
-  </si>
-  <si>
-    <t>e_w293224489-220</t>
+    <t>e_w1167367928-220</t>
+  </si>
+  <si>
+    <t>e_DZ114-220,e_DZ73-220,e_w221085150-220,e_DZ125-220,e_w226879630-220,e_w381355305-220</t>
+  </si>
+  <si>
+    <t>e_w226922540-220,e_w637266751-220,e_w293224489-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220,e_w310510674-220</t>
+  </si>
+  <si>
+    <t>e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_w217930454-220,e_w217933346-220,e_DZ156-220,e_DZ145-220,e_DZ159-220,e_w262778515-220</t>
+  </si>
+  <si>
+    <t>e_DZ75-220,e_w176684982-220,e_w175343993-220,e_w174512286-400,e_w694011253-400,e_w694000748-220,e_w175176155-220,e_w177011339-220</t>
+  </si>
+  <si>
+    <t>e_DZ40-220,e_DZ3-220,e_w379387167-220,e_w173534563-220,e_w177004931-220,e_DZ7-220,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>e_DZ118-220,e_w1031001205-220,e_DZ103-220,e_DZ115-220</t>
+  </si>
+  <si>
+    <t>e_w1031851533-220,e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220</t>
+  </si>
+  <si>
+    <t>e_DZ145-220,e_w317645796-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ129-220,e_DZ124-220,e_DZ113-400,e_w381266482-220,e_DZ102-220,e_w174342293-220,e_DZ88-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w292110924-220</t>
+  </si>
+  <si>
+    <t>e_DZ132-220,e_w173808767-220,e_w833562295-400,e_DZ131-220</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w292110924-220,e_w226922540-220,e_w1056389360-220</t>
+  </si>
+  <si>
+    <t>e_DZ137-220,e_w261824495-220,e_DZ138-220,e_w380271836-220,e_w43843800-220</t>
+  </si>
+  <si>
+    <t>e_w226922540-220,e_w1056389360-220,e_w637266751-220</t>
   </si>
   <si>
     <t>e_w1167367928-220,e_w226918874-220,e_w227962923-220,e_w292110924-220,e_w569616494-220,e_w1056389360-220</t>
@@ -1730,33 +1823,9 @@
     <t>e_w575738414-220,e_DZ128-400,e_w390634433-220</t>
   </si>
   <si>
-    <t>e_w310510674-220,e_w226918874-220,e_w1167367928-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_DZ160-220,e_w227962923-220,e_w569616494-220</t>
-  </si>
-  <si>
-    <t>e_DZ130-220,e_w173805804-220,e_DZ126-220,e_DZ118-220</t>
-  </si>
-  <si>
-    <t>e_w174338940-220,e_w359380463-400,e_DZ118-220,e_w174347010-220,e_DZ103-220,e_DZ74-220</t>
-  </si>
-  <si>
-    <t>e_DZ87-400,e_w174171686-220,e_DZ85-220,e_w936350097-220,e_w340227647-220</t>
-  </si>
-  <si>
-    <t>e_w261824495-220,e_w1031001205-220</t>
-  </si>
-  <si>
     <t>e_w310510674-220,e_w1167367928-220,e_w226918874-220</t>
   </si>
   <si>
-    <t>e_w1167367928-220</t>
-  </si>
-  <si>
     <t>e_w293467436-220,e_w381517754-220,e_DZ130-220,e_w261824495-220</t>
   </si>
   <si>
@@ -1769,48 +1838,6 @@
     <t>e_w637266751-220,e_w293224489-220,e_w262778514-220,e_w262778513-220</t>
   </si>
   <si>
-    <t>e_DZ118-220,e_w1031001205-220,e_DZ103-220,e_DZ115-220</t>
-  </si>
-  <si>
-    <t>e_w1031851533-220,e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220</t>
-  </si>
-  <si>
-    <t>e_DZ145-220,e_w317645796-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220,e_DZ160-220,e_w310510674-220</t>
-  </si>
-  <si>
-    <t>e_w226922540-220,e_w637266751-220</t>
-  </si>
-  <si>
-    <t>e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_w217930454-220,e_w217933346-220,e_DZ156-220,e_DZ145-220,e_DZ159-220,e_w262778515-220</t>
-  </si>
-  <si>
-    <t>e_DZ75-220,e_w176684982-220,e_w175343993-220,e_w174512286-400,e_w694011253-400,e_w694000748-220,e_w175176155-220,e_w177011339-220</t>
-  </si>
-  <si>
-    <t>e_DZ40-220,e_DZ3-220,e_w379387167-220,e_w173534563-220,e_w177004931-220,e_DZ7-220,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>e_w637288557-220,e_w262778515-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_w569616494-220</t>
-  </si>
-  <si>
-    <t>e_w993660788-220,e_DZ150-220,e_w217933343-220,e_DZ149-220,e_DZ152-220,e_w217933346-220,e_DZ148-220</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_DZ160-220</t>
-  </si>
-  <si>
-    <t>e_w1031001205-220,e_DZ115-220,e_w226985195-220,e_DZ133-220,e_DZ125-220</t>
-  </si>
-  <si>
-    <t>e_w380271836-400,e_DZ133-220,e_DZ150-220,e_w1031851533-220</t>
-  </si>
-  <si>
     <t>e_w569616494-220,e_w293467436-220,e_w261824497-220,e_w1056389360-220,e_w993660788-220</t>
   </si>
   <si>
@@ -1823,31 +1850,70 @@
     <t>e_w637266751-220,e_DZ159-220,e_w293224489-220,e_w476360977-220</t>
   </si>
   <si>
-    <t>e_DZ127-220,e_DZ129-220,e_DZ124-220,e_DZ113-400,e_w381266482-220,e_DZ102-220,e_w174342293-220,e_DZ88-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w292110924-220</t>
-  </si>
-  <si>
-    <t>e_DZ132-220,e_w173808767-220,e_w833562295-400,e_DZ131-220</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w292110924-220,e_w226922540-220,e_w1056389360-220</t>
-  </si>
-  <si>
-    <t>e_DZ137-220,e_w261824495-220,e_DZ138-220,e_w380271836-220,e_w43843800-220</t>
-  </si>
-  <si>
-    <t>e_w226922540-220,e_w1056389360-220,e_w637266751-220</t>
-  </si>
-  <si>
-    <t>e_w1056389360-220,e_w637266751-220,e_w217926708-220</t>
-  </si>
-  <si>
-    <t>e_DZ114-220,e_DZ73-220,e_w221085150-220,e_DZ125-220,e_w226879630-220,e_w381355305-220</t>
-  </si>
-  <si>
-    <t>e_w226922540-220,e_w637266751-220,e_w293224489-220</t>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wonelc_won_047</t>
@@ -1904,6 +1970,144 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_052</t>
   </si>
   <si>
@@ -1928,316 +2132,160 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_054</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 54</t>
   </si>
   <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>e_w293467436-220,e_w381517754-220,e_w261824495-220,e_DZ137-220,e_DZ138-220,e_w380271836-220,e_w43843800-220,e_w380271836-400,e_DZ133-220,e_DZ125-220</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_DZ74-220,e_DZ103-220,e_DZ64-220,e_DZ60-220,e_DZ115-220,e_DZ91-220,e_DZ50-400,e_DZ114-220,e_DZ73-220,e_w221085150-220,e_w221085150-400,e_w226879630-220,e_DZ53-220</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_w1167367928-220,e_w226918874-220</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>e_w226918874-220,e_DZ160-220,e_w1167367928-220,e_w227962923-220,e_w569616494-220</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_w227962923-220,e_w569616494-220,e_w1056389360-220</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
   </si>
   <si>
     <t>elc_won_047</t>
@@ -2282,6 +2330,102 @@
     <t>elc_won_020</t>
   </si>
   <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w226879630-220,e_DZ80-220,e_w294673631-220,e_w226392269-400,e_DZ51-220,e_w365883660-220,e_w385608518-220,e_DZ75-220,e_w694000747-400,e_w175343993-220,e_w174512286-400,e_w1377912118-400</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>e_w993660788-220,e_w261824497-220,e_w217933343-220,e_DZ152-220</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w1056389360-220,e_w226922540-220,e_w637266751-220</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220,e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w226918874-220,e_DZ160-220</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w173808767-220,e_w833562295-400,e_DZ131-220,e_w381517754-220,e_DZ130-220,e_DZ126-220,e_w261824495-220</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_DZ124-220,e_DZ113-400,e_DZ107-220,e_DZ102-220,e_DZ88-220,e_DZ87-400,e_w174171686-220,e_w936350097-220,e_w340227647-220,e_DZ65-400,e_w377716686-400,e_w371593266-220,e_w107655510-220,e_DZ10-220,e_DZ8-220,e_DZ37-220</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w293467436-220,e_w569616494-220,e_w261824497-220,e_w261824495-220,e_w380271836-220,e_DZ138-220</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
     <t>elc_won_052</t>
   </si>
   <si>
@@ -2300,229 +2444,91 @@
     <t>e_w694000748-220,e_w175176155-220,e_w387845900-220,e_w312609390-220,e_DZ40-220,e_w390634433-220,e_w380645355-220,e_w379387167-220,e_DZ86-225,e_w177004931-220</t>
   </si>
   <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>e_w310510674-220,e_w569616494-220,e_w261824497-220,e_w993660788-220</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_DZ23-220,e_DZ34-220,e_w176684982-220,e_w694011253-400,e_w177011339-220,e_DZ3-220,e_w173534563-220,e_DZ7-220,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ132-220,e_DZ129-220,e_w173808767-220,e_DZ131-220</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_w993660788-220,e_w217933343-220,e_DZ152-220,e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_DZ156-220,e_DZ159-220</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w637266751-220,e_w217926708-220,e_w293224489-220</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_w217933346-220,e_w217930454-220,e_w292487199-220,e_DZ145-220,e_w317645796-220,e_w262778515-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w381266482-220,e_w173805804-220,e_w174342293-220,e_DZ130-220,e_w174338940-220,e_DZ126-220,e_w359380463-400,e_DZ85-220,e_DZ118-220,e_w174347010-220,e_DZ103-220</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_DZ125-220,e_w1031851533-220,e_w381355305-220,e_DZ121-220,e_w226886714-220,e_w1033643187-220,e_w317645604-220,e_w694205382-220,e_w694205380-220</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w217926708-220,e_w637266751-220,e_DZ156-220,e_DZ159-220,e_w293224489-220,e_w476360977-220,e_w637288557-220,e_w262778515-220,e_w262778513-220,e_w262778514-220</t>
+  </si>
+  <si>
     <t>elc_won_054</t>
   </si>
   <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w226879630-220,e_DZ80-220,e_w294673631-220,e_w226392269-400,e_DZ51-220,e_w365883660-220,e_w385608518-220,e_DZ75-220,e_w694000747-400,e_w175343993-220,e_w174512286-400,e_w1377912118-400</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w226918874-220,e_DZ160-220</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_DZ132-220,e_w833562295-220,e_w173808767-220,e_w833562295-400,e_DZ131-220,e_w381517754-220,e_DZ130-220,e_DZ126-220,e_w261824495-220</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_DZ124-220,e_DZ113-400,e_DZ107-220,e_DZ102-220,e_DZ88-220,e_DZ87-400,e_w174171686-220,e_w936350097-220,e_w340227647-220,e_DZ65-400,e_w377716686-400,e_w371593266-220,e_w107655510-220,e_DZ10-220,e_DZ8-220,e_DZ37-220</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220,e_w569616494-220,e_w261824497-220,e_w261824495-220,e_w380271836-220,e_DZ138-220</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_w217941443-220,e_w1033643187-220,e_w569616485-400,e_DZ139-220,e_DZ139-400,e_w575738414-220,e_w217976993-220,e_w533163474-220,e_w218114438-220,e_DZ128-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_DZ127-220,e_DZ132-220,e_DZ129-220,e_w173808767-220,e_DZ131-220</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_w993660788-220,e_w217933343-220,e_DZ152-220,e_w217926708-220,e_w292487199-220,e_w217926711-220,e_w217926710-220,e_DZ156-220,e_DZ159-220</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w637266751-220,e_w217926708-220,e_w293224489-220</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_w217933346-220,e_w217930454-220,e_w292487199-220,e_DZ145-220,e_w317645796-220,e_w262778515-220,e_DZ141-220,e_w218114438-220,e_w262778513-220</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>e_w293467436-220,e_w381517754-220,e_w261824495-220,e_DZ137-220,e_DZ138-220,e_w380271836-220,e_w43843800-220,e_w380271836-400,e_DZ133-220,e_DZ125-220</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_DZ74-220,e_DZ103-220,e_DZ64-220,e_DZ60-220,e_DZ115-220,e_DZ91-220,e_DZ50-400,e_DZ114-220,e_DZ73-220,e_w221085150-220,e_w221085150-400,e_w226879630-220,e_DZ53-220</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w381266482-220,e_w173805804-220,e_w174342293-220,e_DZ130-220,e_w174338940-220,e_DZ126-220,e_w359380463-400,e_DZ85-220,e_DZ118-220,e_w174347010-220,e_DZ103-220</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_DZ125-220,e_w1031851533-220,e_w381355305-220,e_DZ121-220,e_w226886714-220,e_w1033643187-220,e_w317645604-220,e_w694205382-220,e_w694205380-220</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w217926708-220,e_w637266751-220,e_DZ156-220,e_DZ159-220,e_w293224489-220,e_w476360977-220,e_w637288557-220,e_w262778515-220,e_w262778513-220,e_w262778514-220</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_065</t>
-  </si>
-  <si>
-    <t>e_w993660788-220,e_w261824497-220,e_w217933343-220,e_DZ152-220</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w1056389360-220,e_w226922540-220,e_w637266751-220</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_w1167367928-220,e_w226918874-220</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>elc_won_045</t>
-  </si>
-  <si>
-    <t>e_w226918874-220,e_DZ160-220,e_w1167367928-220,e_w227962923-220,e_w569616494-220</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_w227962923-220,e_w569616494-220,e_w1056389360-220</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w569616494-220,e_w261824497-220,e_w993660788-220</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_DZ23-220,e_DZ34-220,e_w176684982-220,e_w694011253-400,e_w177011339-220,e_DZ3-220,e_w173534563-220,e_DZ7-220,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_w310510674-220,e_w293467436-220</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -2531,6 +2537,36 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_007</t>
   </si>
   <si>
@@ -2543,46 +2579,16 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_005</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_DZ107-220,e_DZ102-220</t>
   </si>
   <si>
     <t>elc_wof_001</t>
@@ -2591,6 +2597,36 @@
     <t>e_DZ1-400,e_DZ7-220</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_DZ5-220,e_w694011253-400</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_DZ88-220</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w174171686-220,e_w936350097-220</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w176932220-400,e_DZ3-220</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_DZ127-220,e_DZ124-220</t>
+  </si>
+  <si>
     <t>elc_wof_007</t>
   </si>
   <si>
@@ -2603,46 +2639,10 @@
     <t>e_DZ42-220,e_w377716686-400</t>
   </si>
   <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_DZ127-220,e_DZ124-220</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_DZ5-220,e_w694011253-400</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_DZ88-220</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_DZ107-220,e_DZ102-220</t>
-  </si>
-  <si>
     <t>elc_wof_005</t>
   </si>
   <si>
     <t>e_w172698243-220,e_w107655510-220,e_DZ10-220</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w174171686-220,e_w936350097-220</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w176932220-400,e_DZ3-220</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -8461,7 +8461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0999DBAF-E388-4EE4-B97C-500ACA1273FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C812C6B2-6434-468C-9859-42FA46758BCD}">
   <dimension ref="B9:BD75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8699,16 +8699,16 @@
         <v>385</v>
       </c>
       <c r="Y11" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="Z11" t="s">
         <v>519</v>
       </c>
       <c r="AA11">
-        <v>0.98979380819350882</v>
+        <v>0.99883776385939382</v>
       </c>
       <c r="AB11">
-        <v>187.11351645233776</v>
+        <v>21.30766257777988</v>
       </c>
       <c r="AD11" t="s">
         <v>384</v>
@@ -8738,13 +8738,13 @@
         <v>703</v>
       </c>
       <c r="AN11" t="s">
-        <v>534</v>
+        <v>704</v>
       </c>
       <c r="AO11">
-        <v>0.97500946832970314</v>
+        <v>0.99478509214205779</v>
       </c>
       <c r="AP11">
-        <v>458.15974728877472</v>
+        <v>95.606644062274157</v>
       </c>
       <c r="AR11" t="s">
         <v>384</v>
@@ -8777,10 +8777,10 @@
         <v>819</v>
       </c>
       <c r="BC11">
-        <v>0.9965021251763384</v>
+        <v>0.99790771621959851</v>
       </c>
       <c r="BD11">
-        <v>64.127705100462705</v>
+        <v>38.358535974026807</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8845,16 +8845,16 @@
         <v>389</v>
       </c>
       <c r="Y12" t="s">
-        <v>376</v>
+        <v>337</v>
       </c>
       <c r="Z12" t="s">
         <v>520</v>
       </c>
       <c r="AA12">
-        <v>0.9798698468265471</v>
+        <v>0.99648965438197512</v>
       </c>
       <c r="AB12">
-        <v>369.05280817996936</v>
+        <v>64.356336330456202</v>
       </c>
       <c r="AD12" t="s">
         <v>384</v>
@@ -8881,16 +8881,16 @@
         <v>575</v>
       </c>
       <c r="AM12" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AN12" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="AO12">
-        <v>0.97657215376744144</v>
+        <v>0.98290798239987243</v>
       </c>
       <c r="AP12">
-        <v>429.51051426357446</v>
+        <v>313.35365600233933</v>
       </c>
       <c r="AR12" t="s">
         <v>384</v>
@@ -8923,10 +8923,10 @@
         <v>821</v>
       </c>
       <c r="BC12">
-        <v>0.99529500707002927</v>
+        <v>0.9965021251763384</v>
       </c>
       <c r="BD12">
-        <v>86.258203716130154</v>
+        <v>64.127705100462705</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8991,16 +8991,16 @@
         <v>391</v>
       </c>
       <c r="Y13" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="Z13" t="s">
         <v>521</v>
       </c>
       <c r="AA13">
-        <v>0.99038856814984766</v>
+        <v>0.95021137372232145</v>
       </c>
       <c r="AB13">
-        <v>176.20958391945942</v>
+        <v>912.79148175744024</v>
       </c>
       <c r="AD13" t="s">
         <v>384</v>
@@ -9027,16 +9027,16 @@
         <v>577</v>
       </c>
       <c r="AM13" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AN13" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AO13">
-        <v>0.98402112024048205</v>
+        <v>0.9982900002192614</v>
       </c>
       <c r="AP13">
-        <v>292.94612892449663</v>
+        <v>31.349995980207169</v>
       </c>
       <c r="AR13" t="s">
         <v>384</v>
@@ -9069,10 +9069,10 @@
         <v>823</v>
       </c>
       <c r="BC13">
-        <v>0.99819616407025835</v>
+        <v>0.99690129108492354</v>
       </c>
       <c r="BD13">
-        <v>33.070325378597239</v>
+        <v>56.809663443069056</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -9137,16 +9137,16 @@
         <v>393</v>
       </c>
       <c r="Y14" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="Z14" t="s">
         <v>522</v>
       </c>
       <c r="AA14">
-        <v>0.96778401809933534</v>
+        <v>0.99140122988281854</v>
       </c>
       <c r="AB14">
-        <v>590.62633484551873</v>
+        <v>157.64411881499262</v>
       </c>
       <c r="AD14" t="s">
         <v>384</v>
@@ -9173,16 +9173,16 @@
         <v>579</v>
       </c>
       <c r="AM14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AN14" t="s">
-        <v>708</v>
+        <v>566</v>
       </c>
       <c r="AO14">
-        <v>0.99471898599413955</v>
+        <v>0.97712291195856049</v>
       </c>
       <c r="AP14">
-        <v>96.818590107441551</v>
+        <v>419.41328075972342</v>
       </c>
       <c r="AR14" t="s">
         <v>384</v>
@@ -9215,10 +9215,10 @@
         <v>825</v>
       </c>
       <c r="BC14">
-        <v>0.99801675448684013</v>
+        <v>0.99970264496455319</v>
       </c>
       <c r="BD14">
-        <v>36.359501074597006</v>
+        <v>5.4515089831922632</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -9283,16 +9283,16 @@
         <v>395</v>
       </c>
       <c r="Y15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="Z15" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AA15">
-        <v>0.98023840447090371</v>
+        <v>0.95056191060937778</v>
       </c>
       <c r="AB15">
-        <v>362.29591803343288</v>
+        <v>906.36497216140765</v>
       </c>
       <c r="AD15" t="s">
         <v>384</v>
@@ -9322,13 +9322,13 @@
         <v>709</v>
       </c>
       <c r="AN15" t="s">
-        <v>710</v>
+        <v>566</v>
       </c>
       <c r="AO15">
-        <v>0.98741925140550357</v>
+        <v>0.95922852522417379</v>
       </c>
       <c r="AP15">
-        <v>230.64705756576762</v>
+        <v>747.47703755681346</v>
       </c>
       <c r="AR15" t="s">
         <v>384</v>
@@ -9361,10 +9361,10 @@
         <v>827</v>
       </c>
       <c r="BC15">
-        <v>0.99690129108492354</v>
+        <v>0.99767880649372143</v>
       </c>
       <c r="BD15">
-        <v>56.809663443069056</v>
+        <v>42.555214281773615</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -9429,16 +9429,16 @@
         <v>397</v>
       </c>
       <c r="Y16" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="Z16" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AA16">
-        <v>0.96873365246705256</v>
+        <v>0.99693870689560904</v>
       </c>
       <c r="AB16">
-        <v>573.2163714373695</v>
+        <v>56.123706913834091</v>
       </c>
       <c r="AD16" t="s">
         <v>384</v>
@@ -9465,16 +9465,16 @@
         <v>583</v>
       </c>
       <c r="AM16" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AN16" t="s">
-        <v>712</v>
+        <v>566</v>
       </c>
       <c r="AO16">
-        <v>0.99775066197427953</v>
+        <v>0.96810449790566344</v>
       </c>
       <c r="AP16">
-        <v>41.237863804874586</v>
+        <v>584.75087172950259</v>
       </c>
       <c r="AR16" t="s">
         <v>384</v>
@@ -9507,10 +9507,10 @@
         <v>829</v>
       </c>
       <c r="BC16">
-        <v>0.99970264496455319</v>
+        <v>0.99766851268386103</v>
       </c>
       <c r="BD16">
-        <v>5.4515089831922632</v>
+        <v>42.743934129214161</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9575,16 +9575,16 @@
         <v>399</v>
       </c>
       <c r="Y17" t="s">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="Z17" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA17">
-        <v>0.99513490828923246</v>
+        <v>0.97773943430281773</v>
       </c>
       <c r="AB17">
-        <v>89.193348030739003</v>
+        <v>408.11037111500889</v>
       </c>
       <c r="AD17" t="s">
         <v>384</v>
@@ -9611,16 +9611,16 @@
         <v>585</v>
       </c>
       <c r="AM17" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="AN17" t="s">
-        <v>543</v>
+        <v>712</v>
       </c>
       <c r="AO17">
-        <v>0.96555290739289967</v>
+        <v>0.96153074659796378</v>
       </c>
       <c r="AP17">
-        <v>631.53003113017269</v>
+        <v>705.26964570399718</v>
       </c>
       <c r="AR17" t="s">
         <v>384</v>
@@ -9653,10 +9653,10 @@
         <v>831</v>
       </c>
       <c r="BC17">
-        <v>0.99790771621959851</v>
+        <v>0.99801675448684013</v>
       </c>
       <c r="BD17">
-        <v>38.358535974026807</v>
+        <v>36.359501074597006</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9721,16 +9721,16 @@
         <v>401</v>
       </c>
       <c r="Y18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Z18" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AA18">
-        <v>0.99859143525552441</v>
+        <v>0.99711217881919312</v>
       </c>
       <c r="AB18">
-        <v>25.823686982052106</v>
+        <v>52.943388314793616</v>
       </c>
       <c r="AD18" t="s">
         <v>384</v>
@@ -9757,16 +9757,16 @@
         <v>587</v>
       </c>
       <c r="AM18" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AN18" t="s">
-        <v>715</v>
+        <v>545</v>
       </c>
       <c r="AO18">
-        <v>0.99626371781833423</v>
+        <v>0.97193777368455281</v>
       </c>
       <c r="AP18">
-        <v>68.49850666387222</v>
+        <v>514.47414911653129</v>
       </c>
       <c r="AR18" t="s">
         <v>384</v>
@@ -9799,10 +9799,10 @@
         <v>833</v>
       </c>
       <c r="BC18">
-        <v>0.99893527403150917</v>
+        <v>0.99529500707002927</v>
       </c>
       <c r="BD18">
-        <v>19.519976088998508</v>
+        <v>86.258203716130154</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9867,16 +9867,16 @@
         <v>403</v>
       </c>
       <c r="Y19" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="Z19" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA19">
-        <v>0.99942899655278006</v>
+        <v>0.99520306771735667</v>
       </c>
       <c r="AB19">
-        <v>10.468396532365567</v>
+        <v>87.943758515128479</v>
       </c>
       <c r="AD19" t="s">
         <v>384</v>
@@ -9903,16 +9903,16 @@
         <v>589</v>
       </c>
       <c r="AM19" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AN19" t="s">
-        <v>550</v>
+        <v>715</v>
       </c>
       <c r="AO19">
-        <v>0.97107796146874092</v>
+        <v>0.99534050757450643</v>
       </c>
       <c r="AP19">
-        <v>530.23737307308215</v>
+        <v>85.424027800715081</v>
       </c>
       <c r="AR19" t="s">
         <v>384</v>
@@ -9945,10 +9945,10 @@
         <v>835</v>
       </c>
       <c r="BC19">
-        <v>0.99767880649372143</v>
+        <v>0.99819616407025835</v>
       </c>
       <c r="BD19">
-        <v>42.555214281773615</v>
+        <v>33.070325378597239</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -10013,16 +10013,16 @@
         <v>405</v>
       </c>
       <c r="Y20" t="s">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="Z20" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA20">
-        <v>0.99883776385939382</v>
+        <v>0.95279789096470435</v>
       </c>
       <c r="AB20">
-        <v>21.30766257777988</v>
+        <v>865.37199898041979</v>
       </c>
       <c r="AD20" t="s">
         <v>384</v>
@@ -10049,16 +10049,16 @@
         <v>591</v>
       </c>
       <c r="AM20" t="s">
+        <v>716</v>
+      </c>
+      <c r="AN20" t="s">
         <v>717</v>
       </c>
-      <c r="AN20" t="s">
-        <v>718</v>
-      </c>
       <c r="AO20">
-        <v>0.95357273401837306</v>
+        <v>0.99277178058643201</v>
       </c>
       <c r="AP20">
-        <v>851.1665429964944</v>
+        <v>132.51735591541228</v>
       </c>
       <c r="AR20" t="s">
         <v>384</v>
@@ -10091,10 +10091,10 @@
         <v>837</v>
       </c>
       <c r="BC20">
-        <v>0.99766851268386103</v>
+        <v>0.99893527403150917</v>
       </c>
       <c r="BD20">
-        <v>42.743934129214161</v>
+        <v>19.519976088998508</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -10159,16 +10159,16 @@
         <v>407</v>
       </c>
       <c r="Y21" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="Z21" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA21">
-        <v>0.99648965438197512</v>
+        <v>0.96873365246705256</v>
       </c>
       <c r="AB21">
-        <v>64.356336330456202</v>
+        <v>573.2163714373695</v>
       </c>
       <c r="AD21" t="s">
         <v>384</v>
@@ -10195,16 +10195,16 @@
         <v>593</v>
       </c>
       <c r="AM21" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AN21" t="s">
         <v>523</v>
       </c>
       <c r="AO21">
-        <v>0.98030978036614613</v>
+        <v>0.99185568153246984</v>
       </c>
       <c r="AP21">
-        <v>360.98735995398783</v>
+        <v>149.31250523805363</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -10269,16 +10269,16 @@
         <v>409</v>
       </c>
       <c r="Y22" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="Z22" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA22">
-        <v>0.95021137372232145</v>
+        <v>0.99513490828923246</v>
       </c>
       <c r="AB22">
-        <v>912.79148175744024</v>
+        <v>89.193348030739003</v>
       </c>
       <c r="AD22" t="s">
         <v>384</v>
@@ -10305,16 +10305,16 @@
         <v>595</v>
       </c>
       <c r="AM22" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AN22" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="AO22">
-        <v>0.96113902088653813</v>
+        <v>0.97500946832970314</v>
       </c>
       <c r="AP22">
-        <v>712.45128374680007</v>
+        <v>458.15974728877472</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -10379,16 +10379,16 @@
         <v>411</v>
       </c>
       <c r="Y23" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="Z23" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA23">
-        <v>0.99538973816509291</v>
+        <v>0.99859143525552441</v>
       </c>
       <c r="AB23">
-        <v>84.521466973297393</v>
+        <v>25.823686982052106</v>
       </c>
       <c r="AD23" t="s">
         <v>384</v>
@@ -10415,16 +10415,16 @@
         <v>597</v>
       </c>
       <c r="AM23" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AN23" t="s">
-        <v>722</v>
+        <v>545</v>
       </c>
       <c r="AO23">
-        <v>0.99849102734574458</v>
+        <v>0.97657215376744144</v>
       </c>
       <c r="AP23">
-        <v>27.664498661350322</v>
+        <v>429.51051426357446</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -10489,16 +10489,16 @@
         <v>413</v>
       </c>
       <c r="Y24" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="Z24" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA24">
-        <v>0.98685658514563523</v>
+        <v>0.99942899655278006</v>
       </c>
       <c r="AB24">
-        <v>240.96260566335508</v>
+        <v>10.468396532365567</v>
       </c>
       <c r="AD24" t="s">
         <v>384</v>
@@ -10525,16 +10525,16 @@
         <v>599</v>
       </c>
       <c r="AM24" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="AN24" t="s">
-        <v>534</v>
+        <v>722</v>
       </c>
       <c r="AO24">
-        <v>0.99456229904023075</v>
+        <v>0.98402112024048205</v>
       </c>
       <c r="AP24">
-        <v>99.691184262436323</v>
+        <v>292.94612892449663</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10599,16 +10599,16 @@
         <v>415</v>
       </c>
       <c r="Y25" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="Z25" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA25">
-        <v>0.99775167610563054</v>
+        <v>0.99087272805509874</v>
       </c>
       <c r="AB25">
-        <v>41.219271396774424</v>
+        <v>167.33331898985637</v>
       </c>
       <c r="AD25" t="s">
         <v>384</v>
@@ -10635,16 +10635,16 @@
         <v>601</v>
       </c>
       <c r="AM25" t="s">
+        <v>723</v>
+      </c>
+      <c r="AN25" t="s">
         <v>724</v>
       </c>
-      <c r="AN25" t="s">
-        <v>550</v>
-      </c>
       <c r="AO25">
-        <v>0.98179238163829652</v>
+        <v>0.99471898599413955</v>
       </c>
       <c r="AP25">
-        <v>333.80633663123064</v>
+        <v>96.818590107441551</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10709,16 +10709,16 @@
         <v>417</v>
       </c>
       <c r="Y26" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="Z26" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AA26">
-        <v>0.95575770595896115</v>
+        <v>0.9646219268942855</v>
       </c>
       <c r="AB26">
-        <v>811.10872408571242</v>
+        <v>648.59800693809962</v>
       </c>
       <c r="AD26" t="s">
         <v>384</v>
@@ -10748,13 +10748,13 @@
         <v>725</v>
       </c>
       <c r="AN26" t="s">
-        <v>531</v>
+        <v>726</v>
       </c>
       <c r="AO26">
-        <v>0.97994970755923727</v>
+        <v>0.98741925140550357</v>
       </c>
       <c r="AP26">
-        <v>367.58869474731648</v>
+        <v>230.64705756576762</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10819,16 +10819,16 @@
         <v>419</v>
       </c>
       <c r="Y27" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z27" t="s">
         <v>534</v>
       </c>
       <c r="AA27">
-        <v>0.95951701524155131</v>
+        <v>0.95575770595896115</v>
       </c>
       <c r="AB27">
-        <v>742.18805390489183</v>
+        <v>811.10872408571242</v>
       </c>
       <c r="AD27" t="s">
         <v>384</v>
@@ -10855,16 +10855,16 @@
         <v>605</v>
       </c>
       <c r="AM27" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AN27" t="s">
-        <v>520</v>
+        <v>728</v>
       </c>
       <c r="AO27">
-        <v>0.96599440792497671</v>
+        <v>0.99775066197427953</v>
       </c>
       <c r="AP27">
-        <v>623.43585470875962</v>
+        <v>41.237863804874586</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10929,16 +10929,16 @@
         <v>421</v>
       </c>
       <c r="Y28" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z28" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA28">
-        <v>0.98916491572478116</v>
+        <v>0.95951701524155131</v>
       </c>
       <c r="AB28">
-        <v>198.64321171234531</v>
+        <v>742.18805390489183</v>
       </c>
       <c r="AD28" t="s">
         <v>384</v>
@@ -10965,16 +10965,16 @@
         <v>607</v>
       </c>
       <c r="AM28" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AN28" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO28">
-        <v>0.96976012134850453</v>
+        <v>0.96555290739289967</v>
       </c>
       <c r="AP28">
-        <v>554.39777527741785</v>
+        <v>631.53003113017269</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -11039,16 +11039,16 @@
         <v>423</v>
       </c>
       <c r="Y29" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="Z29" t="s">
         <v>535</v>
       </c>
       <c r="AA29">
-        <v>0.99211425265089781</v>
+        <v>0.98916491572478116</v>
       </c>
       <c r="AB29">
-        <v>144.5720347335392</v>
+        <v>198.64321171234531</v>
       </c>
       <c r="AD29" t="s">
         <v>384</v>
@@ -11075,16 +11075,16 @@
         <v>609</v>
       </c>
       <c r="AM29" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AN29" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AO29">
-        <v>0.99893003381794343</v>
+        <v>0.99626371781833423</v>
       </c>
       <c r="AP29">
-        <v>19.616046671036653</v>
+        <v>68.49850666387222</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -11149,16 +11149,16 @@
         <v>425</v>
       </c>
       <c r="Y30" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="Z30" t="s">
         <v>536</v>
       </c>
       <c r="AA30">
-        <v>0.99704781228873474</v>
+        <v>0.99211425265089781</v>
       </c>
       <c r="AB30">
-        <v>54.123441373196478</v>
+        <v>144.5720347335392</v>
       </c>
       <c r="AD30" t="s">
         <v>384</v>
@@ -11185,16 +11185,16 @@
         <v>611</v>
       </c>
       <c r="AM30" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="AN30" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="AO30">
-        <v>0.96939675941164705</v>
+        <v>0.97107796146874092</v>
       </c>
       <c r="AP30">
-        <v>561.05941078647095</v>
+        <v>530.23737307308215</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -11259,16 +11259,16 @@
         <v>427</v>
       </c>
       <c r="Y31" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z31" t="s">
         <v>537</v>
       </c>
       <c r="AA31">
-        <v>0.99928861254927026</v>
+        <v>0.99704781228873474</v>
       </c>
       <c r="AB31">
-        <v>13.04210326337761</v>
+        <v>54.123441373196478</v>
       </c>
       <c r="AD31" t="s">
         <v>384</v>
@@ -11295,16 +11295,16 @@
         <v>613</v>
       </c>
       <c r="AM31" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AN31" t="s">
-        <v>532</v>
+        <v>734</v>
       </c>
       <c r="AO31">
-        <v>0.99774195493840256</v>
+        <v>0.99893003381794343</v>
       </c>
       <c r="AP31">
-        <v>41.397492795953291</v>
+        <v>19.616046671036653</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -11369,16 +11369,16 @@
         <v>429</v>
       </c>
       <c r="Y32" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z32" t="s">
         <v>538</v>
       </c>
       <c r="AA32">
-        <v>0.99918279077066829</v>
+        <v>0.99928861254927026</v>
       </c>
       <c r="AB32">
-        <v>14.982169204414204</v>
+        <v>13.04210326337761</v>
       </c>
       <c r="AD32" t="s">
         <v>384</v>
@@ -11405,16 +11405,16 @@
         <v>615</v>
       </c>
       <c r="AM32" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AN32" t="s">
-        <v>733</v>
+        <v>566</v>
       </c>
       <c r="AO32">
-        <v>0.96887169792625616</v>
+        <v>0.96939675941164705</v>
       </c>
       <c r="AP32">
-        <v>570.68553801863686</v>
+        <v>561.05941078647095</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -11479,16 +11479,16 @@
         <v>431</v>
       </c>
       <c r="Y33" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="Z33" t="s">
         <v>539</v>
       </c>
       <c r="AA33">
-        <v>0.99701498192870486</v>
+        <v>0.99918279077066829</v>
       </c>
       <c r="AB33">
-        <v>54.725331307078172</v>
+        <v>14.982169204414204</v>
       </c>
       <c r="AD33" t="s">
         <v>384</v>
@@ -11515,16 +11515,16 @@
         <v>617</v>
       </c>
       <c r="AM33" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AN33" t="s">
-        <v>735</v>
+        <v>563</v>
       </c>
       <c r="AO33">
-        <v>0.99522505489766133</v>
+        <v>0.99774195493840256</v>
       </c>
       <c r="AP33">
-        <v>87.54066020954204</v>
+        <v>41.397492795953291</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -11589,16 +11589,16 @@
         <v>433</v>
       </c>
       <c r="Y34" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="Z34" t="s">
         <v>540</v>
       </c>
       <c r="AA34">
-        <v>0.96681320638730428</v>
+        <v>0.99701498192870486</v>
       </c>
       <c r="AB34">
-        <v>608.42454956608799</v>
+        <v>54.725331307078172</v>
       </c>
       <c r="AD34" t="s">
         <v>384</v>
@@ -11625,16 +11625,16 @@
         <v>619</v>
       </c>
       <c r="AM34" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AN34" t="s">
-        <v>737</v>
+        <v>535</v>
       </c>
       <c r="AO34">
-        <v>0.99880608610203336</v>
+        <v>0.98622313794978356</v>
       </c>
       <c r="AP34">
-        <v>21.888421462720675</v>
+        <v>252.57580425396782</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11699,16 +11699,16 @@
         <v>435</v>
       </c>
       <c r="Y35" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="Z35" t="s">
         <v>541</v>
       </c>
       <c r="AA35">
-        <v>0.99003291540359517</v>
+        <v>0.9951402828161694</v>
       </c>
       <c r="AB35">
-        <v>182.72988426742148</v>
+        <v>89.094815036894559</v>
       </c>
       <c r="AD35" t="s">
         <v>384</v>
@@ -11741,10 +11741,10 @@
         <v>739</v>
       </c>
       <c r="AO35">
-        <v>0.98962776346505854</v>
+        <v>0.99468247729100656</v>
       </c>
       <c r="AP35">
-        <v>190.15766980725988</v>
+        <v>97.487916331546771</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11809,16 +11809,16 @@
         <v>437</v>
       </c>
       <c r="Y36" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="Z36" t="s">
         <v>542</v>
       </c>
       <c r="AA36">
-        <v>0.99451774199646181</v>
+        <v>0.99038856814984766</v>
       </c>
       <c r="AB36">
-        <v>100.50806339819938</v>
+        <v>176.20958391945942</v>
       </c>
       <c r="AD36" t="s">
         <v>384</v>
@@ -11848,13 +11848,13 @@
         <v>740</v>
       </c>
       <c r="AN36" t="s">
-        <v>550</v>
+        <v>741</v>
       </c>
       <c r="AO36">
-        <v>0.94978410374301969</v>
+        <v>0.9861789081627198</v>
       </c>
       <c r="AP36">
-        <v>920.6247647113064</v>
+        <v>253.38668368347109</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11919,16 +11919,16 @@
         <v>439</v>
       </c>
       <c r="Y37" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="Z37" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="AA37">
-        <v>0.97030132885522102</v>
+        <v>0.96778401809933534</v>
       </c>
       <c r="AB37">
-        <v>544.47563765428208</v>
+        <v>590.62633484551873</v>
       </c>
       <c r="AD37" t="s">
         <v>384</v>
@@ -11955,16 +11955,16 @@
         <v>625</v>
       </c>
       <c r="AM37" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AN37" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="AO37">
-        <v>0.96417711299224196</v>
+        <v>0.98988983533388286</v>
       </c>
       <c r="AP37">
-        <v>656.75292847556489</v>
+        <v>185.35301887881516</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -12029,16 +12029,16 @@
         <v>441</v>
       </c>
       <c r="Y38" t="s">
-        <v>334</v>
+        <v>380</v>
       </c>
       <c r="Z38" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="AA38">
-        <v>0.99876642704737761</v>
+        <v>0.98023840447090371</v>
       </c>
       <c r="AB38">
-        <v>22.615504131410646</v>
+        <v>362.29591803343288</v>
       </c>
       <c r="AD38" t="s">
         <v>384</v>
@@ -12065,16 +12065,16 @@
         <v>627</v>
       </c>
       <c r="AM38" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN38" t="s">
-        <v>520</v>
+        <v>744</v>
       </c>
       <c r="AO38">
-        <v>0.94931253417293127</v>
+        <v>0.99386337452089002</v>
       </c>
       <c r="AP38">
-        <v>929.27020682959278</v>
+        <v>112.50480045034956</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -12139,16 +12139,16 @@
         <v>443</v>
       </c>
       <c r="Y39" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="Z39" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AA39">
-        <v>0.99064855295491527</v>
+        <v>0.98979380819350882</v>
       </c>
       <c r="AB39">
-        <v>171.44319582655291</v>
+        <v>187.11351645233776</v>
       </c>
       <c r="AD39" t="s">
         <v>384</v>
@@ -12175,16 +12175,16 @@
         <v>629</v>
       </c>
       <c r="AM39" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AN39" t="s">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="AO39">
-        <v>0.97927855406064401</v>
+        <v>0.968274309035423</v>
       </c>
       <c r="AP39">
-        <v>379.89317555486042</v>
+        <v>581.63766768391201</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -12249,16 +12249,16 @@
         <v>445</v>
       </c>
       <c r="Y40" t="s">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="Z40" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AA40">
-        <v>0.99735162606593653</v>
+        <v>0.9798698468265471</v>
       </c>
       <c r="AB40">
-        <v>48.553522124496595</v>
+        <v>369.05280817996936</v>
       </c>
       <c r="AD40" t="s">
         <v>384</v>
@@ -12285,16 +12285,16 @@
         <v>631</v>
       </c>
       <c r="AM40" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="AN40" t="s">
-        <v>565</v>
+        <v>521</v>
       </c>
       <c r="AO40">
-        <v>0.99261416554290038</v>
+        <v>0.95295378578294154</v>
       </c>
       <c r="AP40">
-        <v>135.40696504682549</v>
+        <v>862.51392731273927</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -12359,16 +12359,16 @@
         <v>447</v>
       </c>
       <c r="Y41" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="Z41" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AA41">
-        <v>0.99752334755484584</v>
+        <v>0.96752396217182168</v>
       </c>
       <c r="AB41">
-        <v>45.405294827827106</v>
+        <v>595.39402684993593</v>
       </c>
       <c r="AD41" t="s">
         <v>384</v>
@@ -12395,16 +12395,16 @@
         <v>633</v>
       </c>
       <c r="AM41" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AN41" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="AO41">
-        <v>0.94939310241101427</v>
+        <v>0.97927855406064401</v>
       </c>
       <c r="AP41">
-        <v>927.79312246473887</v>
+        <v>379.89317555486042</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -12469,16 +12469,16 @@
         <v>449</v>
       </c>
       <c r="Y42" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="Z42" t="s">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="AA42">
-        <v>0.99394570454136</v>
+        <v>0.96000937928358443</v>
       </c>
       <c r="AB42">
-        <v>110.99541674173295</v>
+        <v>733.16137980095198</v>
       </c>
       <c r="AD42" t="s">
         <v>384</v>
@@ -12505,16 +12505,16 @@
         <v>635</v>
       </c>
       <c r="AM42" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AN42" t="s">
-        <v>747</v>
+        <v>556</v>
       </c>
       <c r="AO42">
-        <v>0.99702300519026088</v>
+        <v>0.99261416554290038</v>
       </c>
       <c r="AP42">
-        <v>54.578238178550102</v>
+        <v>135.40696504682549</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -12579,16 +12579,16 @@
         <v>451</v>
       </c>
       <c r="Y43" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="Z43" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AA43">
-        <v>0.98255746585766901</v>
+        <v>0.99804665079186261</v>
       </c>
       <c r="AB43">
-        <v>319.77979260940054</v>
+        <v>35.811402149186421</v>
       </c>
       <c r="AD43" t="s">
         <v>384</v>
@@ -12615,16 +12615,16 @@
         <v>637</v>
       </c>
       <c r="AM43" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN43" t="s">
-        <v>749</v>
+        <v>566</v>
       </c>
       <c r="AO43">
-        <v>0.99858163704266301</v>
+        <v>0.94939310241101427</v>
       </c>
       <c r="AP43">
-        <v>26.003320884511144</v>
+        <v>927.79312246473887</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12689,16 +12689,16 @@
         <v>453</v>
       </c>
       <c r="Y44" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="Z44" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AA44">
-        <v>0.97767806396937151</v>
+        <v>0.97118475866494502</v>
       </c>
       <c r="AB44">
-        <v>409.23549389485521</v>
+        <v>528.27942447600776</v>
       </c>
       <c r="AD44" t="s">
         <v>384</v>
@@ -12731,10 +12731,10 @@
         <v>751</v>
       </c>
       <c r="AO44">
-        <v>0.9947854490299548</v>
+        <v>0.99702300519026088</v>
       </c>
       <c r="AP44">
-        <v>95.600101117495868</v>
+        <v>54.578238178550102</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12799,16 +12799,16 @@
         <v>455</v>
       </c>
       <c r="Y45" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="Z45" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AA45">
-        <v>0.99672701953917697</v>
+        <v>0.98255746585766901</v>
       </c>
       <c r="AB45">
-        <v>60.004641781756348</v>
+        <v>319.77979260940054</v>
       </c>
       <c r="AD45" t="s">
         <v>384</v>
@@ -12838,13 +12838,13 @@
         <v>752</v>
       </c>
       <c r="AN45" t="s">
-        <v>753</v>
+        <v>556</v>
       </c>
       <c r="AO45">
-        <v>0.99300875779692943</v>
+        <v>0.96976012134850453</v>
       </c>
       <c r="AP45">
-        <v>128.17277372296059</v>
+        <v>554.39777527741785</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12909,16 +12909,16 @@
         <v>457</v>
       </c>
       <c r="Y46" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="Z46" t="s">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="AA46">
-        <v>0.9983826950953073</v>
+        <v>0.97767806396937151</v>
       </c>
       <c r="AB46">
-        <v>29.650589919365284</v>
+        <v>409.23549389485521</v>
       </c>
       <c r="AD46" t="s">
         <v>384</v>
@@ -12945,16 +12945,16 @@
         <v>643</v>
       </c>
       <c r="AM46" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AN46" t="s">
-        <v>755</v>
+        <v>544</v>
       </c>
       <c r="AO46">
-        <v>0.99484872380281231</v>
+        <v>0.98080645969778191</v>
       </c>
       <c r="AP46">
-        <v>94.440063615107306</v>
+        <v>351.88157220733245</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -13019,16 +13019,16 @@
         <v>459</v>
       </c>
       <c r="Y47" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
       <c r="Z47" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AA47">
-        <v>0.9989617523467913</v>
+        <v>0.99672701953917697</v>
       </c>
       <c r="AB47">
-        <v>19.034540308826394</v>
+        <v>60.004641781756348</v>
       </c>
       <c r="AD47" t="s">
         <v>384</v>
@@ -13055,16 +13055,16 @@
         <v>645</v>
       </c>
       <c r="AM47" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="AN47" t="s">
-        <v>550</v>
+        <v>755</v>
       </c>
       <c r="AO47">
-        <v>0.9562603934457885</v>
+        <v>0.96887169792625616</v>
       </c>
       <c r="AP47">
-        <v>801.89278682721124</v>
+        <v>570.68553801863686</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -13129,16 +13129,16 @@
         <v>461</v>
       </c>
       <c r="Y48" t="s">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="Z48" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="AA48">
-        <v>0.95385659112728594</v>
+        <v>0.9983826950953073</v>
       </c>
       <c r="AB48">
-        <v>845.96249599975874</v>
+        <v>29.650589919365284</v>
       </c>
       <c r="AD48" t="s">
         <v>384</v>
@@ -13165,16 +13165,16 @@
         <v>647</v>
       </c>
       <c r="AM48" t="s">
+        <v>756</v>
+      </c>
+      <c r="AN48" t="s">
         <v>757</v>
       </c>
-      <c r="AN48" t="s">
-        <v>758</v>
-      </c>
       <c r="AO48">
-        <v>0.99478509214205779</v>
+        <v>0.99522505489766133</v>
       </c>
       <c r="AP48">
-        <v>95.606644062274157</v>
+        <v>87.54066020954204</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -13239,16 +13239,16 @@
         <v>463</v>
       </c>
       <c r="Y49" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="Z49" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="AA49">
-        <v>0.9951402828161694</v>
+        <v>0.9989617523467913</v>
       </c>
       <c r="AB49">
-        <v>89.094815036894559</v>
+        <v>19.034540308826394</v>
       </c>
       <c r="AD49" t="s">
         <v>384</v>
@@ -13275,16 +13275,16 @@
         <v>649</v>
       </c>
       <c r="AM49" t="s">
+        <v>758</v>
+      </c>
+      <c r="AN49" t="s">
         <v>759</v>
       </c>
-      <c r="AN49" t="s">
-        <v>522</v>
-      </c>
       <c r="AO49">
-        <v>0.98290798239987243</v>
+        <v>0.99880608610203336</v>
       </c>
       <c r="AP49">
-        <v>313.35365600233933</v>
+        <v>21.888421462720675</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -13349,16 +13349,16 @@
         <v>465</v>
       </c>
       <c r="Y50" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="Z50" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="AA50">
-        <v>0.99140122988281854</v>
+        <v>0.95385659112728594</v>
       </c>
       <c r="AB50">
-        <v>157.64411881499262</v>
+        <v>845.96249599975874</v>
       </c>
       <c r="AD50" t="s">
         <v>384</v>
@@ -13391,10 +13391,10 @@
         <v>761</v>
       </c>
       <c r="AO50">
-        <v>0.9982900002192614</v>
+        <v>0.98962776346505854</v>
       </c>
       <c r="AP50">
-        <v>31.349995980207169</v>
+        <v>190.15766980725988</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13459,16 +13459,16 @@
         <v>467</v>
       </c>
       <c r="Y51" t="s">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="Z51" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="AA51">
-        <v>0.95056191060937778</v>
+        <v>0.99735162606593653</v>
       </c>
       <c r="AB51">
-        <v>906.36497216140765</v>
+        <v>48.553522124496595</v>
       </c>
       <c r="AD51" t="s">
         <v>384</v>
@@ -13498,13 +13498,13 @@
         <v>762</v>
       </c>
       <c r="AN51" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="AO51">
-        <v>0.97712291195856049</v>
+        <v>0.94978410374301969</v>
       </c>
       <c r="AP51">
-        <v>419.41328075972342</v>
+        <v>920.6247647113064</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13569,16 +13569,16 @@
         <v>469</v>
       </c>
       <c r="Y52" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Z52" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AA52">
-        <v>0.99693870689560904</v>
+        <v>0.99752334755484584</v>
       </c>
       <c r="AB52">
-        <v>56.123706913834091</v>
+        <v>45.405294827827106</v>
       </c>
       <c r="AD52" t="s">
         <v>384</v>
@@ -13608,13 +13608,13 @@
         <v>763</v>
       </c>
       <c r="AN52" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="AO52">
-        <v>0.95922852522417379</v>
+        <v>0.96417711299224196</v>
       </c>
       <c r="AP52">
-        <v>747.47703755681346</v>
+        <v>656.75292847556489</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13679,16 +13679,16 @@
         <v>471</v>
       </c>
       <c r="Y53" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="Z53" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="AA53">
-        <v>0.97773943430281773</v>
+        <v>0.99394570454136</v>
       </c>
       <c r="AB53">
-        <v>408.11037111500889</v>
+        <v>110.99541674173295</v>
       </c>
       <c r="AD53" t="s">
         <v>384</v>
@@ -13718,13 +13718,13 @@
         <v>764</v>
       </c>
       <c r="AN53" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO53">
-        <v>0.96810449790566344</v>
+        <v>0.94931253417293127</v>
       </c>
       <c r="AP53">
-        <v>584.75087172950259</v>
+        <v>929.27020682959278</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13789,16 +13789,16 @@
         <v>473</v>
       </c>
       <c r="Y54" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="Z54" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="AA54">
-        <v>0.99711217881919312</v>
+        <v>0.97448562633554281</v>
       </c>
       <c r="AB54">
-        <v>52.943388314793616</v>
+        <v>467.76351718171588</v>
       </c>
       <c r="AD54" t="s">
         <v>384</v>
@@ -13831,10 +13831,10 @@
         <v>766</v>
       </c>
       <c r="AO54">
-        <v>0.99878024082202155</v>
+        <v>0.95357273401837306</v>
       </c>
       <c r="AP54">
-        <v>22.362251596271118</v>
+        <v>851.1665429964944</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13899,16 +13899,16 @@
         <v>475</v>
       </c>
       <c r="Y55" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="Z55" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="AA55">
-        <v>0.99520306771735667</v>
+        <v>0.99499214029327188</v>
       </c>
       <c r="AB55">
-        <v>87.943758515128479</v>
+        <v>91.810761290016288</v>
       </c>
       <c r="AD55" t="s">
         <v>384</v>
@@ -13938,13 +13938,13 @@
         <v>767</v>
       </c>
       <c r="AN55" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="AO55">
-        <v>0.95826105465484257</v>
+        <v>0.98030978036614613</v>
       </c>
       <c r="AP55">
-        <v>765.21399799455378</v>
+        <v>360.98735995398783</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -14009,16 +14009,16 @@
         <v>477</v>
       </c>
       <c r="Y56" t="s">
-        <v>374</v>
+        <v>323</v>
       </c>
       <c r="Z56" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="AA56">
-        <v>0.95279789096470435</v>
+        <v>0.99931793846074402</v>
       </c>
       <c r="AB56">
-        <v>865.37199898041979</v>
+        <v>12.504461553027108</v>
       </c>
       <c r="AD56" t="s">
         <v>384</v>
@@ -14048,13 +14048,13 @@
         <v>768</v>
       </c>
       <c r="AN56" t="s">
-        <v>769</v>
+        <v>566</v>
       </c>
       <c r="AO56">
-        <v>0.99750387705430998</v>
+        <v>0.96113902088653813</v>
       </c>
       <c r="AP56">
-        <v>45.762254004316212</v>
+        <v>712.45128374680007</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -14119,16 +14119,16 @@
         <v>479</v>
       </c>
       <c r="Y57" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="Z57" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AA57">
-        <v>0.98772771860538078</v>
+        <v>0.97472500521308103</v>
       </c>
       <c r="AB57">
-        <v>224.99182556801827</v>
+        <v>463.3749044268481</v>
       </c>
       <c r="AD57" t="s">
         <v>384</v>
@@ -14155,16 +14155,16 @@
         <v>665</v>
       </c>
       <c r="AM57" t="s">
+        <v>769</v>
+      </c>
+      <c r="AN57" t="s">
         <v>770</v>
       </c>
-      <c r="AN57" t="s">
-        <v>771</v>
-      </c>
       <c r="AO57">
-        <v>0.99561014484129162</v>
+        <v>0.99849102734574458</v>
       </c>
       <c r="AP57">
-        <v>80.480677909653664</v>
+        <v>27.664498661350322</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -14229,16 +14229,16 @@
         <v>481</v>
       </c>
       <c r="Y58" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="Z58" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AA58">
-        <v>0.99440237434462508</v>
+        <v>0.99590119173517544</v>
       </c>
       <c r="AB58">
-        <v>102.62313701520689</v>
+        <v>75.144818188450657</v>
       </c>
       <c r="AD58" t="s">
         <v>384</v>
@@ -14265,16 +14265,16 @@
         <v>667</v>
       </c>
       <c r="AM58" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AN58" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="AO58">
-        <v>0.98080645969778191</v>
+        <v>0.96193362161848472</v>
       </c>
       <c r="AP58">
-        <v>351.88157220733245</v>
+        <v>697.88360366111351</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -14339,16 +14339,16 @@
         <v>483</v>
       </c>
       <c r="Y59" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="Z59" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AA59">
-        <v>0.99854932678297781</v>
+        <v>0.99110706411505001</v>
       </c>
       <c r="AB59">
-        <v>26.595675645406835</v>
+        <v>163.03715789074991</v>
       </c>
       <c r="AD59" t="s">
         <v>384</v>
@@ -14375,16 +14375,16 @@
         <v>669</v>
       </c>
       <c r="AM59" t="s">
+        <v>772</v>
+      </c>
+      <c r="AN59" t="s">
         <v>773</v>
       </c>
-      <c r="AN59" t="s">
-        <v>534</v>
-      </c>
       <c r="AO59">
-        <v>0.98622313794978356</v>
+        <v>0.98925468246747761</v>
       </c>
       <c r="AP59">
-        <v>252.57580425396782</v>
+        <v>196.99748809624356</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14449,16 +14449,16 @@
         <v>485</v>
       </c>
       <c r="Y60" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="Z60" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AA60">
-        <v>0.99739948219126473</v>
+        <v>0.99685014674837746</v>
       </c>
       <c r="AB60">
-        <v>47.676159826814242</v>
+        <v>57.74730961308002</v>
       </c>
       <c r="AD60" t="s">
         <v>384</v>
@@ -14488,13 +14488,13 @@
         <v>774</v>
       </c>
       <c r="AN60" t="s">
-        <v>775</v>
+        <v>523</v>
       </c>
       <c r="AO60">
-        <v>0.99468247729100656</v>
+        <v>0.94921224886563393</v>
       </c>
       <c r="AP60">
-        <v>97.487916331546771</v>
+        <v>931.10877079671207</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14559,16 +14559,16 @@
         <v>487</v>
       </c>
       <c r="Y61" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="Z61" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="AA61">
-        <v>0.97448562633554281</v>
+        <v>0.98711864194461818</v>
       </c>
       <c r="AB61">
-        <v>467.76351718171588</v>
+        <v>236.15823101533312</v>
       </c>
       <c r="AD61" t="s">
         <v>384</v>
@@ -14595,16 +14595,16 @@
         <v>673</v>
       </c>
       <c r="AM61" t="s">
+        <v>775</v>
+      </c>
+      <c r="AN61" t="s">
         <v>776</v>
       </c>
-      <c r="AN61" t="s">
-        <v>777</v>
-      </c>
       <c r="AO61">
-        <v>0.9861789081627198</v>
+        <v>0.99916742781336532</v>
       </c>
       <c r="AP61">
-        <v>253.38668368347109</v>
+        <v>15.263823421635696</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14669,16 +14669,16 @@
         <v>489</v>
       </c>
       <c r="Y62" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="Z62" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AA62">
-        <v>0.99499214029327188</v>
+        <v>0.99031833701436367</v>
       </c>
       <c r="AB62">
-        <v>91.810761290016288</v>
+        <v>177.49715473666521</v>
       </c>
       <c r="AD62" t="s">
         <v>384</v>
@@ -14705,16 +14705,16 @@
         <v>675</v>
       </c>
       <c r="AM62" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AN62" t="s">
-        <v>520</v>
+        <v>562</v>
       </c>
       <c r="AO62">
-        <v>0.98988983533388286</v>
+        <v>0.97346893638374543</v>
       </c>
       <c r="AP62">
-        <v>185.35301887881516</v>
+        <v>486.40283296466674</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14779,16 +14779,16 @@
         <v>491</v>
       </c>
       <c r="Y63" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="Z63" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AA63">
-        <v>0.99931793846074402</v>
+        <v>0.99538973816509291</v>
       </c>
       <c r="AB63">
-        <v>12.504461553027108</v>
+        <v>84.521466973297393</v>
       </c>
       <c r="AD63" t="s">
         <v>384</v>
@@ -14815,16 +14815,16 @@
         <v>677</v>
       </c>
       <c r="AM63" t="s">
+        <v>778</v>
+      </c>
+      <c r="AN63" t="s">
         <v>779</v>
       </c>
-      <c r="AN63" t="s">
-        <v>780</v>
-      </c>
       <c r="AO63">
-        <v>0.96153074659796378</v>
+        <v>0.99858163704266301</v>
       </c>
       <c r="AP63">
-        <v>705.26964570399718</v>
+        <v>26.003320884511144</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14889,16 +14889,16 @@
         <v>493</v>
       </c>
       <c r="Y64" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="Z64" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AA64">
-        <v>0.97472500521308103</v>
+        <v>0.98685658514563523</v>
       </c>
       <c r="AB64">
-        <v>463.3749044268481</v>
+        <v>240.96260566335508</v>
       </c>
       <c r="AD64" t="s">
         <v>384</v>
@@ -14925,16 +14925,16 @@
         <v>679</v>
       </c>
       <c r="AM64" t="s">
+        <v>780</v>
+      </c>
+      <c r="AN64" t="s">
         <v>781</v>
       </c>
-      <c r="AN64" t="s">
-        <v>541</v>
-      </c>
       <c r="AO64">
-        <v>0.97193777368455281</v>
+        <v>0.9947854490299548</v>
       </c>
       <c r="AP64">
-        <v>514.47414911653129</v>
+        <v>95.600101117495868</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14999,16 +14999,16 @@
         <v>495</v>
       </c>
       <c r="Y65" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="Z65" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AA65">
-        <v>0.99590119173517544</v>
+        <v>0.99775167610563054</v>
       </c>
       <c r="AB65">
-        <v>75.144818188450657</v>
+        <v>41.219271396774424</v>
       </c>
       <c r="AD65" t="s">
         <v>384</v>
@@ -15041,10 +15041,10 @@
         <v>783</v>
       </c>
       <c r="AO65">
-        <v>0.99534050757450643</v>
+        <v>0.99300875779692943</v>
       </c>
       <c r="AP65">
-        <v>85.424027800715081</v>
+        <v>128.17277372296059</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -15109,16 +15109,16 @@
         <v>497</v>
       </c>
       <c r="Y66" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="Z66" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AA66">
-        <v>0.99110706411505001</v>
+        <v>0.96681320638730428</v>
       </c>
       <c r="AB66">
-        <v>163.03715789074991</v>
+        <v>608.42454956608799</v>
       </c>
       <c r="AD66" t="s">
         <v>384</v>
@@ -15151,10 +15151,10 @@
         <v>785</v>
       </c>
       <c r="AO66">
-        <v>0.99277178058643201</v>
+        <v>0.99484872380281231</v>
       </c>
       <c r="AP66">
-        <v>132.51735591541228</v>
+        <v>94.440063615107306</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -15219,16 +15219,16 @@
         <v>499</v>
       </c>
       <c r="Y67" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="Z67" t="s">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="AA67">
-        <v>0.99685014674837746</v>
+        <v>0.99003291540359517</v>
       </c>
       <c r="AB67">
-        <v>57.74730961308002</v>
+        <v>182.72988426742148</v>
       </c>
       <c r="AD67" t="s">
         <v>384</v>
@@ -15258,13 +15258,13 @@
         <v>786</v>
       </c>
       <c r="AN67" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AO67">
-        <v>0.99185568153246984</v>
+        <v>0.9562603934457885</v>
       </c>
       <c r="AP67">
-        <v>149.31250523805363</v>
+        <v>801.89278682721124</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -15329,16 +15329,16 @@
         <v>501</v>
       </c>
       <c r="Y68" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="Z68" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AA68">
-        <v>0.98711864194461818</v>
+        <v>0.99451774199646181</v>
       </c>
       <c r="AB68">
-        <v>236.15823101533312</v>
+        <v>100.50806339819938</v>
       </c>
       <c r="AD68" t="s">
         <v>384</v>
@@ -15368,13 +15368,13 @@
         <v>787</v>
       </c>
       <c r="AN68" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="AO68">
-        <v>0.96193362161848472</v>
+        <v>0.98179238163829652</v>
       </c>
       <c r="AP68">
-        <v>697.88360366111351</v>
+        <v>333.80633663123064</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -15439,16 +15439,16 @@
         <v>503</v>
       </c>
       <c r="Y69" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="Z69" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="AA69">
-        <v>0.99031833701436367</v>
+        <v>0.97030132885522102</v>
       </c>
       <c r="AB69">
-        <v>177.49715473666521</v>
+        <v>544.47563765428208</v>
       </c>
       <c r="AD69" t="s">
         <v>384</v>
@@ -15478,13 +15478,13 @@
         <v>788</v>
       </c>
       <c r="AN69" t="s">
-        <v>789</v>
+        <v>562</v>
       </c>
       <c r="AO69">
-        <v>0.98925468246747761</v>
+        <v>0.97994970755923727</v>
       </c>
       <c r="AP69">
-        <v>196.99748809624356</v>
+        <v>367.58869474731648</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15549,16 +15549,16 @@
         <v>505</v>
       </c>
       <c r="Y70" t="s">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="Z70" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="AA70">
-        <v>0.99087272805509874</v>
+        <v>0.99876642704737761</v>
       </c>
       <c r="AB70">
-        <v>167.33331898985637</v>
+        <v>22.615504131410646</v>
       </c>
       <c r="AD70" t="s">
         <v>384</v>
@@ -15585,16 +15585,16 @@
         <v>691</v>
       </c>
       <c r="AM70" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AN70" t="s">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="AO70">
-        <v>0.94921224886563393</v>
+        <v>0.96599440792497671</v>
       </c>
       <c r="AP70">
-        <v>931.10877079671207</v>
+        <v>623.43585470875962</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15659,16 +15659,16 @@
         <v>507</v>
       </c>
       <c r="Y71" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="Z71" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="AA71">
-        <v>0.9646219268942855</v>
+        <v>0.99064855295491527</v>
       </c>
       <c r="AB71">
-        <v>648.59800693809962</v>
+        <v>171.44319582655291</v>
       </c>
       <c r="AD71" t="s">
         <v>384</v>
@@ -15695,16 +15695,16 @@
         <v>693</v>
       </c>
       <c r="AM71" t="s">
+        <v>790</v>
+      </c>
+      <c r="AN71" t="s">
         <v>791</v>
       </c>
-      <c r="AN71" t="s">
-        <v>792</v>
-      </c>
       <c r="AO71">
-        <v>0.99916742781336532</v>
+        <v>0.99878024082202155</v>
       </c>
       <c r="AP71">
-        <v>15.263823421635696</v>
+        <v>22.362251596271118</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15769,16 +15769,16 @@
         <v>509</v>
       </c>
       <c r="Y72" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="Z72" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="AA72">
-        <v>0.96752396217182168</v>
+        <v>0.98772771860538078</v>
       </c>
       <c r="AB72">
-        <v>595.39402684993593</v>
+        <v>224.99182556801827</v>
       </c>
       <c r="AD72" t="s">
         <v>384</v>
@@ -15805,16 +15805,16 @@
         <v>695</v>
       </c>
       <c r="AM72" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AN72" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AO72">
-        <v>0.97346893638374543</v>
+        <v>0.95826105465484257</v>
       </c>
       <c r="AP72">
-        <v>486.40283296466674</v>
+        <v>765.21399799455378</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -15879,16 +15879,16 @@
         <v>511</v>
       </c>
       <c r="Y73" t="s">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="Z73" t="s">
-        <v>522</v>
+        <v>570</v>
       </c>
       <c r="AA73">
-        <v>0.96000937928358443</v>
+        <v>0.99440237434462508</v>
       </c>
       <c r="AB73">
-        <v>733.16137980095198</v>
+        <v>102.62313701520689</v>
       </c>
       <c r="AD73" t="s">
         <v>384</v>
@@ -15915,16 +15915,16 @@
         <v>697</v>
       </c>
       <c r="AM73" t="s">
+        <v>793</v>
+      </c>
+      <c r="AN73" t="s">
         <v>794</v>
       </c>
-      <c r="AN73" t="s">
-        <v>795</v>
-      </c>
       <c r="AO73">
-        <v>0.99386337452089002</v>
+        <v>0.99750387705430998</v>
       </c>
       <c r="AP73">
-        <v>112.50480045034956</v>
+        <v>45.762254004316212</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -15989,16 +15989,16 @@
         <v>513</v>
       </c>
       <c r="Y74" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="Z74" t="s">
         <v>571</v>
       </c>
       <c r="AA74">
-        <v>0.99804665079186261</v>
+        <v>0.99854932678297781</v>
       </c>
       <c r="AB74">
-        <v>35.811402149186421</v>
+        <v>26.595675645406835</v>
       </c>
       <c r="AD74" t="s">
         <v>384</v>
@@ -16025,16 +16025,16 @@
         <v>699</v>
       </c>
       <c r="AM74" t="s">
+        <v>795</v>
+      </c>
+      <c r="AN74" t="s">
         <v>796</v>
       </c>
-      <c r="AN74" t="s">
-        <v>522</v>
-      </c>
       <c r="AO74">
-        <v>0.968274309035423</v>
+        <v>0.99561014484129162</v>
       </c>
       <c r="AP74">
-        <v>581.63766768391201</v>
+        <v>80.480677909653664</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -16099,16 +16099,16 @@
         <v>515</v>
       </c>
       <c r="Y75" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="Z75" t="s">
         <v>572</v>
       </c>
       <c r="AA75">
-        <v>0.97118475866494502</v>
+        <v>0.99739948219126473</v>
       </c>
       <c r="AB75">
-        <v>528.27942447600776</v>
+        <v>47.676159826814242</v>
       </c>
       <c r="AD75" t="s">
         <v>384</v>
@@ -16138,13 +16138,13 @@
         <v>797</v>
       </c>
       <c r="AN75" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="AO75">
-        <v>0.95295378578294154</v>
+        <v>0.99456229904023075</v>
       </c>
       <c r="AP75">
-        <v>862.51392731273927</v>
+        <v>99.691184262436323</v>
       </c>
     </row>
   </sheetData>
@@ -16153,7 +16153,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5B677E-E748-497D-84C9-57B45DA1F700}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DFD321-D1EA-497B-9E1A-EF0DA494F4B4}">
   <dimension ref="B9:Z75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16265,7 +16265,7 @@
         <v>838</v>
       </c>
       <c r="K11" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="L11">
         <v>4.2668408855841076</v>
@@ -16298,7 +16298,7 @@
         <v>968</v>
       </c>
       <c r="X11" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="Y11">
         <v>11.795999999999999</v>
@@ -16333,7 +16333,7 @@
         <v>840</v>
       </c>
       <c r="K12" t="s">
-        <v>721</v>
+        <v>769</v>
       </c>
       <c r="L12">
         <v>1.8684162546234937</v>
@@ -16366,7 +16366,7 @@
         <v>970</v>
       </c>
       <c r="X12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="Y12">
         <v>3.17625</v>
@@ -16401,7 +16401,7 @@
         <v>842</v>
       </c>
       <c r="K13" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="L13">
         <v>0.70776635133171628</v>
@@ -16434,7 +16434,7 @@
         <v>972</v>
       </c>
       <c r="X13" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="Y13">
         <v>0.83550000000000002</v>
@@ -16469,7 +16469,7 @@
         <v>844</v>
       </c>
       <c r="K14" t="s">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="L14">
         <v>38.566850937358645</v>
@@ -16502,7 +16502,7 @@
         <v>974</v>
       </c>
       <c r="X14" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="Y14">
         <v>2.22675</v>
@@ -16537,7 +16537,7 @@
         <v>846</v>
       </c>
       <c r="K15" t="s">
-        <v>748</v>
+        <v>778</v>
       </c>
       <c r="L15">
         <v>2.0845713431158761</v>
@@ -16570,7 +16570,7 @@
         <v>976</v>
       </c>
       <c r="X15" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="Y15">
         <v>4.7437500000000004</v>
@@ -16605,7 +16605,7 @@
         <v>848</v>
       </c>
       <c r="K16" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="L16">
         <v>5.0973809601425186</v>
@@ -16638,7 +16638,7 @@
         <v>978</v>
       </c>
       <c r="X16" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="Y16">
         <v>11.138249999999999</v>
@@ -16673,7 +16673,7 @@
         <v>850</v>
       </c>
       <c r="K17" t="s">
-        <v>736</v>
+        <v>758</v>
       </c>
       <c r="L17">
         <v>2.1877470691969978</v>
@@ -16706,7 +16706,7 @@
         <v>980</v>
       </c>
       <c r="X17" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="Y17">
         <v>4.9755000000000003</v>
@@ -16741,7 +16741,7 @@
         <v>852</v>
       </c>
       <c r="K18" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
       <c r="L18">
         <v>5.5730316958223378</v>
@@ -16774,7 +16774,7 @@
         <v>982</v>
       </c>
       <c r="X18" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="Y18">
         <v>3.4162499999999998</v>
@@ -16809,7 +16809,7 @@
         <v>854</v>
       </c>
       <c r="K19" t="s">
-        <v>760</v>
+        <v>706</v>
       </c>
       <c r="L19">
         <v>6.4986819696730596</v>
@@ -16842,7 +16842,7 @@
         <v>984</v>
       </c>
       <c r="X19" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="Y19">
         <v>2.8919999999999999</v>
@@ -16877,7 +16877,7 @@
         <v>856</v>
       </c>
       <c r="K20" t="s">
-        <v>778</v>
+        <v>742</v>
       </c>
       <c r="L20">
         <v>47.844720893056341</v>
@@ -16910,7 +16910,7 @@
         <v>986</v>
       </c>
       <c r="X20" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="Y20">
         <v>2.1</v>
@@ -16945,7 +16945,7 @@
         <v>858</v>
       </c>
       <c r="K21" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="L21">
         <v>98.68994695303239</v>
@@ -16980,7 +16980,7 @@
         <v>860</v>
       </c>
       <c r="K22" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="L22">
         <v>96.181751330332375</v>
@@ -17015,7 +17015,7 @@
         <v>862</v>
       </c>
       <c r="K23" t="s">
-        <v>752</v>
+        <v>782</v>
       </c>
       <c r="L23">
         <v>87.202849070038098</v>
@@ -17050,7 +17050,7 @@
         <v>864</v>
       </c>
       <c r="K24" t="s">
-        <v>776</v>
+        <v>740</v>
       </c>
       <c r="L24">
         <v>78.197884523894999</v>
@@ -17085,7 +17085,7 @@
         <v>866</v>
       </c>
       <c r="K25" t="s">
-        <v>726</v>
+        <v>789</v>
       </c>
       <c r="L25">
         <v>42.529732597711799</v>
@@ -17120,7 +17120,7 @@
         <v>868</v>
       </c>
       <c r="K26" t="s">
-        <v>797</v>
+        <v>746</v>
       </c>
       <c r="L26">
         <v>34.587215740299207</v>
@@ -17155,7 +17155,7 @@
         <v>870</v>
       </c>
       <c r="K27" t="s">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="L27">
         <v>42.25643238813123</v>
@@ -17190,7 +17190,7 @@
         <v>872</v>
       </c>
       <c r="K28" t="s">
-        <v>720</v>
+        <v>768</v>
       </c>
       <c r="L28">
         <v>19.303135607289168</v>
@@ -17225,7 +17225,7 @@
         <v>874</v>
       </c>
       <c r="K29" t="s">
-        <v>741</v>
+        <v>763</v>
       </c>
       <c r="L29">
         <v>50.305360025131641</v>
@@ -17260,7 +17260,7 @@
         <v>876</v>
       </c>
       <c r="K30" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="L30">
         <v>25.462515402991507</v>
@@ -17295,7 +17295,7 @@
         <v>878</v>
       </c>
       <c r="K31" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="L31">
         <v>27.658680455660367</v>
@@ -17330,7 +17330,7 @@
         <v>880</v>
       </c>
       <c r="K32" t="s">
-        <v>764</v>
+        <v>710</v>
       </c>
       <c r="L32">
         <v>26.661225597421318</v>
@@ -17365,7 +17365,7 @@
         <v>882</v>
       </c>
       <c r="K33" t="s">
-        <v>724</v>
+        <v>787</v>
       </c>
       <c r="L33">
         <v>43.955323212040426</v>
@@ -17400,7 +17400,7 @@
         <v>884</v>
       </c>
       <c r="K34" t="s">
-        <v>725</v>
+        <v>788</v>
       </c>
       <c r="L34">
         <v>16.489617433165694</v>
@@ -17435,7 +17435,7 @@
         <v>886</v>
       </c>
       <c r="K35" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="L35">
         <v>25.647547433244167</v>
@@ -17470,7 +17470,7 @@
         <v>888</v>
       </c>
       <c r="K36" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="L36">
         <v>52.43600239879752</v>
@@ -17505,7 +17505,7 @@
         <v>890</v>
       </c>
       <c r="K37" t="s">
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="L37">
         <v>49.250791120392286</v>
@@ -17540,7 +17540,7 @@
         <v>892</v>
       </c>
       <c r="K38" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="L38">
         <v>96.8691729106054</v>
@@ -17575,7 +17575,7 @@
         <v>894</v>
       </c>
       <c r="K39" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="L39">
         <v>39.121166186979593</v>
@@ -17610,7 +17610,7 @@
         <v>896</v>
       </c>
       <c r="K40" t="s">
-        <v>763</v>
+        <v>709</v>
       </c>
       <c r="L40">
         <v>52.098216977205659</v>
@@ -17645,7 +17645,7 @@
         <v>898</v>
       </c>
       <c r="K41" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="L41">
         <v>71.143701624958894</v>
@@ -17680,7 +17680,7 @@
         <v>900</v>
       </c>
       <c r="K42" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="L42">
         <v>123.17884915939072</v>
@@ -17715,7 +17715,7 @@
         <v>902</v>
       </c>
       <c r="K43" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="L43">
         <v>91.323946420506616</v>
@@ -17750,7 +17750,7 @@
         <v>904</v>
       </c>
       <c r="K44" t="s">
-        <v>786</v>
+        <v>718</v>
       </c>
       <c r="L44">
         <v>51.618040044402491</v>
@@ -17785,7 +17785,7 @@
         <v>906</v>
       </c>
       <c r="K45" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="L45">
         <v>99.011450390281297</v>
@@ -17820,7 +17820,7 @@
         <v>908</v>
       </c>
       <c r="K46" t="s">
-        <v>759</v>
+        <v>705</v>
       </c>
       <c r="L46">
         <v>61.706057214399763</v>
@@ -17855,7 +17855,7 @@
         <v>910</v>
       </c>
       <c r="K47" t="s">
-        <v>762</v>
+        <v>708</v>
       </c>
       <c r="L47">
         <v>49.137871464813081</v>
@@ -17890,7 +17890,7 @@
         <v>912</v>
       </c>
       <c r="K48" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="L48">
         <v>33.734564973116228</v>
@@ -17925,7 +17925,7 @@
         <v>914</v>
       </c>
       <c r="K49" t="s">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="L49">
         <v>47.816600382052599</v>
@@ -17960,7 +17960,7 @@
         <v>916</v>
       </c>
       <c r="K50" t="s">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="L50">
         <v>46.698997298088187</v>
@@ -17995,7 +17995,7 @@
         <v>918</v>
       </c>
       <c r="K51" t="s">
-        <v>796</v>
+        <v>745</v>
       </c>
       <c r="L51">
         <v>75.050246959082855</v>
@@ -18030,7 +18030,7 @@
         <v>920</v>
       </c>
       <c r="K52" t="s">
-        <v>719</v>
+        <v>767</v>
       </c>
       <c r="L52">
         <v>75.030891903133281</v>
@@ -18065,7 +18065,7 @@
         <v>922</v>
       </c>
       <c r="K53" t="s">
-        <v>781</v>
+        <v>713</v>
       </c>
       <c r="L53">
         <v>78.488972319419887</v>
@@ -18100,7 +18100,7 @@
         <v>924</v>
       </c>
       <c r="K54" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="L54">
         <v>56.196726218849591</v>
@@ -18135,7 +18135,7 @@
         <v>926</v>
       </c>
       <c r="K55" t="s">
-        <v>782</v>
+        <v>714</v>
       </c>
       <c r="L55">
         <v>79.392159968768212</v>
@@ -18170,7 +18170,7 @@
         <v>928</v>
       </c>
       <c r="K56" t="s">
-        <v>784</v>
+        <v>716</v>
       </c>
       <c r="L56">
         <v>62.768179395836441</v>
@@ -18205,7 +18205,7 @@
         <v>930</v>
       </c>
       <c r="K57" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
       <c r="L57">
         <v>38.863455871308048</v>
@@ -18240,7 +18240,7 @@
         <v>932</v>
       </c>
       <c r="K58" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="L58">
         <v>49.332782197188976</v>
@@ -18275,7 +18275,7 @@
         <v>934</v>
       </c>
       <c r="K59" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="L59">
         <v>47.929375805367769</v>
@@ -18310,7 +18310,7 @@
         <v>936</v>
       </c>
       <c r="K60" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
       <c r="L60">
         <v>77.393342850934502</v>
@@ -18345,7 +18345,7 @@
         <v>938</v>
       </c>
       <c r="K61" t="s">
-        <v>779</v>
+        <v>711</v>
       </c>
       <c r="L61">
         <v>45.478139706797812</v>
@@ -18380,7 +18380,7 @@
         <v>940</v>
       </c>
       <c r="K62" t="s">
-        <v>717</v>
+        <v>765</v>
       </c>
       <c r="L62">
         <v>48.140294920365903</v>
@@ -18415,7 +18415,7 @@
         <v>942</v>
       </c>
       <c r="K63" t="s">
-        <v>794</v>
+        <v>743</v>
       </c>
       <c r="L63">
         <v>15.637923531445407</v>
@@ -18450,7 +18450,7 @@
         <v>944</v>
       </c>
       <c r="K64" t="s">
-        <v>723</v>
+        <v>797</v>
       </c>
       <c r="L64">
         <v>51.794566350258954</v>
@@ -18485,7 +18485,7 @@
         <v>946</v>
       </c>
       <c r="K65" t="s">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="L65">
         <v>78.70246336743719</v>
@@ -18520,7 +18520,7 @@
         <v>948</v>
       </c>
       <c r="K66" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="L66">
         <v>86.908524101933608</v>
@@ -18555,7 +18555,7 @@
         <v>950</v>
       </c>
       <c r="K67" t="s">
-        <v>757</v>
+        <v>703</v>
       </c>
       <c r="L67">
         <v>54.455844858601104</v>
@@ -18590,7 +18590,7 @@
         <v>952</v>
       </c>
       <c r="K68" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="L68">
         <v>1.0625916947319844</v>
@@ -18625,7 +18625,7 @@
         <v>954</v>
       </c>
       <c r="K69" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="L69">
         <v>19.300562207456217</v>
@@ -18660,7 +18660,7 @@
         <v>956</v>
       </c>
       <c r="K70" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L70">
         <v>29.976025047721809</v>
@@ -18695,7 +18695,7 @@
         <v>958</v>
       </c>
       <c r="K71" t="s">
-        <v>754</v>
+        <v>784</v>
       </c>
       <c r="L71">
         <v>55.882428131538255</v>
@@ -18730,7 +18730,7 @@
         <v>960</v>
       </c>
       <c r="K72" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="L72">
         <v>58.276159234953511</v>
@@ -18765,7 +18765,7 @@
         <v>962</v>
       </c>
       <c r="K73" t="s">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="L73">
         <v>110.24417575298389</v>
@@ -18800,7 +18800,7 @@
         <v>964</v>
       </c>
       <c r="K74" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="L74">
         <v>56.928196652598764</v>
@@ -18835,7 +18835,7 @@
         <v>966</v>
       </c>
       <c r="K75" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="L75">
         <v>57.985815283224305</v>
@@ -18850,7 +18850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940D22E2-1155-44CB-BA44-4AFF83ABD79D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F3FA258-FC68-43C8-ABB4-C38B54D2E0A1}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20667,7 +20667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95FE2CF6-D61B-42A2-9E59-C6E48F85B3A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C457D9-8C5E-47F7-B4DA-79E090978D9F}">
   <dimension ref="B2:M51"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_DZA_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37EF8D80-2082-40E0-84DF-F588D4365162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18C70031-A310-47E9-A039-8B7AC1A8A04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1327,6 +1327,228 @@
     <t>connecting solar to buses in cluster 41</t>
   </si>
   <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_010</t>
   </si>
   <si>
@@ -1357,6 +1579,66 @@
     <t>connecting solar to buses in cluster 62</t>
   </si>
   <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_057</t>
   </si>
   <si>
@@ -1399,288 +1681,6 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1702,6 +1702,60 @@
     <t>e_w383754584-400,e_DZ139-400</t>
   </si>
   <si>
+    <t>e_w833562295-400</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_w383754584-400</t>
+  </si>
+  <si>
+    <t>e_w173682343-400,e_w359380463-400</t>
+  </si>
+  <si>
+    <t>e_w380271836-400</t>
+  </si>
+  <si>
+    <t>e_w1377912118-400,e_DZ109-400,e_w226912498-400,e_DZ128-400,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_w380271836-400</t>
+  </si>
+  <si>
+    <t>e_DZ87-400,e_w359380463-400,e_w574859222-400</t>
+  </si>
+  <si>
+    <t>e_w176932212-400,e_w177004931-400,e_DZ1-400,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>e_DZ134-400,e_w833562295-400</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_DZ134-400,e_w173682343-400</t>
+  </si>
+  <si>
+    <t>e_w610844609-400</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_DZ134-400</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_w380271836-400,e_w383754584-400</t>
+  </si>
+  <si>
+    <t>e_DZ135-400,e_w569616485-400,e_DZ139-400,e_w569616471-400</t>
+  </si>
+  <si>
+    <t>e_DZ134-400,e_DZ113-400,e_w173677993-400,e_w635672953-400</t>
+  </si>
+  <si>
+    <t>e_w226392269-400,e_DZ71-400,e_DZ63-400</t>
+  </si>
+  <si>
+    <t>e_DZ65-400,e_DZ67-400,e_w377716686-400,e_DZ50-400,e_w173670759-400</t>
+  </si>
+  <si>
+    <t>e_w226392269-400,e_w569616485-400,e_w569616471-400,e_w694000747-400</t>
+  </si>
+  <si>
     <t>e_DZ87-400,e_DZ66-400</t>
   </si>
   <si>
@@ -1711,79 +1765,133 @@
     <t>e_DZ63-400,e_w694011250-400,e_w174512286-400,e_w694011253-400,e_w1377912118-400,e_w176932212-400,e_w176932220-400</t>
   </si>
   <si>
-    <t>e_DZ134-400,e_w833562295-400</t>
-  </si>
-  <si>
-    <t>e_w833562295-400</t>
+    <t>e_DZ134-400,e_w173682343-400</t>
+  </si>
+  <si>
+    <t>e_DZ72-400,e_DZ13-400,e_w221085150-400,e_DZ2-400,e_DZ71-400</t>
+  </si>
+  <si>
+    <t>e_w380271836-400,e_w383754584-400</t>
+  </si>
+  <si>
+    <t>e_w610844609-400,e_DZ72-400,e_w221085150-400,e_w226392269-400,e_DZ71-400</t>
+  </si>
+  <si>
+    <t>e_w380271836-400,e_w383754584-400,e_DZ135-400</t>
   </si>
   <si>
     <t>e_w359380463-400,e_w380271836-400,e_w610844609-400</t>
   </si>
   <si>
-    <t>e_w380271836-400,e_w383754584-400</t>
-  </si>
-  <si>
     <t>e_DZ139-400,e_w1377912118-400,e_DZ128-400</t>
   </si>
   <si>
-    <t>e_w610844609-400,e_DZ72-400,e_w221085150-400,e_w226392269-400,e_DZ71-400</t>
-  </si>
-  <si>
-    <t>e_w380271836-400,e_w383754584-400,e_DZ135-400</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_w380271836-400</t>
-  </si>
-  <si>
-    <t>e_DZ87-400,e_w359380463-400,e_w574859222-400</t>
-  </si>
-  <si>
-    <t>e_w380271836-400</t>
-  </si>
-  <si>
-    <t>e_w176932212-400,e_w177004931-400,e_DZ1-400,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_DZ134-400</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_w383754584-400</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_w380271836-400,e_w383754584-400</t>
-  </si>
-  <si>
-    <t>e_DZ135-400,e_w569616485-400,e_DZ139-400,e_w569616471-400</t>
-  </si>
-  <si>
-    <t>e_DZ65-400,e_DZ67-400,e_w377716686-400,e_DZ50-400,e_w173670759-400</t>
-  </si>
-  <si>
-    <t>e_w226392269-400,e_w569616485-400,e_w569616471-400,e_w694000747-400</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_DZ134-400,e_w173682343-400</t>
-  </si>
-  <si>
-    <t>e_w610844609-400</t>
-  </si>
-  <si>
-    <t>e_w173682343-400,e_w359380463-400</t>
-  </si>
-  <si>
-    <t>e_w1377912118-400,e_DZ109-400,e_w226912498-400,e_DZ128-400,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>e_DZ134-400,e_DZ113-400,e_w173677993-400,e_w635672953-400</t>
-  </si>
-  <si>
-    <t>e_w226392269-400,e_DZ71-400,e_DZ63-400</t>
-  </si>
-  <si>
-    <t>e_DZ134-400,e_w173682343-400</t>
-  </si>
-  <si>
-    <t>e_DZ72-400,e_DZ13-400,e_w221085150-400,e_DZ2-400,e_DZ71-400</t>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
   </si>
   <si>
     <t>distr_wonelc_won_045</t>
@@ -1804,6 +1912,234 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_028</t>
   </si>
   <si>
@@ -1828,108 +2164,6 @@
     <t>connecting wind onshore to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_065</t>
   </si>
   <si>
@@ -1942,238 +2176,73 @@
     <t>connecting wind onshore to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w377716686-400,e_w173670759-400,e_DZ13-400,e_DZ2-400</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_DZ71-400,e_DZ63-400,e_w694011250-400,e_w694011253-400,e_w176932220-400,e_w176932212-400,e_DZ1-400,e_w177004931-400,e_DZ45-400</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_DZ113-400,e_w173677993-400,e_w635672953-400,e_DZ87-400,e_DZ66-400,e_DZ65-400</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_w1377912118-400,e_DZ128-400</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_w380271836-400,e_w383754584-400,e_DZ135-400,e_DZ139-400</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
   </si>
   <si>
     <t>elc_won_045</t>
@@ -2191,6 +2260,138 @@
     <t>e_w694000747-400,e_w174512286-400,e_w1377912118-400,e_w176932212-400,e_DZ109-400,e_w226912498-400,e_DZ128-400,e_w177004931-400,e_DZ45-400</t>
   </si>
   <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_DZ134-400,e_w173682343-400,e_w359380463-400</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>e_w833562295-400,e_w380271836-400,e_w610844609-400</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_DZ134-400,e_DZ113-400,e_w173682343-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w173677993-400,e_w173682343-400,e_w635672953-400,e_w359380463-400,e_DZ87-400,e_w574859222-400</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w574859222-400,e_DZ67-400,e_w377716686-400,e_w610844609-400,e_DZ50-400,e_DZ72-400,e_w221085150-400</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_DZ71-400,e_w226392269-400,e_DZ63-400,e_w694000747-400,e_w174512286-400</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
     <t>elc_won_028</t>
   </si>
   <si>
@@ -2203,63 +2404,6 @@
     <t>elc_won_025</t>
   </si>
   <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_w1377912118-400,e_DZ128-400</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>elc_won_052</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_DZ134-400,e_w173682343-400,e_w359380463-400</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
     <t>elc_won_065</t>
   </si>
   <si>
@@ -2269,148 +2413,52 @@
     <t>elc_won_029</t>
   </si>
   <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w377716686-400,e_w173670759-400,e_DZ13-400,e_DZ2-400</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_DZ71-400,e_DZ63-400,e_w694011250-400,e_w694011253-400,e_w176932220-400,e_w176932212-400,e_DZ1-400,e_w177004931-400,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>elc_won_057</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_DZ113-400,e_w173677993-400,e_w635672953-400,e_DZ87-400,e_DZ66-400,e_DZ65-400</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_DZ134-400,e_DZ113-400,e_w173682343-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>elc_won_048</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>elc_won_056</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w173677993-400,e_w173682343-400,e_w635672953-400,e_w359380463-400,e_DZ87-400,e_w574859222-400</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w574859222-400,e_DZ67-400,e_w377716686-400,e_w610844609-400,e_DZ50-400,e_DZ72-400,e_w221085150-400</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_DZ71-400,e_w226392269-400,e_DZ63-400,e_w694000747-400,e_w174512286-400</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_w380271836-400,e_w383754584-400,e_DZ135-400,e_DZ139-400</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>elc_won_063</t>
-  </si>
-  <si>
-    <t>e_w833562295-400,e_w380271836-400,e_w610844609-400</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>elc_won_050</t>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_003</t>
@@ -2419,58 +2467,58 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w173670759-400,e_DZ13-400</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_DZ96-400,e_DZ87-400</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_DZ113-400</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w176932220-400</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_DZ113-400,e_w173677993-400</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w635672953-400</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_DZ66-400,e_w377716686-400</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_DZ1-400,e_DZ45-400</t>
   </si>
   <si>
     <t>elc_wof_003</t>
@@ -2479,58 +2527,10 @@
     <t>e_w694011250-400,e_w694011253-400</t>
   </si>
   <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_DZ96-400,e_DZ87-400</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w176932220-400</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w173670759-400,e_DZ13-400</t>
-  </si>
-  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
     <t>e_DZ134-400,e_DZ113-400</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_DZ66-400,e_w377716686-400</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_DZ1-400,e_DZ45-400</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_DZ113-400</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_DZ113-400,e_w173677993-400</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w635672953-400</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7911,7 +7911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C2755B-AED3-4D18-8735-F0117FA6E6E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D610ECA6-6D84-4D37-AE1D-6CEDAF7354D1}">
   <dimension ref="B9:BD75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8188,13 +8188,13 @@
         <v>682</v>
       </c>
       <c r="AN11" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="AO11">
-        <v>0.94955837899358098</v>
+        <v>0.94051622946940883</v>
       </c>
       <c r="AP11">
-        <v>924.76305178434825</v>
+        <v>1090.5357930608377</v>
       </c>
       <c r="AR11" t="s">
         <v>384</v>
@@ -8227,10 +8227,10 @@
         <v>782</v>
       </c>
       <c r="BC11">
-        <v>0.99666833031040181</v>
+        <v>0.99821376186130728</v>
       </c>
       <c r="BD11">
-        <v>61.080610975966621</v>
+        <v>32.747699209366665</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -8334,13 +8334,13 @@
         <v>683</v>
       </c>
       <c r="AN12" t="s">
-        <v>684</v>
+        <v>529</v>
       </c>
       <c r="AO12">
-        <v>0.99579421566997561</v>
+        <v>0.98834980855783927</v>
       </c>
       <c r="AP12">
-        <v>77.106046050446551</v>
+        <v>213.58684310628055</v>
       </c>
       <c r="AR12" t="s">
         <v>384</v>
@@ -8477,16 +8477,16 @@
         <v>556</v>
       </c>
       <c r="AM13" t="s">
+        <v>684</v>
+      </c>
+      <c r="AN13" t="s">
         <v>685</v>
       </c>
-      <c r="AN13" t="s">
-        <v>686</v>
-      </c>
       <c r="AO13">
-        <v>0.99739859158838851</v>
+        <v>0.99676169282936067</v>
       </c>
       <c r="AP13">
-        <v>47.692487546211247</v>
+        <v>59.368964795055021</v>
       </c>
       <c r="AR13" t="s">
         <v>384</v>
@@ -8519,10 +8519,10 @@
         <v>786</v>
       </c>
       <c r="BC13">
-        <v>0.99725890076894208</v>
+        <v>0.99453288259674533</v>
       </c>
       <c r="BD13">
-        <v>50.253485902728066</v>
+        <v>100.23048572633493</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8623,16 +8623,16 @@
         <v>558</v>
       </c>
       <c r="AM14" t="s">
+        <v>686</v>
+      </c>
+      <c r="AN14" t="s">
         <v>687</v>
       </c>
-      <c r="AN14" t="s">
-        <v>528</v>
-      </c>
       <c r="AO14">
-        <v>0.9412405456309284</v>
+        <v>0.99755473811457307</v>
       </c>
       <c r="AP14">
-        <v>1077.2566634329794</v>
+        <v>44.829801232827165</v>
       </c>
       <c r="AR14" t="s">
         <v>384</v>
@@ -8665,10 +8665,10 @@
         <v>788</v>
       </c>
       <c r="BC14">
-        <v>0.99821376186130728</v>
+        <v>0.99725890076894208</v>
       </c>
       <c r="BD14">
-        <v>32.747699209366665</v>
+        <v>50.253485902728066</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8772,13 +8772,13 @@
         <v>688</v>
       </c>
       <c r="AN15" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AO15">
-        <v>0.97032680215300582</v>
+        <v>0.98113402979335829</v>
       </c>
       <c r="AP15">
-        <v>544.00862719489396</v>
+        <v>345.87612045509712</v>
       </c>
       <c r="AR15" t="s">
         <v>384</v>
@@ -8811,10 +8811,10 @@
         <v>790</v>
       </c>
       <c r="BC15">
-        <v>0.99559373373679849</v>
+        <v>0.99768114994705415</v>
       </c>
       <c r="BD15">
-        <v>80.781548158693312</v>
+        <v>42.512250970673364</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8918,13 +8918,13 @@
         <v>689</v>
       </c>
       <c r="AN16" t="s">
-        <v>520</v>
+        <v>690</v>
       </c>
       <c r="AO16">
-        <v>0.94676925034254755</v>
+        <v>0.99814486453404194</v>
       </c>
       <c r="AP16">
-        <v>975.89707705329522</v>
+        <v>34.010816875898144</v>
       </c>
       <c r="AR16" t="s">
         <v>384</v>
@@ -8957,10 +8957,10 @@
         <v>792</v>
       </c>
       <c r="BC16">
-        <v>0.99752072397310498</v>
+        <v>0.99945793152703599</v>
       </c>
       <c r="BD16">
-        <v>45.453393826407655</v>
+        <v>9.9379220043409635</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -9025,16 +9025,16 @@
         <v>399</v>
       </c>
       <c r="Y17" t="s">
-        <v>327</v>
+        <v>373</v>
       </c>
       <c r="Z17" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="AA17">
-        <v>0.99785225350862616</v>
+        <v>0.95092084901325236</v>
       </c>
       <c r="AB17">
-        <v>39.375352341852881</v>
+        <v>899.78443475704057</v>
       </c>
       <c r="AD17" t="s">
         <v>384</v>
@@ -9061,16 +9061,16 @@
         <v>564</v>
       </c>
       <c r="AM17" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AN17" t="s">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="AO17">
-        <v>0.97192734479279941</v>
+        <v>0.95891366758494356</v>
       </c>
       <c r="AP17">
-        <v>514.66534546534479</v>
+        <v>753.24942760936881</v>
       </c>
       <c r="AR17" t="s">
         <v>384</v>
@@ -9103,10 +9103,10 @@
         <v>794</v>
       </c>
       <c r="BC17">
-        <v>0.99638760888775468</v>
+        <v>0.99752072397310498</v>
       </c>
       <c r="BD17">
-        <v>66.227170391164663</v>
+        <v>45.453393826407655</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -9171,16 +9171,16 @@
         <v>401</v>
       </c>
       <c r="Y18" t="s">
-        <v>319</v>
+        <v>368</v>
       </c>
       <c r="Z18" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AA18">
-        <v>0.99456724695264065</v>
+        <v>0.95627852682955183</v>
       </c>
       <c r="AB18">
-        <v>99.600472534921394</v>
+        <v>801.56034145821604</v>
       </c>
       <c r="AD18" t="s">
         <v>384</v>
@@ -9207,16 +9207,16 @@
         <v>566</v>
       </c>
       <c r="AM18" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AN18" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="AO18">
-        <v>0.95187717828011942</v>
+        <v>0.94448964125191193</v>
       </c>
       <c r="AP18">
-        <v>882.25173153114304</v>
+        <v>1017.6899103816154</v>
       </c>
       <c r="AR18" t="s">
         <v>384</v>
@@ -9249,10 +9249,10 @@
         <v>796</v>
       </c>
       <c r="BC18">
-        <v>0.99453288259674533</v>
+        <v>0.99638760888775468</v>
       </c>
       <c r="BD18">
-        <v>100.23048572633493</v>
+        <v>66.227170391164663</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -9317,16 +9317,16 @@
         <v>403</v>
       </c>
       <c r="Y19" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="Z19" t="s">
         <v>520</v>
       </c>
       <c r="AA19">
-        <v>0.97910521725056054</v>
+        <v>0.964394360083076</v>
       </c>
       <c r="AB19">
-        <v>383.071017073056</v>
+        <v>652.77006514360744</v>
       </c>
       <c r="AD19" t="s">
         <v>384</v>
@@ -9353,16 +9353,16 @@
         <v>568</v>
       </c>
       <c r="AM19" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AN19" t="s">
         <v>520</v>
       </c>
       <c r="AO19">
-        <v>0.93123908610256811</v>
+        <v>0.98249899662312545</v>
       </c>
       <c r="AP19">
-        <v>1260.6167547862519</v>
+        <v>320.85172857603243</v>
       </c>
       <c r="AR19" t="s">
         <v>384</v>
@@ -9395,10 +9395,10 @@
         <v>798</v>
       </c>
       <c r="BC19">
-        <v>0.99768114994705415</v>
+        <v>0.99666833031040181</v>
       </c>
       <c r="BD19">
-        <v>42.512250970673364</v>
+        <v>61.080610975966621</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9463,16 +9463,16 @@
         <v>405</v>
       </c>
       <c r="Y20" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="Z20" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AA20">
-        <v>0.99774906718813006</v>
+        <v>0.98397547854041056</v>
       </c>
       <c r="AB20">
-        <v>41.267101550949633</v>
+        <v>293.78289342580621</v>
       </c>
       <c r="AD20" t="s">
         <v>384</v>
@@ -9499,16 +9499,16 @@
         <v>570</v>
       </c>
       <c r="AM20" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN20" t="s">
         <v>523</v>
       </c>
       <c r="AO20">
-        <v>0.99329510561532575</v>
+        <v>0.9822063405637812</v>
       </c>
       <c r="AP20">
-        <v>122.92306371902798</v>
+        <v>326.21708966401127</v>
       </c>
       <c r="AR20" t="s">
         <v>384</v>
@@ -9541,10 +9541,10 @@
         <v>800</v>
       </c>
       <c r="BC20">
-        <v>0.99945793152703599</v>
+        <v>0.99559373373679849</v>
       </c>
       <c r="BD20">
-        <v>9.9379220043409635</v>
+        <v>80.781548158693312</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9609,16 +9609,16 @@
         <v>407</v>
       </c>
       <c r="Y21" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="Z21" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AA21">
-        <v>0.97425429819147469</v>
+        <v>0.93395005189428693</v>
       </c>
       <c r="AB21">
-        <v>472.00453315629693</v>
+        <v>1210.915715271407</v>
       </c>
       <c r="AD21" t="s">
         <v>384</v>
@@ -9645,16 +9645,16 @@
         <v>572</v>
       </c>
       <c r="AM21" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AN21" t="s">
-        <v>695</v>
+        <v>520</v>
       </c>
       <c r="AO21">
-        <v>0.99676023225274279</v>
+        <v>0.93123908610256811</v>
       </c>
       <c r="AP21">
-        <v>59.39574203304835</v>
+        <v>1260.6167547862519</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9719,16 +9719,16 @@
         <v>409</v>
       </c>
       <c r="Y22" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="Z22" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AA22">
-        <v>0.96180069092062781</v>
+        <v>0.9946704540941137</v>
       </c>
       <c r="AB22">
-        <v>700.32066645515795</v>
+        <v>97.708341607915628</v>
       </c>
       <c r="AD22" t="s">
         <v>384</v>
@@ -9758,13 +9758,13 @@
         <v>696</v>
       </c>
       <c r="AN22" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AO22">
-        <v>0.95083546532803764</v>
+        <v>0.99329510561532575</v>
       </c>
       <c r="AP22">
-        <v>901.3498023193107</v>
+        <v>122.92306371902798</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9829,16 +9829,16 @@
         <v>411</v>
       </c>
       <c r="Y23" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="Z23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AA23">
-        <v>0.97274751764992162</v>
+        <v>0.99392929419831677</v>
       </c>
       <c r="AB23">
-        <v>499.6288430847701</v>
+        <v>111.29627303086014</v>
       </c>
       <c r="AD23" t="s">
         <v>384</v>
@@ -9868,13 +9868,13 @@
         <v>697</v>
       </c>
       <c r="AN23" t="s">
-        <v>521</v>
+        <v>698</v>
       </c>
       <c r="AO23">
-        <v>0.95998246085996786</v>
+        <v>0.99676023225274279</v>
       </c>
       <c r="AP23">
-        <v>733.65488423392264</v>
+        <v>59.39574203304835</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9939,16 +9939,16 @@
         <v>413</v>
       </c>
       <c r="Y24" t="s">
-        <v>325</v>
+        <v>378</v>
       </c>
       <c r="Z24" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="AA24">
-        <v>0.9900739715800958</v>
+        <v>0.99241046515009568</v>
       </c>
       <c r="AB24">
-        <v>181.9771876982428</v>
+        <v>139.14147224824609</v>
       </c>
       <c r="AD24" t="s">
         <v>384</v>
@@ -9975,16 +9975,16 @@
         <v>578</v>
       </c>
       <c r="AM24" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AN24" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AO24">
-        <v>0.97867072425191259</v>
+        <v>0.95083546532803764</v>
       </c>
       <c r="AP24">
-        <v>391.03672204826887</v>
+        <v>901.3498023193107</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -10049,16 +10049,16 @@
         <v>415</v>
       </c>
       <c r="Y25" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="Z25" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AA25">
-        <v>0.96390615299028259</v>
+        <v>0.99695853185056948</v>
       </c>
       <c r="AB25">
-        <v>661.7205285114859</v>
+        <v>55.760249406226841</v>
       </c>
       <c r="AD25" t="s">
         <v>384</v>
@@ -10085,16 +10085,16 @@
         <v>580</v>
       </c>
       <c r="AM25" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AN25" t="s">
-        <v>520</v>
+        <v>701</v>
       </c>
       <c r="AO25">
-        <v>0.94830795758953823</v>
+        <v>0.99358556749518001</v>
       </c>
       <c r="AP25">
-        <v>947.68744419179825</v>
+        <v>117.59792925503248</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -10159,16 +10159,16 @@
         <v>417</v>
       </c>
       <c r="Y26" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Z26" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA26">
-        <v>0.9445225305044197</v>
+        <v>0.94751402221263747</v>
       </c>
       <c r="AB26">
-        <v>1017.0869407523058</v>
+        <v>962.2429261016473</v>
       </c>
       <c r="AD26" t="s">
         <v>384</v>
@@ -10195,16 +10195,16 @@
         <v>582</v>
       </c>
       <c r="AM26" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AN26" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AO26">
-        <v>0.96608967222173958</v>
+        <v>0.95872311541153676</v>
       </c>
       <c r="AP26">
-        <v>621.68934260143999</v>
+        <v>756.74288412182625</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10269,16 +10269,16 @@
         <v>419</v>
       </c>
       <c r="Y27" t="s">
-        <v>381</v>
+        <v>326</v>
       </c>
       <c r="Z27" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="AA27">
-        <v>0.98504860509376779</v>
+        <v>0.99312250672874891</v>
       </c>
       <c r="AB27">
-        <v>274.10890661425793</v>
+        <v>126.08737663960262</v>
       </c>
       <c r="AD27" t="s">
         <v>384</v>
@@ -10305,16 +10305,16 @@
         <v>584</v>
       </c>
       <c r="AM27" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AN27" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AO27">
-        <v>0.99019817387948927</v>
+        <v>0.96608967222173958</v>
       </c>
       <c r="AP27">
-        <v>179.70014554269721</v>
+        <v>621.68934260143999</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10379,16 +10379,16 @@
         <v>421</v>
       </c>
       <c r="Y28" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="Z28" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AA28">
-        <v>0.99519548170790972</v>
+        <v>0.99802219450699958</v>
       </c>
       <c r="AB28">
-        <v>88.082835354989243</v>
+        <v>36.259767371674911</v>
       </c>
       <c r="AD28" t="s">
         <v>384</v>
@@ -10415,16 +10415,16 @@
         <v>586</v>
       </c>
       <c r="AM28" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AN28" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="AO28">
-        <v>0.97044979723130242</v>
+        <v>0.99019817387948927</v>
       </c>
       <c r="AP28">
-        <v>541.75371742612197</v>
+        <v>179.70014554269721</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10489,16 +10489,16 @@
         <v>423</v>
       </c>
       <c r="Y29" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="Z29" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="AA29">
-        <v>0.93331654548075482</v>
+        <v>0.99249810310312347</v>
       </c>
       <c r="AB29">
-        <v>1222.529999519496</v>
+        <v>137.53477644273678</v>
       </c>
       <c r="AD29" t="s">
         <v>384</v>
@@ -10525,16 +10525,16 @@
         <v>588</v>
       </c>
       <c r="AM29" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AN29" t="s">
-        <v>704</v>
+        <v>521</v>
       </c>
       <c r="AO29">
-        <v>0.99448677280644449</v>
+        <v>0.94955837899358098</v>
       </c>
       <c r="AP29">
-        <v>101.07583188185161</v>
+        <v>924.76305178434825</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10599,16 +10599,16 @@
         <v>425</v>
       </c>
       <c r="Y30" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="Z30" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AA30">
-        <v>0.98351827395448832</v>
+        <v>0.91924480775997031</v>
       </c>
       <c r="AB30">
-        <v>302.16497750104838</v>
+        <v>1480.5118577338778</v>
       </c>
       <c r="AD30" t="s">
         <v>384</v>
@@ -10635,16 +10635,16 @@
         <v>590</v>
       </c>
       <c r="AM30" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AN30" t="s">
-        <v>540</v>
+        <v>707</v>
       </c>
       <c r="AO30">
-        <v>0.96658550487633221</v>
+        <v>0.99579421566997561</v>
       </c>
       <c r="AP30">
-        <v>612.59907726724202</v>
+        <v>77.106046050446551</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10709,16 +10709,16 @@
         <v>427</v>
       </c>
       <c r="Y31" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="Z31" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AA31">
-        <v>0.99531334834867624</v>
+        <v>0.99775535618327416</v>
       </c>
       <c r="AB31">
-        <v>85.921946940936536</v>
+        <v>41.151803306639543</v>
       </c>
       <c r="AD31" t="s">
         <v>384</v>
@@ -10745,16 +10745,16 @@
         <v>592</v>
       </c>
       <c r="AM31" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AN31" t="s">
-        <v>520</v>
+        <v>709</v>
       </c>
       <c r="AO31">
-        <v>0.93082939136036824</v>
+        <v>0.99739859158838851</v>
       </c>
       <c r="AP31">
-        <v>1268.1278250599159</v>
+        <v>47.692487546211247</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10819,16 +10819,16 @@
         <v>429</v>
       </c>
       <c r="Y32" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="Z32" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AA32">
-        <v>0.99169894704281958</v>
+        <v>0.97863416508473733</v>
       </c>
       <c r="AB32">
-        <v>152.18597088164097</v>
+        <v>391.70697344648261</v>
       </c>
       <c r="AD32" t="s">
         <v>384</v>
@@ -10855,16 +10855,16 @@
         <v>594</v>
       </c>
       <c r="AM32" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AN32" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="AO32">
-        <v>0.92249590599073328</v>
+        <v>0.97044979723130242</v>
       </c>
       <c r="AP32">
-        <v>1420.90839016989</v>
+        <v>541.75371742612197</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10929,16 +10929,16 @@
         <v>431</v>
       </c>
       <c r="Y33" t="s">
-        <v>377</v>
+        <v>323</v>
       </c>
       <c r="Z33" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="AA33">
-        <v>0.99247786079412359</v>
+        <v>0.99515568903735085</v>
       </c>
       <c r="AB33">
-        <v>137.90588544106748</v>
+        <v>88.812367648567218</v>
       </c>
       <c r="AD33" t="s">
         <v>384</v>
@@ -10965,16 +10965,16 @@
         <v>596</v>
       </c>
       <c r="AM33" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AN33" t="s">
-        <v>520</v>
+        <v>712</v>
       </c>
       <c r="AO33">
-        <v>0.9481926147139631</v>
+        <v>0.99448677280644449</v>
       </c>
       <c r="AP33">
-        <v>949.80206357734346</v>
+        <v>101.07583188185161</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -11039,16 +11039,16 @@
         <v>433</v>
       </c>
       <c r="Y34" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="Z34" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AA34">
-        <v>0.94751402221263747</v>
+        <v>0.92686643973261318</v>
       </c>
       <c r="AB34">
-        <v>962.2429261016473</v>
+        <v>1340.7819382354255</v>
       </c>
       <c r="AD34" t="s">
         <v>384</v>
@@ -11075,16 +11075,16 @@
         <v>598</v>
       </c>
       <c r="AM34" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AN34" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="AO34">
-        <v>0.96013290362495074</v>
+        <v>0.96658550487633221</v>
       </c>
       <c r="AP34">
-        <v>730.89676687590281</v>
+        <v>612.59907726724202</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11149,16 +11149,16 @@
         <v>435</v>
       </c>
       <c r="Y35" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="Z35" t="s">
         <v>534</v>
       </c>
       <c r="AA35">
-        <v>0.99312250672874891</v>
+        <v>0.99456659992729313</v>
       </c>
       <c r="AB35">
-        <v>126.08737663960262</v>
+        <v>99.61233466629254</v>
       </c>
       <c r="AD35" t="s">
         <v>384</v>
@@ -11185,16 +11185,16 @@
         <v>600</v>
       </c>
       <c r="AM35" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AN35" t="s">
-        <v>711</v>
+        <v>520</v>
       </c>
       <c r="AO35">
-        <v>0.99431725858154596</v>
+        <v>0.93082939136036824</v>
       </c>
       <c r="AP35">
-        <v>104.18359267165788</v>
+        <v>1268.1278250599159</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11259,16 +11259,16 @@
         <v>437</v>
       </c>
       <c r="Y36" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="Z36" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="AA36">
-        <v>0.99802219450699958</v>
+        <v>0.93141537592166213</v>
       </c>
       <c r="AB36">
-        <v>36.259767371674911</v>
+        <v>1257.384774769527</v>
       </c>
       <c r="AD36" t="s">
         <v>384</v>
@@ -11295,16 +11295,16 @@
         <v>602</v>
       </c>
       <c r="AM36" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="AN36" t="s">
         <v>520</v>
       </c>
       <c r="AO36">
-        <v>0.93434249421812909</v>
+        <v>0.92249590599073328</v>
       </c>
       <c r="AP36">
-        <v>1203.7209393342998</v>
+        <v>1420.90839016989</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11369,16 +11369,16 @@
         <v>439</v>
       </c>
       <c r="Y37" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="Z37" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AA37">
-        <v>0.99249810310312347</v>
+        <v>0.94240538704132404</v>
       </c>
       <c r="AB37">
-        <v>137.53477644273678</v>
+        <v>1055.9012375757261</v>
       </c>
       <c r="AD37" t="s">
         <v>384</v>
@@ -11405,16 +11405,16 @@
         <v>604</v>
       </c>
       <c r="AM37" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="AN37" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="AO37">
-        <v>0.94051622946940883</v>
+        <v>0.9481926147139631</v>
       </c>
       <c r="AP37">
-        <v>1090.5357930608377</v>
+        <v>949.80206357734346</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11479,16 +11479,16 @@
         <v>441</v>
       </c>
       <c r="Y38" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="Z38" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AA38">
-        <v>0.91924480775997031</v>
+        <v>0.93407383455905413</v>
       </c>
       <c r="AB38">
-        <v>1480.5118577338778</v>
+        <v>1208.6463664173409</v>
       </c>
       <c r="AD38" t="s">
         <v>384</v>
@@ -11515,16 +11515,16 @@
         <v>606</v>
       </c>
       <c r="AM38" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="AN38" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="AO38">
-        <v>0.98834980855783927</v>
+        <v>0.96013290362495074</v>
       </c>
       <c r="AP38">
-        <v>213.58684310628055</v>
+        <v>730.89676687590281</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11589,16 +11589,16 @@
         <v>443</v>
       </c>
       <c r="Y39" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="Z39" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AA39">
-        <v>0.99775535618327416</v>
+        <v>0.98933589132254729</v>
       </c>
       <c r="AB39">
-        <v>41.151803306639543</v>
+        <v>195.50865908663351</v>
       </c>
       <c r="AD39" t="s">
         <v>384</v>
@@ -11625,16 +11625,16 @@
         <v>608</v>
       </c>
       <c r="AM39" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="AN39" t="s">
-        <v>716</v>
+        <v>529</v>
       </c>
       <c r="AO39">
-        <v>0.99676169282936067</v>
+        <v>0.95187717828011942</v>
       </c>
       <c r="AP39">
-        <v>59.368964795055021</v>
+        <v>882.25173153114304</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11699,16 +11699,16 @@
         <v>445</v>
       </c>
       <c r="Y40" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="Z40" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AA40">
-        <v>0.94240538704132404</v>
+        <v>0.97274011289298934</v>
       </c>
       <c r="AB40">
-        <v>1055.9012375757261</v>
+        <v>499.76459696186282</v>
       </c>
       <c r="AD40" t="s">
         <v>384</v>
@@ -11735,16 +11735,16 @@
         <v>610</v>
       </c>
       <c r="AM40" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AN40" t="s">
-        <v>718</v>
+        <v>529</v>
       </c>
       <c r="AO40">
-        <v>0.99755473811457307</v>
+        <v>0.98080213304783737</v>
       </c>
       <c r="AP40">
-        <v>44.829801232827165</v>
+        <v>351.96089412298221</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11809,16 +11809,16 @@
         <v>447</v>
       </c>
       <c r="Y41" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="Z41" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="AA41">
-        <v>0.93407383455905413</v>
+        <v>0.97636932039261881</v>
       </c>
       <c r="AB41">
-        <v>1208.6463664173409</v>
+        <v>433.22912613532151</v>
       </c>
       <c r="AD41" t="s">
         <v>384</v>
@@ -11845,16 +11845,16 @@
         <v>612</v>
       </c>
       <c r="AM41" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AN41" t="s">
-        <v>527</v>
+        <v>721</v>
       </c>
       <c r="AO41">
-        <v>0.98113402979335829</v>
+        <v>0.9926254342737908</v>
       </c>
       <c r="AP41">
-        <v>345.87612045509712</v>
+        <v>135.20037164716879</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11919,16 +11919,16 @@
         <v>449</v>
       </c>
       <c r="Y42" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="Z42" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AA42">
-        <v>0.98933589132254729</v>
+        <v>0.99568560858856903</v>
       </c>
       <c r="AB42">
-        <v>195.50865908663351</v>
+        <v>79.097175876234388</v>
       </c>
       <c r="AD42" t="s">
         <v>384</v>
@@ -11955,16 +11955,16 @@
         <v>614</v>
       </c>
       <c r="AM42" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AN42" t="s">
-        <v>721</v>
+        <v>520</v>
       </c>
       <c r="AO42">
-        <v>0.99814486453404194</v>
+        <v>0.922364240170786</v>
       </c>
       <c r="AP42">
-        <v>34.010816875898144</v>
+        <v>1423.3222635355901</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -12029,16 +12029,16 @@
         <v>451</v>
       </c>
       <c r="Y43" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="Z43" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AA43">
-        <v>0.97274011289298934</v>
+        <v>0.99708131753222806</v>
       </c>
       <c r="AB43">
-        <v>499.76459696186282</v>
+        <v>53.509178575819661</v>
       </c>
       <c r="AD43" t="s">
         <v>384</v>
@@ -12065,16 +12065,16 @@
         <v>616</v>
       </c>
       <c r="AM43" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AN43" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AO43">
-        <v>0.95891366758494356</v>
+        <v>0.96559203855369335</v>
       </c>
       <c r="AP43">
-        <v>753.24942760936881</v>
+        <v>630.81262651562236</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12139,16 +12139,16 @@
         <v>453</v>
       </c>
       <c r="Y44" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Z44" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="AA44">
-        <v>0.97636932039261881</v>
+        <v>0.98164032362202902</v>
       </c>
       <c r="AB44">
-        <v>433.22912613532151</v>
+        <v>336.5940669294684</v>
       </c>
       <c r="AD44" t="s">
         <v>384</v>
@@ -12175,16 +12175,16 @@
         <v>618</v>
       </c>
       <c r="AM44" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AN44" t="s">
         <v>520</v>
       </c>
       <c r="AO44">
-        <v>0.94448964125191193</v>
+        <v>0.93218357774037441</v>
       </c>
       <c r="AP44">
-        <v>1017.6899103816154</v>
+        <v>1243.3010747598034</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12249,16 +12249,16 @@
         <v>455</v>
       </c>
       <c r="Y45" t="s">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="Z45" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="AA45">
-        <v>0.99568560858856903</v>
+        <v>0.96506973637135485</v>
       </c>
       <c r="AB45">
-        <v>79.097175876234388</v>
+        <v>640.38816652516039</v>
       </c>
       <c r="AD45" t="s">
         <v>384</v>
@@ -12285,16 +12285,16 @@
         <v>620</v>
       </c>
       <c r="AM45" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AN45" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AO45">
-        <v>0.98249899662312545</v>
+        <v>0.9395409140459815</v>
       </c>
       <c r="AP45">
-        <v>320.85172857603243</v>
+        <v>1108.4165758236729</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12359,16 +12359,16 @@
         <v>457</v>
       </c>
       <c r="Y46" t="s">
-        <v>373</v>
+        <v>331</v>
       </c>
       <c r="Z46" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="AA46">
-        <v>0.95092084901325236</v>
+        <v>0.99767908816061546</v>
       </c>
       <c r="AB46">
-        <v>899.78443475704057</v>
+        <v>42.550050388717629</v>
       </c>
       <c r="AD46" t="s">
         <v>384</v>
@@ -12395,16 +12395,16 @@
         <v>622</v>
       </c>
       <c r="AM46" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AN46" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO46">
-        <v>0.9822063405637812</v>
+        <v>0.93887576571402298</v>
       </c>
       <c r="AP46">
-        <v>326.21708966401127</v>
+        <v>1120.6109619095782</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12469,16 +12469,16 @@
         <v>459</v>
       </c>
       <c r="Y47" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Z47" t="s">
         <v>520</v>
       </c>
       <c r="AA47">
-        <v>0.95627852682955183</v>
+        <v>0.94624539205794911</v>
       </c>
       <c r="AB47">
-        <v>801.56034145821604</v>
+        <v>985.50114560426641</v>
       </c>
       <c r="AD47" t="s">
         <v>384</v>
@@ -12505,16 +12505,16 @@
         <v>624</v>
       </c>
       <c r="AM47" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AN47" t="s">
-        <v>727</v>
+        <v>550</v>
       </c>
       <c r="AO47">
-        <v>0.99732941880385861</v>
+        <v>0.99217580400103222</v>
       </c>
       <c r="AP47">
-        <v>48.960655262591807</v>
+        <v>143.44359331440998</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12579,16 +12579,16 @@
         <v>461</v>
       </c>
       <c r="Y48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Z48" t="s">
         <v>520</v>
       </c>
       <c r="AA48">
-        <v>0.964394360083076</v>
+        <v>0.93866072843058268</v>
       </c>
       <c r="AB48">
-        <v>652.77006514360744</v>
+        <v>1124.553312105985</v>
       </c>
       <c r="AD48" t="s">
         <v>384</v>
@@ -12621,10 +12621,10 @@
         <v>520</v>
       </c>
       <c r="AO48">
-        <v>0.94147347395757119</v>
+        <v>0.97345977228128666</v>
       </c>
       <c r="AP48">
-        <v>1072.9863107778624</v>
+        <v>486.57084150974435</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12689,16 +12689,16 @@
         <v>463</v>
       </c>
       <c r="Y49" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Z49" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="AA49">
-        <v>0.95701836677838237</v>
+        <v>0.94416692065916552</v>
       </c>
       <c r="AB49">
-        <v>787.99660906299084</v>
+        <v>1023.6064545819663</v>
       </c>
       <c r="AD49" t="s">
         <v>384</v>
@@ -12728,13 +12728,13 @@
         <v>729</v>
       </c>
       <c r="AN49" t="s">
-        <v>520</v>
+        <v>730</v>
       </c>
       <c r="AO49">
-        <v>0.94081699807033814</v>
+        <v>0.99732941880385861</v>
       </c>
       <c r="AP49">
-        <v>1085.0217020438001</v>
+        <v>48.960655262591807</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12799,16 +12799,16 @@
         <v>465</v>
       </c>
       <c r="Y50" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Z50" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="AA50">
-        <v>0.94701516843854283</v>
+        <v>0.96887884140791136</v>
       </c>
       <c r="AB50">
-        <v>971.38857862671478</v>
+        <v>570.55457418829201</v>
       </c>
       <c r="AD50" t="s">
         <v>384</v>
@@ -12835,16 +12835,16 @@
         <v>630</v>
       </c>
       <c r="AM50" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AN50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AO50">
-        <v>0.9395409140459815</v>
+        <v>0.94147347395757119</v>
       </c>
       <c r="AP50">
-        <v>1108.4165758236729</v>
+        <v>1072.9863107778624</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12909,16 +12909,16 @@
         <v>467</v>
       </c>
       <c r="Y51" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="Z51" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA51">
-        <v>0.94416692065916552</v>
+        <v>0.9553697829070843</v>
       </c>
       <c r="AB51">
-        <v>1023.6064545819663</v>
+        <v>818.22064670345389</v>
       </c>
       <c r="AD51" t="s">
         <v>384</v>
@@ -12945,16 +12945,16 @@
         <v>632</v>
       </c>
       <c r="AM51" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AN51" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AO51">
-        <v>0.93887576571402298</v>
+        <v>0.94081699807033814</v>
       </c>
       <c r="AP51">
-        <v>1120.6109619095782</v>
+        <v>1085.0217020438001</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13019,16 +13019,16 @@
         <v>469</v>
       </c>
       <c r="Y52" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="Z52" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AA52">
-        <v>0.96887884140791136</v>
+        <v>0.99796046238026981</v>
       </c>
       <c r="AB52">
-        <v>570.55457418829201</v>
+        <v>37.39152302838729</v>
       </c>
       <c r="AD52" t="s">
         <v>384</v>
@@ -13055,16 +13055,16 @@
         <v>634</v>
       </c>
       <c r="AM52" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AN52" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AO52">
-        <v>0.99217580400103222</v>
+        <v>0.95152414227022919</v>
       </c>
       <c r="AP52">
-        <v>143.44359331440998</v>
+        <v>888.72405837913129</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13129,16 +13129,16 @@
         <v>471</v>
       </c>
       <c r="Y53" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="Z53" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="AA53">
-        <v>0.9553697829070843</v>
+        <v>0.99588899978911039</v>
       </c>
       <c r="AB53">
-        <v>818.22064670345389</v>
+        <v>75.368337199642838</v>
       </c>
       <c r="AD53" t="s">
         <v>384</v>
@@ -13165,16 +13165,16 @@
         <v>636</v>
       </c>
       <c r="AM53" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AN53" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO53">
-        <v>0.97345977228128666</v>
+        <v>0.95404010460315924</v>
       </c>
       <c r="AP53">
-        <v>486.57084150974435</v>
+        <v>842.59808227541362</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13239,16 +13239,16 @@
         <v>473</v>
       </c>
       <c r="Y54" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="Z54" t="s">
         <v>542</v>
       </c>
       <c r="AA54">
-        <v>0.99796046238026981</v>
+        <v>0.99785225350862616</v>
       </c>
       <c r="AB54">
-        <v>37.39152302838729</v>
+        <v>39.375352341852881</v>
       </c>
       <c r="AD54" t="s">
         <v>384</v>
@@ -13275,16 +13275,16 @@
         <v>638</v>
       </c>
       <c r="AM54" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AN54" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="AO54">
-        <v>0.93780897896633364</v>
+        <v>0.92828711808630038</v>
       </c>
       <c r="AP54">
-        <v>1140.1687189505506</v>
+        <v>1314.7361684178261</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13349,16 +13349,16 @@
         <v>475</v>
       </c>
       <c r="Y55" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="Z55" t="s">
         <v>543</v>
       </c>
       <c r="AA55">
-        <v>0.99588899978911039</v>
+        <v>0.99456724695264065</v>
       </c>
       <c r="AB55">
-        <v>75.368337199642838</v>
+        <v>99.600472534921394</v>
       </c>
       <c r="AD55" t="s">
         <v>384</v>
@@ -13385,16 +13385,16 @@
         <v>640</v>
       </c>
       <c r="AM55" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AN55" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AO55">
-        <v>0.99188597448157934</v>
+        <v>0.99154375423443009</v>
       </c>
       <c r="AP55">
-        <v>148.75713450437817</v>
+        <v>155.03117236878097</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -13459,16 +13459,16 @@
         <v>477</v>
       </c>
       <c r="Y56" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="Z56" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="AA56">
-        <v>0.97863416508473733</v>
+        <v>0.97910521725056054</v>
       </c>
       <c r="AB56">
-        <v>391.70697344648261</v>
+        <v>383.071017073056</v>
       </c>
       <c r="AD56" t="s">
         <v>384</v>
@@ -13495,16 +13495,16 @@
         <v>642</v>
       </c>
       <c r="AM56" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AN56" t="s">
-        <v>737</v>
+        <v>520</v>
       </c>
       <c r="AO56">
-        <v>0.99696250898544003</v>
+        <v>0.9654653203800333</v>
       </c>
       <c r="AP56">
-        <v>55.687335266933502</v>
+        <v>633.13579303272206</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -13569,16 +13569,16 @@
         <v>479</v>
       </c>
       <c r="Y57" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="Z57" t="s">
         <v>544</v>
       </c>
       <c r="AA57">
-        <v>0.99515568903735085</v>
+        <v>0.99774906718813006</v>
       </c>
       <c r="AB57">
-        <v>88.812367648567218</v>
+        <v>41.267101550949633</v>
       </c>
       <c r="AD57" t="s">
         <v>384</v>
@@ -13608,13 +13608,13 @@
         <v>738</v>
       </c>
       <c r="AN57" t="s">
-        <v>739</v>
+        <v>521</v>
       </c>
       <c r="AO57">
-        <v>0.99732604522700541</v>
+        <v>0.95998246085996786</v>
       </c>
       <c r="AP57">
-        <v>49.02250417156759</v>
+        <v>733.65488423392264</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -13679,16 +13679,16 @@
         <v>481</v>
       </c>
       <c r="Y58" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="Z58" t="s">
         <v>520</v>
       </c>
       <c r="AA58">
-        <v>0.92686643973261318</v>
+        <v>0.97425429819147469</v>
       </c>
       <c r="AB58">
-        <v>1340.7819382354255</v>
+        <v>472.00453315629693</v>
       </c>
       <c r="AD58" t="s">
         <v>384</v>
@@ -13715,16 +13715,16 @@
         <v>646</v>
       </c>
       <c r="AM58" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AN58" t="s">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="AO58">
-        <v>0.92030235471623756</v>
+        <v>0.97867072425191259</v>
       </c>
       <c r="AP58">
-        <v>1461.1234968689785</v>
+        <v>391.03672204826887</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -13789,16 +13789,16 @@
         <v>483</v>
       </c>
       <c r="Y59" t="s">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="Z59" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="AA59">
-        <v>0.99456659992729313</v>
+        <v>0.98919011268303692</v>
       </c>
       <c r="AB59">
-        <v>99.61233466629254</v>
+        <v>198.1812674776574</v>
       </c>
       <c r="AD59" t="s">
         <v>384</v>
@@ -13825,16 +13825,16 @@
         <v>648</v>
       </c>
       <c r="AM59" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AN59" t="s">
         <v>520</v>
       </c>
       <c r="AO59">
-        <v>0.9340841158361346</v>
+        <v>0.94830795758953823</v>
       </c>
       <c r="AP59">
-        <v>1208.4578763375325</v>
+        <v>947.68744419179825</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -13899,16 +13899,16 @@
         <v>485</v>
       </c>
       <c r="Y60" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="Z60" t="s">
-        <v>520</v>
+        <v>545</v>
       </c>
       <c r="AA60">
-        <v>0.93141537592166213</v>
+        <v>0.99654636831403465</v>
       </c>
       <c r="AB60">
-        <v>1257.384774769527</v>
+        <v>63.316580909365108</v>
       </c>
       <c r="AD60" t="s">
         <v>384</v>
@@ -13935,16 +13935,16 @@
         <v>650</v>
       </c>
       <c r="AM60" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AN60" t="s">
-        <v>743</v>
+        <v>525</v>
       </c>
       <c r="AO60">
-        <v>0.99727633984664521</v>
+        <v>0.93780897896633364</v>
       </c>
       <c r="AP60">
-        <v>49.933769478171371</v>
+        <v>1140.1687189505506</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14009,16 +14009,16 @@
         <v>487</v>
       </c>
       <c r="Y61" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="Z61" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="AA61">
-        <v>0.98397547854041056</v>
+        <v>0.99693888695694832</v>
       </c>
       <c r="AB61">
-        <v>293.78289342580621</v>
+        <v>56.120405789280852</v>
       </c>
       <c r="AD61" t="s">
         <v>384</v>
@@ -14045,16 +14045,16 @@
         <v>652</v>
       </c>
       <c r="AM61" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="AN61" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO61">
-        <v>0.95560390571555842</v>
+        <v>0.99188597448157934</v>
       </c>
       <c r="AP61">
-        <v>813.92839521476139</v>
+        <v>148.75713450437817</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14119,16 +14119,16 @@
         <v>489</v>
       </c>
       <c r="Y62" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Z62" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="AA62">
-        <v>0.93395005189428693</v>
+        <v>0.95701836677838237</v>
       </c>
       <c r="AB62">
-        <v>1210.915715271407</v>
+        <v>787.99660906299084</v>
       </c>
       <c r="AD62" t="s">
         <v>384</v>
@@ -14155,16 +14155,16 @@
         <v>654</v>
       </c>
       <c r="AM62" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="AN62" t="s">
-        <v>520</v>
+        <v>744</v>
       </c>
       <c r="AO62">
-        <v>0.94915344933102974</v>
+        <v>0.99696250898544003</v>
       </c>
       <c r="AP62">
-        <v>932.18676226445439</v>
+        <v>55.687335266933502</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14229,16 +14229,16 @@
         <v>491</v>
       </c>
       <c r="Y63" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="Z63" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="AA63">
-        <v>0.9946704540941137</v>
+        <v>0.94701516843854283</v>
       </c>
       <c r="AB63">
-        <v>97.708341607915628</v>
+        <v>971.38857862671478</v>
       </c>
       <c r="AD63" t="s">
         <v>384</v>
@@ -14265,16 +14265,16 @@
         <v>656</v>
       </c>
       <c r="AM63" t="s">
+        <v>745</v>
+      </c>
+      <c r="AN63" t="s">
         <v>746</v>
       </c>
-      <c r="AN63" t="s">
-        <v>520</v>
-      </c>
       <c r="AO63">
-        <v>0.9371750842720129</v>
+        <v>0.99732604522700541</v>
       </c>
       <c r="AP63">
-        <v>1151.7901216797641</v>
+        <v>49.02250417156759</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14339,16 +14339,16 @@
         <v>493</v>
       </c>
       <c r="Y64" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Z64" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="AA64">
-        <v>0.99392929419831677</v>
+        <v>0.98351827395448832</v>
       </c>
       <c r="AB64">
-        <v>111.29627303086014</v>
+        <v>302.16497750104838</v>
       </c>
       <c r="AD64" t="s">
         <v>384</v>
@@ -14378,13 +14378,13 @@
         <v>747</v>
       </c>
       <c r="AN64" t="s">
-        <v>748</v>
+        <v>520</v>
       </c>
       <c r="AO64">
-        <v>0.99358556749518001</v>
+        <v>0.92030235471623756</v>
       </c>
       <c r="AP64">
-        <v>117.59792925503248</v>
+        <v>1461.1234968689785</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14449,16 +14449,16 @@
         <v>495</v>
       </c>
       <c r="Y65" t="s">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="Z65" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="AA65">
-        <v>0.99241046515009568</v>
+        <v>0.99531334834867624</v>
       </c>
       <c r="AB65">
-        <v>139.14147224824609</v>
+        <v>85.921946940936536</v>
       </c>
       <c r="AD65" t="s">
         <v>384</v>
@@ -14485,16 +14485,16 @@
         <v>660</v>
       </c>
       <c r="AM65" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AN65" t="s">
         <v>520</v>
       </c>
       <c r="AO65">
-        <v>0.95872311541153676</v>
+        <v>0.9340841158361346</v>
       </c>
       <c r="AP65">
-        <v>756.74288412182625</v>
+        <v>1208.4578763375325</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -14559,16 +14559,16 @@
         <v>497</v>
       </c>
       <c r="Y66" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Z66" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AA66">
-        <v>0.99695853185056948</v>
+        <v>0.99169894704281958</v>
       </c>
       <c r="AB66">
-        <v>55.760249406226841</v>
+        <v>152.18597088164097</v>
       </c>
       <c r="AD66" t="s">
         <v>384</v>
@@ -14595,16 +14595,16 @@
         <v>662</v>
       </c>
       <c r="AM66" t="s">
+        <v>749</v>
+      </c>
+      <c r="AN66" t="s">
         <v>750</v>
       </c>
-      <c r="AN66" t="s">
-        <v>534</v>
-      </c>
       <c r="AO66">
-        <v>0.98080213304783737</v>
+        <v>0.99727633984664521</v>
       </c>
       <c r="AP66">
-        <v>351.96089412298221</v>
+        <v>49.933769478171371</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -14669,16 +14669,16 @@
         <v>499</v>
       </c>
       <c r="Y67" t="s">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="Z67" t="s">
-        <v>548</v>
+        <v>520</v>
       </c>
       <c r="AA67">
-        <v>0.99708131753222806</v>
+        <v>0.99247786079412359</v>
       </c>
       <c r="AB67">
-        <v>53.509178575819661</v>
+        <v>137.90588544106748</v>
       </c>
       <c r="AD67" t="s">
         <v>384</v>
@@ -14708,13 +14708,13 @@
         <v>751</v>
       </c>
       <c r="AN67" t="s">
-        <v>752</v>
+        <v>520</v>
       </c>
       <c r="AO67">
-        <v>0.9926254342737908</v>
+        <v>0.95560390571555842</v>
       </c>
       <c r="AP67">
-        <v>135.20037164716879</v>
+        <v>813.92839521476139</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -14779,16 +14779,16 @@
         <v>501</v>
       </c>
       <c r="Y68" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="Z68" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="AA68">
-        <v>0.98164032362202902</v>
+        <v>0.93331654548075482</v>
       </c>
       <c r="AB68">
-        <v>336.5940669294684</v>
+        <v>1222.529999519496</v>
       </c>
       <c r="AD68" t="s">
         <v>384</v>
@@ -14815,16 +14815,16 @@
         <v>666</v>
       </c>
       <c r="AM68" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AN68" t="s">
         <v>520</v>
       </c>
       <c r="AO68">
-        <v>0.922364240170786</v>
+        <v>0.94915344933102974</v>
       </c>
       <c r="AP68">
-        <v>1423.3222635355901</v>
+        <v>932.18676226445439</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -14889,16 +14889,16 @@
         <v>503</v>
       </c>
       <c r="Y69" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="Z69" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="AA69">
-        <v>0.96506973637135485</v>
+        <v>0.96180069092062781</v>
       </c>
       <c r="AB69">
-        <v>640.38816652516039</v>
+        <v>700.32066645515795</v>
       </c>
       <c r="AD69" t="s">
         <v>384</v>
@@ -14925,16 +14925,16 @@
         <v>668</v>
       </c>
       <c r="AM69" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="AN69" t="s">
         <v>520</v>
       </c>
       <c r="AO69">
-        <v>0.96559203855369335</v>
+        <v>0.9371750842720129</v>
       </c>
       <c r="AP69">
-        <v>630.81262651562236</v>
+        <v>1151.7901216797641</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -14999,16 +14999,16 @@
         <v>505</v>
       </c>
       <c r="Y70" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="Z70" t="s">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="AA70">
-        <v>0.99767908816061546</v>
+        <v>0.97274751764992162</v>
       </c>
       <c r="AB70">
-        <v>42.550050388717629</v>
+        <v>499.6288430847701</v>
       </c>
       <c r="AD70" t="s">
         <v>384</v>
@@ -15035,16 +15035,16 @@
         <v>670</v>
       </c>
       <c r="AM70" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AN70" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AO70">
-        <v>0.93218357774037441</v>
+        <v>0.9412405456309284</v>
       </c>
       <c r="AP70">
-        <v>1243.3010747598034</v>
+        <v>1077.2566634329794</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15109,16 +15109,16 @@
         <v>507</v>
       </c>
       <c r="Y71" t="s">
-        <v>370</v>
+        <v>325</v>
       </c>
       <c r="Z71" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="AA71">
-        <v>0.94624539205794911</v>
+        <v>0.9900739715800958</v>
       </c>
       <c r="AB71">
-        <v>985.50114560426641</v>
+        <v>181.9771876982428</v>
       </c>
       <c r="AD71" t="s">
         <v>384</v>
@@ -15145,16 +15145,16 @@
         <v>672</v>
       </c>
       <c r="AM71" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AN71" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AO71">
-        <v>0.95152414227022919</v>
+        <v>0.97032680215300582</v>
       </c>
       <c r="AP71">
-        <v>888.72405837913129</v>
+        <v>544.00862719489396</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15219,16 +15219,16 @@
         <v>509</v>
       </c>
       <c r="Y72" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="Z72" t="s">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="AA72">
-        <v>0.93866072843058268</v>
+        <v>0.96390615299028259</v>
       </c>
       <c r="AB72">
-        <v>1124.553312105985</v>
+        <v>661.7205285114859</v>
       </c>
       <c r="AD72" t="s">
         <v>384</v>
@@ -15255,16 +15255,16 @@
         <v>674</v>
       </c>
       <c r="AM72" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AN72" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AO72">
-        <v>0.95404010460315924</v>
+        <v>0.94676925034254755</v>
       </c>
       <c r="AP72">
-        <v>842.59808227541362</v>
+        <v>975.89707705329522</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -15329,16 +15329,16 @@
         <v>511</v>
       </c>
       <c r="Y73" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="Z73" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="AA73">
-        <v>0.98919011268303692</v>
+        <v>0.9445225305044197</v>
       </c>
       <c r="AB73">
-        <v>198.1812674776574</v>
+        <v>1017.0869407523058</v>
       </c>
       <c r="AD73" t="s">
         <v>384</v>
@@ -15365,16 +15365,16 @@
         <v>676</v>
       </c>
       <c r="AM73" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AN73" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="AO73">
-        <v>0.92828711808630038</v>
+        <v>0.97192734479279941</v>
       </c>
       <c r="AP73">
-        <v>1314.7361684178261</v>
+        <v>514.66534546534479</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -15439,16 +15439,16 @@
         <v>513</v>
       </c>
       <c r="Y74" t="s">
-        <v>329</v>
+        <v>381</v>
       </c>
       <c r="Z74" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="AA74">
-        <v>0.99654636831403465</v>
+        <v>0.98504860509376779</v>
       </c>
       <c r="AB74">
-        <v>63.316580909365108</v>
+        <v>274.10890661425793</v>
       </c>
       <c r="AD74" t="s">
         <v>384</v>
@@ -15475,16 +15475,16 @@
         <v>678</v>
       </c>
       <c r="AM74" t="s">
+        <v>758</v>
+      </c>
+      <c r="AN74" t="s">
         <v>759</v>
       </c>
-      <c r="AN74" t="s">
-        <v>520</v>
-      </c>
       <c r="AO74">
-        <v>0.99154375423443009</v>
+        <v>0.99431725858154596</v>
       </c>
       <c r="AP74">
-        <v>155.03117236878097</v>
+        <v>104.18359267165788</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -15549,16 +15549,16 @@
         <v>515</v>
       </c>
       <c r="Y75" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="Z75" t="s">
         <v>551</v>
       </c>
       <c r="AA75">
-        <v>0.99693888695694832</v>
+        <v>0.99519548170790972</v>
       </c>
       <c r="AB75">
-        <v>56.120405789280852</v>
+        <v>88.082835354989243</v>
       </c>
       <c r="AD75" t="s">
         <v>384</v>
@@ -15591,10 +15591,10 @@
         <v>520</v>
       </c>
       <c r="AO75">
-        <v>0.9654653203800333</v>
+        <v>0.93434249421812909</v>
       </c>
       <c r="AP75">
-        <v>633.13579303272206</v>
+        <v>1203.7209393342998</v>
       </c>
     </row>
   </sheetData>
@@ -15603,7 +15603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C547CEFB-EFA3-465A-9DE1-D0A2F4015E2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C4E5E6-CDCF-4AB6-B264-AF91624784FD}">
   <dimension ref="B9:Z75"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15715,7 +15715,7 @@
         <v>801</v>
       </c>
       <c r="K11" t="s">
-        <v>717</v>
+        <v>686</v>
       </c>
       <c r="L11">
         <v>0.70776635133171628</v>
@@ -15748,7 +15748,7 @@
         <v>931</v>
       </c>
       <c r="X11" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="Y11">
         <v>11.795999999999999</v>
@@ -15783,7 +15783,7 @@
         <v>803</v>
       </c>
       <c r="K12" t="s">
-        <v>685</v>
+        <v>708</v>
       </c>
       <c r="L12">
         <v>2.8200477507065131</v>
@@ -15816,7 +15816,7 @@
         <v>933</v>
       </c>
       <c r="X12" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="Y12">
         <v>3.17625</v>
@@ -15851,7 +15851,7 @@
         <v>805</v>
       </c>
       <c r="K13" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="L13">
         <v>3.3152093895010868</v>
@@ -15884,7 +15884,7 @@
         <v>935</v>
       </c>
       <c r="X13" t="s">
-        <v>781</v>
+        <v>797</v>
       </c>
       <c r="Y13">
         <v>0.83550000000000002</v>
@@ -15919,7 +15919,7 @@
         <v>807</v>
       </c>
       <c r="K14" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L14">
         <v>38.566850937358645</v>
@@ -15952,7 +15952,7 @@
         <v>937</v>
       </c>
       <c r="X14" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="Y14">
         <v>2.22675</v>
@@ -15987,7 +15987,7 @@
         <v>809</v>
       </c>
       <c r="K15" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="L15">
         <v>2.0845713431158761</v>
@@ -16020,7 +16020,7 @@
         <v>939</v>
       </c>
       <c r="X15" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="Y15">
         <v>4.7437500000000004</v>
@@ -16055,7 +16055,7 @@
         <v>811</v>
       </c>
       <c r="K16" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="L16">
         <v>5.0973809601425186</v>
@@ -16088,7 +16088,7 @@
         <v>941</v>
       </c>
       <c r="X16" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="Y16">
         <v>11.138249999999999</v>
@@ -16123,7 +16123,7 @@
         <v>813</v>
       </c>
       <c r="K17" t="s">
-        <v>715</v>
+        <v>684</v>
       </c>
       <c r="L17">
         <v>0.30859956153411233</v>
@@ -16156,7 +16156,7 @@
         <v>943</v>
       </c>
       <c r="X17" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="Y17">
         <v>4.9755000000000003</v>
@@ -16191,7 +16191,7 @@
         <v>815</v>
       </c>
       <c r="K18" t="s">
-        <v>720</v>
+        <v>689</v>
       </c>
       <c r="L18">
         <v>1.8791475076628852</v>
@@ -16259,7 +16259,7 @@
         <v>817</v>
       </c>
       <c r="K19" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="L19">
         <v>5.5730316958223378</v>
@@ -16292,7 +16292,7 @@
         <v>947</v>
       </c>
       <c r="X19" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="Y19">
         <v>2.8919999999999999</v>
@@ -16327,7 +16327,7 @@
         <v>819</v>
       </c>
       <c r="K20" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="L20">
         <v>6.4986819696730596</v>
@@ -16360,7 +16360,7 @@
         <v>949</v>
       </c>
       <c r="X20" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="Y20">
         <v>2.1</v>
@@ -16395,7 +16395,7 @@
         <v>821</v>
       </c>
       <c r="K21" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="L21">
         <v>50.305360025131641</v>
@@ -16430,7 +16430,7 @@
         <v>823</v>
       </c>
       <c r="K22" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="L22">
         <v>19.303135607289168</v>
@@ -16465,7 +16465,7 @@
         <v>825</v>
       </c>
       <c r="K23" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="L23">
         <v>42.25643238813123</v>
@@ -16500,7 +16500,7 @@
         <v>827</v>
       </c>
       <c r="K24" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="L24">
         <v>34.587215740299207</v>
@@ -16535,7 +16535,7 @@
         <v>829</v>
       </c>
       <c r="K25" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="L25">
         <v>42.529732597711799</v>
@@ -16570,7 +16570,7 @@
         <v>831</v>
       </c>
       <c r="K26" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="L26">
         <v>25.462515402991507</v>
@@ -16605,7 +16605,7 @@
         <v>833</v>
       </c>
       <c r="K27" t="s">
-        <v>723</v>
+        <v>692</v>
       </c>
       <c r="L27">
         <v>27.658680455660367</v>
@@ -16640,7 +16640,7 @@
         <v>835</v>
       </c>
       <c r="K28" t="s">
-        <v>699</v>
+        <v>740</v>
       </c>
       <c r="L28">
         <v>26.661225597421318</v>
@@ -16675,7 +16675,7 @@
         <v>837</v>
       </c>
       <c r="K29" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="L29">
         <v>43.955323212040426</v>
@@ -16710,7 +16710,7 @@
         <v>839</v>
       </c>
       <c r="K30" t="s">
-        <v>754</v>
+        <v>723</v>
       </c>
       <c r="L30">
         <v>16.489617433165694</v>
@@ -16745,7 +16745,7 @@
         <v>841</v>
       </c>
       <c r="K31" t="s">
-        <v>749</v>
+        <v>702</v>
       </c>
       <c r="L31">
         <v>25.647547433244167</v>
@@ -16780,7 +16780,7 @@
         <v>843</v>
       </c>
       <c r="K32" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="L32">
         <v>65.823870400996412</v>
@@ -16815,7 +16815,7 @@
         <v>845</v>
       </c>
       <c r="K33" t="s">
-        <v>722</v>
+        <v>691</v>
       </c>
       <c r="L33">
         <v>107.3286538829402</v>
@@ -16850,7 +16850,7 @@
         <v>847</v>
       </c>
       <c r="K34" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="L34">
         <v>100.56047380683498</v>
@@ -16885,7 +16885,7 @@
         <v>849</v>
       </c>
       <c r="K35" t="s">
-        <v>690</v>
+        <v>757</v>
       </c>
       <c r="L35">
         <v>78.197884523894999</v>
@@ -16920,7 +16920,7 @@
         <v>851</v>
       </c>
       <c r="K36" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="L36">
         <v>123.17884915939072</v>
@@ -16955,7 +16955,7 @@
         <v>853</v>
       </c>
       <c r="K37" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="L37">
         <v>71.143701624958894</v>
@@ -16990,7 +16990,7 @@
         <v>855</v>
       </c>
       <c r="K38" t="s">
-        <v>687</v>
+        <v>754</v>
       </c>
       <c r="L38">
         <v>78.488972319419887</v>
@@ -17025,7 +17025,7 @@
         <v>857</v>
       </c>
       <c r="K39" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
       <c r="L39">
         <v>52.43600239879752</v>
@@ -17060,7 +17060,7 @@
         <v>859</v>
       </c>
       <c r="K40" t="s">
-        <v>755</v>
+        <v>724</v>
       </c>
       <c r="L40">
         <v>49.250791120392286</v>
@@ -17095,7 +17095,7 @@
         <v>861</v>
       </c>
       <c r="K41" t="s">
-        <v>753</v>
+        <v>722</v>
       </c>
       <c r="L41">
         <v>63.229876995732269</v>
@@ -17130,7 +17130,7 @@
         <v>863</v>
       </c>
       <c r="K42" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="L42">
         <v>58.0478004394026</v>
@@ -17165,7 +17165,7 @@
         <v>865</v>
       </c>
       <c r="K43" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L43">
         <v>66.810878639655797</v>
@@ -17200,7 +17200,7 @@
         <v>867</v>
       </c>
       <c r="K44" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="L44">
         <v>49.137871464813081</v>
@@ -17235,7 +17235,7 @@
         <v>869</v>
       </c>
       <c r="K45" t="s">
-        <v>689</v>
+        <v>756</v>
       </c>
       <c r="L45">
         <v>61.706057214399763</v>
@@ -17270,7 +17270,7 @@
         <v>871</v>
       </c>
       <c r="K46" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="L46">
         <v>33.734564973116228</v>
@@ -17305,7 +17305,7 @@
         <v>873</v>
       </c>
       <c r="K47" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="L47">
         <v>47.816600382052599</v>
@@ -17340,7 +17340,7 @@
         <v>875</v>
       </c>
       <c r="K48" t="s">
-        <v>758</v>
+        <v>735</v>
       </c>
       <c r="L48">
         <v>46.698997298088187</v>
@@ -17375,7 +17375,7 @@
         <v>877</v>
       </c>
       <c r="K49" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="L49">
         <v>75.050246959082855</v>
@@ -17410,7 +17410,7 @@
         <v>879</v>
       </c>
       <c r="K50" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="L50">
         <v>106.7956382872259</v>
@@ -17445,7 +17445,7 @@
         <v>881</v>
       </c>
       <c r="K51" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="L51">
         <v>69.596976409703828</v>
@@ -17480,7 +17480,7 @@
         <v>883</v>
       </c>
       <c r="K52" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="L52">
         <v>86.713798928451226</v>
@@ -17515,7 +17515,7 @@
         <v>885</v>
       </c>
       <c r="K53" t="s">
-        <v>697</v>
+        <v>738</v>
       </c>
       <c r="L53">
         <v>38.863455871308048</v>
@@ -17550,7 +17550,7 @@
         <v>887</v>
       </c>
       <c r="K54" t="s">
-        <v>688</v>
+        <v>755</v>
       </c>
       <c r="L54">
         <v>42.51850066462562</v>
@@ -17585,7 +17585,7 @@
         <v>889</v>
       </c>
       <c r="K55" t="s">
-        <v>682</v>
+        <v>705</v>
       </c>
       <c r="L55">
         <v>47.929375805367769</v>
@@ -17620,7 +17620,7 @@
         <v>891</v>
       </c>
       <c r="K56" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="L56">
         <v>77.393342850934502</v>
@@ -17655,7 +17655,7 @@
         <v>893</v>
       </c>
       <c r="K57" t="s">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="L57">
         <v>45.478139706797812</v>
@@ -17690,7 +17690,7 @@
         <v>895</v>
       </c>
       <c r="K58" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="L58">
         <v>48.140294920365903</v>
@@ -17725,7 +17725,7 @@
         <v>897</v>
       </c>
       <c r="K59" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="L59">
         <v>47.844720893056341</v>
@@ -17760,7 +17760,7 @@
         <v>899</v>
       </c>
       <c r="K60" t="s">
-        <v>760</v>
+        <v>737</v>
       </c>
       <c r="L60">
         <v>98.68994695303239</v>
@@ -17795,7 +17795,7 @@
         <v>901</v>
       </c>
       <c r="K61" t="s">
-        <v>724</v>
+        <v>693</v>
       </c>
       <c r="L61">
         <v>87.202849070038098</v>
@@ -17830,7 +17830,7 @@
         <v>903</v>
       </c>
       <c r="K62" t="s">
-        <v>698</v>
+        <v>739</v>
       </c>
       <c r="L62">
         <v>81.518015488521129</v>
@@ -17865,7 +17865,7 @@
         <v>905</v>
       </c>
       <c r="K63" t="s">
-        <v>725</v>
+        <v>694</v>
       </c>
       <c r="L63">
         <v>110.24417575298389</v>
@@ -17900,7 +17900,7 @@
         <v>907</v>
       </c>
       <c r="K64" t="s">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="L64">
         <v>56.928196652598764</v>
@@ -17935,7 +17935,7 @@
         <v>909</v>
       </c>
       <c r="K65" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="L65">
         <v>57.985815283224305</v>
@@ -17970,7 +17970,7 @@
         <v>911</v>
       </c>
       <c r="K66" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="L66">
         <v>15.637923531445407</v>
@@ -18005,7 +18005,7 @@
         <v>913</v>
       </c>
       <c r="K67" t="s">
-        <v>719</v>
+        <v>688</v>
       </c>
       <c r="L67">
         <v>51.794566350258954</v>
@@ -18040,7 +18040,7 @@
         <v>915</v>
       </c>
       <c r="K68" t="s">
-        <v>714</v>
+        <v>683</v>
       </c>
       <c r="L68">
         <v>78.70246336743719</v>
@@ -18075,7 +18075,7 @@
         <v>917</v>
       </c>
       <c r="K69" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="L69">
         <v>86.908524101933608</v>
@@ -18110,7 +18110,7 @@
         <v>919</v>
       </c>
       <c r="K70" t="s">
-        <v>683</v>
+        <v>706</v>
       </c>
       <c r="L70">
         <v>29.976025047721809</v>
@@ -18145,7 +18145,7 @@
         <v>921</v>
       </c>
       <c r="K71" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L71">
         <v>55.882428131538255</v>
@@ -18180,7 +18180,7 @@
         <v>923</v>
       </c>
       <c r="K72" t="s">
-        <v>747</v>
+        <v>700</v>
       </c>
       <c r="L72">
         <v>58.276159234953511</v>
@@ -18215,7 +18215,7 @@
         <v>925</v>
       </c>
       <c r="K73" t="s">
-        <v>751</v>
+        <v>720</v>
       </c>
       <c r="L73">
         <v>54.455844858601104</v>
@@ -18250,7 +18250,7 @@
         <v>927</v>
       </c>
       <c r="K74" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="L74">
         <v>1.0625916947319844</v>
@@ -18285,7 +18285,7 @@
         <v>929</v>
       </c>
       <c r="K75" t="s">
-        <v>710</v>
+        <v>758</v>
       </c>
       <c r="L75">
         <v>19.300562207456217</v>
@@ -18300,7 +18300,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1764C7C-D4B4-4716-B0DD-9114EDFEB7F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22B4B68-E7B6-4C49-B04B-F8E268348477}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
